--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -704,9 +704,181 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Katheryn Hunt</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GROW Marketing Agency (St. Louis, MO)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katherynhunt/</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small digital marketing agency (web design, digital marketing, branding). Confirmed small: 1-10 employees per Crunchbase, ~17 per ContactOut -- either way solidly inside the 5-50 band.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed small-agency founder wearing the ops hat -- one of the cleanest company-size confirmations in this batch.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Adam Goyette</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Growth Union (Chicago) -- boutique growth agency for early-stage B2B SaaS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adam-goyette/</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ex-Help Scout / G2 growth marketing exec, now runs a small agency assembling senior marketers for early-stage B2B SaaS clients (Writer, RevenueHero, Recorded Future named as clients). Exact employee count unconfirmed but the agency's model (small senior team, no bench) implies well under 50.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Founder running a lean agency serving exactly the small-SaaS client base multiplayer targets; company size inferred from agency model, not directly confirmed -- worth a second look before approving.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>David Malevsky</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Lynx Growth Agency (Hallandale Beach, FL)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-malevsky/</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a boutique agency (patient acquisition for regenerative/integrative clinics) built around AI-driven marketing and automation. Employee count unconfirmed -- RocketReach shows only a handful of verified staff, consistent with a small shop.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Self-describes as 'resolving business challenges using AI' -- co-founder at a small, AI-forward agency is a strong qualitative fit even though the exact headcount isn't independently confirmed.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Alex Zlotko</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Forecastio (B2B sales forecasting for HubSpot)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexzlotko/</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17 years in B2B sales/CS, now CEO of Forecastio, a small SaaS company building sales forecasting tools. Publishes regularly on AI agents in RevOps specifically.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Small SaaS founder/CEO already writing publicly about AI agents in RevOps -- direct thematic overlap with multiplayer's pitch, though exact headcount at Forecastio is unconfirmed.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -720,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -867,9 +1039,52 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mike Rizzo</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MarketingOps.com / MO Pros</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikedrizzo/</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Founded and runs MO Pros, the 4,000+ member marketing-ops community outreach-pipeline-context.md names directly as a target community. Certifies GTM Ops teams and runs the annual MOpza conference.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Not a cold-outreach target -- he IS the gatekeeper of the exact community your context doc lists as a source. Worth a warmer, separate approach (community partnership / sponsorship) rather than a first-touch DM template.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="001155CC"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,10 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -428,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -505,7 +512,7 @@
           <t>PrecisionRevOps LLC</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/elizabeth-danowski-8b264513/</t>
         </is>
@@ -548,7 +555,7 @@
           <t>Lamande LLC (fractional RevOps for early/mid-stage SaaS); concurrent fractional roles at Rev, AgentSync, Ekho, OperateWise</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jeremy-lamande/</t>
         </is>
@@ -591,7 +598,7 @@
           <t>Revenue Wizards</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/posts/harisodobasic_what-does-revops-do-revenue-operations-activity-7263475951290740736-3JwA</t>
         </is>
@@ -634,7 +641,7 @@
           <t>Independent — C-Suite advisor across SaaS/AI/startup clients</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/deepa--patel/</t>
         </is>
@@ -677,7 +684,7 @@
           <t>Independent — B2B SaaS clients (~$2M+ ARR)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/mariyavaleva-yourscalingpartner/</t>
         </is>
@@ -720,7 +727,7 @@
           <t>GROW Marketing Agency (St. Louis, MO)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/katherynhunt/</t>
         </is>
@@ -763,7 +770,7 @@
           <t>Growth Union (Chicago) -- boutique growth agency for early-stage B2B SaaS</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/adam-goyette/</t>
         </is>
@@ -806,7 +813,7 @@
           <t>Lynx Growth Agency (Hallandale Beach, FL)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/david-malevsky/</t>
         </is>
@@ -849,7 +856,7 @@
           <t>Forecastio (B2B sales forecasting for HubSpot)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/alexzlotko/</t>
         </is>
@@ -876,12 +883,287 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Kristofer Wille</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>RevOps Consultant &amp; Advisor</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- RevOpsVision (Berlin)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kriswille-revopsvision-revenue-operations-consultant-advisory/</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10+ years in SalesOps/RevOps in Berlin's startup scene. Self-positions explicitly as helping 'C-Level Leaders &amp; Startups Supercharge Their Small RevOps Teams' -- his own tagline names the exact ICP.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>His public positioning IS the ICP description almost word-for-word (small RevOps teams at startups). Company size self-described, not independently verified.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Donna Sluijter</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Startup Operator -- RevOps &amp; Strategy</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Independent / embedded RevOps for startups</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/donnasluijter/</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Self-describes as a 'Startup Operator' bridging gaps and scaling teams in RevOps and strategy roles -- language that matches the ICP's 'founder wearing every hat' profile.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Title and self-description line up with the ICP almost exactly; specific current employer/headcount not independently confirmed.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>John McArdle</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Sequoia Solutions -- RevOps/HubSpot consultancy for early-stage B2B tech</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-mcardle-m-s-71b58178/</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Founded a small consultancy that has worked with dozens of early-stage companies cleaning up CRM/HubSpot data and building GTM systems -- not the 'Sequoia' VC firm, a separate small boutique of the same name.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Founder-led small consultancy serving exactly the early-stage company band multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Roberto Guerra</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Hub Latam -- RevOps + HubSpot for B2B companies in LATAM</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robguerra/</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Runs a boutique RevOps/HubSpot consultancy for B2B companies across LATAM, publicly writing about pipeline, CRM, forecasting -- and AI.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Boutique consultancy founder already writing about AI in the RevOps workflow -- direct thematic and company-stage fit.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Kristy Buige</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Boutique RevOps consultancy -- B2B SaaS GTM systems</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristybuige/</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Founded and leads a boutique RevOps consultancy enabling B2B SaaS companies to scale GTM systems, processes, and revenue performance.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small consultancy serving the same small-SaaS client base as several other rows in this sheet -- exact company name/size not independently confirmed beyond 'boutique.'</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Johnathan Wang</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>The SaaS Consultants -- fractional CMO / marketing agency for SaaS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnathan-wang/</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Runs a small fractional-CMO agency for SaaS businesses and has personally built social-media-management software using Python/JavaScript and AI -- technical enough to be a strong early adopter.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder who is also hands-on technical/AI-building -- good combination of ICP fit and early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -969,7 +1251,7 @@
           <t>Substack (independent) — background includes marketing ops leadership at Amazon</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>https://darrellalfonso.substack.com/</t>
         </is>
@@ -1012,7 +1294,7 @@
           <t>Substack (independent)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>https://jenbergren.substack.com/</t>
         </is>
@@ -1055,7 +1337,7 @@
           <t>MarketingOps.com / MO Pros</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/mikedrizzo/</t>
         </is>
@@ -1088,6 +1370,11 @@
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -445,8 +445,9 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,10 +488,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Draft Message</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Date Found</t>
         </is>
@@ -532,8 +538,13 @@
           <t>Founder of a small (solo/very small) RevOps consulting shop -- exact ICP fit on company stage and role. Likely juggling multiple client workstreams solo, a strong proxy for the 'no shared visibility' pain.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Hey Elizabeth — saw you're running RevOps solo through PrecisionRevOps for multiple SaaS clients. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -575,8 +586,13 @@
           <t>Runs a small consulting practice AND sits inside multiple small SaaS teams concurrently (classic 5-50 person startup engagements) -- doubles as both a direct lead and a channel into several ICP companies at once.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jeremy — saw you're juggling fractional RevOps/CRO roles across Rev, AgentSync, Ekho, and OperateWise at once. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -618,8 +634,13 @@
           <t>Co-founder wearing the ops hat at a small consulting shop; his own public content (silos, alignment) lines up directly with the 'scattered, untracked work' pitch angle.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Hey Haris — saw your recent post on what RevOps actually does and removing GTM silos. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -661,8 +682,13 @@
           <t>Independent operator serving several small/startup clients in parallel -- same 'context lost across separate chats' problem multiplied across accounts rather than teammates.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Hey Deepa — saw you're advising several high-growth startups at once as a fractional RevOps/strategy leader. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -704,8 +730,13 @@
           <t>Ops-adjacent (finance) leader embedded in multiple small SaaS teams; weaker fit than the RevOps/MOps rows above but same team-size band and same fractional-across-many-small-teams dynamic -- worth a lower-priority pass.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mariya — saw you work as a fractional CFO across multiple early-stage B2B SaaS clients. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -747,8 +778,13 @@
           <t>Confirmed small-agency founder wearing the ops hat -- one of the cleanest company-size confirmations in this batch.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Hey Katheryn — saw you're running GROW Marketing Agency as a small, founder-led shop. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -790,8 +826,13 @@
           <t>Founder running a lean agency serving exactly the small-SaaS client base multiplayer targets; company size inferred from agency model, not directly confirmed -- worth a second look before approving.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adam — saw you've built a lean senior team at Growth Union for early-stage B2B SaaS clients like Writer and Recorded Future. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -833,8 +874,13 @@
           <t>Self-describes as 'resolving business challenges using AI' -- co-founder at a small, AI-forward agency is a strong qualitative fit even though the exact headcount isn't independently confirmed.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Hey David — saw you're building Lynx Growth Agency around AI-driven marketing and automation. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -876,8 +922,13 @@
           <t>Small SaaS founder/CEO already writing publicly about AI agents in RevOps -- direct thematic overlap with multiplayer's pitch, though exact headcount at Forecastio is unconfirmed.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex — saw your writing on AI agents in RevOps as CEO of Forecastio. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -919,8 +970,13 @@
           <t>His public positioning IS the ICP description almost word-for-word (small RevOps teams at startups). Company size self-described, not independently verified.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristofer — saw your tagline about helping startups supercharge their small RevOps teams. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -962,8 +1018,13 @@
           <t>Title and self-description line up with the ICP almost exactly; specific current employer/headcount not independently confirmed.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Hey Donna — saw your work bridging gaps and scaling teams as a startup RevOps operator. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1005,8 +1066,13 @@
           <t>Founder-led small consultancy serving exactly the early-stage company band multiplayer targets.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Hey John — saw the dozens of early-stage companies you've helped clean up CRM/HubSpot data at Sequoia Solutions. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1048,8 +1114,13 @@
           <t>Boutique consultancy founder already writing about AI in the RevOps workflow -- direct thematic and company-stage fit.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Hey Roberto — saw your posts on pipeline, forecasting, and AI at Revenue Hub Latam. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1091,8 +1162,13 @@
           <t>Founder of a small consultancy serving the same small-SaaS client base as several other rows in this sheet -- exact company name/size not independently confirmed beyond 'boutique.'</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristy — saw scaling GTM systems for B2B SaaS companies through your boutique RevOps consultancy. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1134,8 +1210,13 @@
           <t>Small agency founder who is also hands-on technical/AI-building -- good combination of ICP fit and early-adopter likelihood.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Hey Johnathan — saw you built your own AI-powered social media tooling while running The SaaS Consultants. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1143,7 +1224,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1174,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1184,8 +1265,9 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1226,10 +1308,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Draft Message</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Date Found</t>
         </is>
@@ -1271,8 +1358,13 @@
           <t>Not a direct ICP lead -- flagged separately as a possible content/community distribution channel into the exact audience (marketing ops leads at small teams) rather than a cold-outreach target.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Hey Darrell — saw your newsletter on marketing ops team structure and career growth. I'm building multiplayer, a shared AI workspace for small ops teams — not pitching the community, just curious whether the 'everyone's using ChatGPT/Claude solo, zero shared visibility' problem is something you hear from members often. Open to a quick chat, and happy to share back whatever I learn.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1314,8 +1406,13 @@
           <t>Same as Darrell Alfonso above -- a distribution/connector play into the ICP audience, not a direct 5-50 person company lead.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jen — saw your weekly newsletter for the marketing ops community. I'm building multiplayer, a shared AI workspace for small ops teams — not pitching the community, just curious whether the 'everyone's using ChatGPT/Claude solo, zero shared visibility' problem is something you hear from members often. Open to a quick chat, and happy to share back whatever I learn.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1357,8 +1454,13 @@
           <t>Not a cold-outreach target -- he IS the gatekeeper of the exact community your context doc lists as a source. Worth a warmer, separate approach (community partnership / sponsorship) rather than a first-touch DM template.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mike — saw MO Pros hitting 4,000+ marketing/RevOps members. I'm building multiplayer, a shared AI workspace for small ops teams — not pitching the community, just curious whether the 'everyone's using ChatGPT/Claude solo, zero shared visibility' problem is something you hear from members often. Open to a quick chat, and happy to share back whatever I learn.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1366,7 +1468,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1222,9 +1222,729 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Shaun Anderson</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>thisisagency.ai / hobo-web.co.uk -- forensic SEO agency</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shaun-anderson-hobo/</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small forensic-SEO agency, also positions himself as an AI Marketing Engineer building agentic AI systems. Found via a single search pass, not cross-verified for exact headcount.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder already hands-on with agentic AI -- strong thematic fit; company size inferred from agency type, not confirmed.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Hey Shaun — saw you're building agentic AI systems as an AI Marketing Engineer while running thisisagency.ai. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Jackie Connors</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Direction -- virtual HubSpot partner agency</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jackiebconnors/</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small virtual agency offering HubSpot/inbound training, consulting and content marketing. Size not independently confirmed beyond 'virtual agency' framing.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Founder-led small HubSpot partner shop -- same ops-tooling audience multiplayer is targeting.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jackie — saw you run Digital Marketing Direction as a virtual HubSpot partner agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Sam Anderson</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Chief Growth Officer / Founder</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Origin 63 -- small growth agency</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samanderson41/</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Founder-level growth leader at a self-described small agency. Weaker verification than other rows -- single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Small growth-agency founder; include but treat as lower-confidence given only one source found.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sam — saw you're running Origin 63 as a small, results-focused growth agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Josh Harcus</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Growth &amp; Retention Lead</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Hüify -- HubSpot partner agency</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joshharcus/</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Works on revenue growth/retention at a HubSpot partner agency. Exact headcount at Hüify unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>HubSpot-partner-agency operator in the ops-tooling audience; company size inferred, not confirmed.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Hey Josh — saw your work on revenue growth and retention at Hüify, a HubSpot partner agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Alex Williams</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Independent HubSpot Consultant</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- solo HubSpot consulting practice</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/awoxford/</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Solo independent HubSpot implementation/strategy consultant -- a one-person shop, which is close to the purest form of the 'wearing every hat, no one to share tool context with' ICP signal.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Solo consultant -- exact company-stage fit by definition, though this is a one-person 'team' rather than 5-50 people; worth including as a different flavor of the same pain (no one to share context with at all).</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex — saw you run your own solo HubSpot consulting practice. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Clwyd Probert</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Founder, AI Consultant</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Whitehat (UK) -- AI consulting</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/clwyd-probert</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>CEO/Founder and AI consultant; company size and exact scope of Whitehat not independently confirmed -- single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Directly in the AI-adoption-for-small-business space -- strong thematic fit, weaker company-size confirmation.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Hey Clwyd — saw you work as an AI consultant at Whitehat, helping businesses adopt AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Clara Ma</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Chief of Staff (Employee #3)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Kairos -- very early-stage startup</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clarama/</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Chief of Staff at a very early-stage startup (self-described as employee #3) -- partners with founders through the hardest parts of scaling. About as small/early as the ICP gets.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Employee #3 at an early-stage startup wearing the ops/chief-of-staff hat -- textbook ICP fit on company stage.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Hey Clara — saw you're employee #3 and Chief of Staff at Kairos. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Josephine Conneely</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Chief of Staff -- GTM, Operations, AI</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed (UK-based startup)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/josephineconneely</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Chief of Staff with GTM/Operations/AI explicitly in her title -- current employer name and headcount not independently confirmed.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Title puts AI and ops in the same remit -- strong thematic fit; company-size confirmation weaker than other rows.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Hey Josephine — saw your Chief of Staff role spanning GTM, Operations, and AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Riddhi Sharma</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Founder</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Thought In A Dot -- content marketing agency</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sharmariddhi/</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14+ years in leadership/brand content strategy, now founder/CEO of a content marketing agency. Employee count unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder in the marketing-ops-adjacent content space.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Hey Riddhi — saw you're running Thought In A Dot as a content marketing agency and brand strategist. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>John Liska</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Creative Engine (Austin, TX) -- branding &amp; digital marketing agency</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-liska-594a52193/</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small branding/digital marketing agency in Austin. Employee count unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- fits the company-stage band, size inferred not confirmed.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Hey John — saw you founded Creative Engine, a branding and digital marketing agency in Austin. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Ajay G.</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>MAWD Agency -- Google Ads/SEO/websites for small businesses</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ajayg514/</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small AI-forward performance-marketing agency serving small-business clients.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder in the exact small-business-serving segment; last-name not public in the source, listed as found.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ajay — saw you run MAWD Agency managing Google Ads, SEO, and websites for small businesses. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Raj Goodman Anand</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Goodman Lantern -- B2B content marketing agency</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rajanand/</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a B2B content marketing agency serving clients across several continents -- distributed small team model, not independently headcount-confirmed.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Founder wearing the ops/marketing hat; 'across five continents' framing suggests a distributed small team rather than a large single office, but worth double-checking size before approving.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Hey Raj — saw you're running Goodman Lantern, a B2B content marketing agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Laney M. Silverman</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>The Design Boutique, Inc.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thedesignboutique/</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a self-described boutique design agency, explicitly positioned around small-team speed/agility.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly 'boutique' self-positioning -- good qualitative company-size signal even without a hard headcount number.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Hey Laney — saw you run The Design Boutique and pride yourselves on being able to pivot quickly as a small shop. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Kranzle</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Founder, Director</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Venture Visuals (Seattle) -- creative agency</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomaskranzle/</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Founder/Director of a small creative agency in Seattle. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Hey Thomas — saw you founded Venture Visuals, a creative agency in Seattle. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Santosh Kushwaha</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Visual Best -- AI Creative Production Agency</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/in/santosh-kushwaha-explorer</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small, explicitly AI-native creative production agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>AI-native agency founder -- strong thematic fit, company size inferred not confirmed.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Hey Santosh — saw you're running Visual Best, an AI creative production agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1244,6 +1964,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1942,9 +1942,633 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>David Simões</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Sounds Good Agency -- Shopify Plus partner (CEE region)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://cz.linkedin.com/in/davidjsimoes/en</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a Shopify Plus agency serving DTC/B2B/Retail brands, self-describes as having an 'AI-first business mindset.' Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder explicitly framing the business around AI-first thinking -- strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Hey David — saw you describe your business as having an AI-first mindset while running Sounds Good Agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Mark Kennaley</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>SoftwareFactory.ai -- AI-native software engineering consultancy</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/markkennaley/</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small AI-native software engineering consultancy. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Small AI-forward software consultancy founder -- exactly the kind of technical early adopter this product needs.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mark — saw you're a pioneer in AI-native software engineering as founder of SoftwareFactory.ai. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Philip Ledgerwood</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>AI Consultant / Software Developer</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- solo AI consulting practice</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/phil-ledgerwood/</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Solo independent consultant helping companies adopt AI securely. One-person practice -- same 'no one to share context with' signal as other solo consultants in this sheet.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Solo AI consultant -- direct thematic fit and purest form of the company-stage signal.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Hey Philip — saw you help companies use AI securely and purposefully as an independent consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Dylan Kinder</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Independent AI Consultant</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- installs AI systems into service businesses</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dylankinder/</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Solo consultant helping small service businesses adopt AI tooling. Weaker verification -- single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Solo AI-adoption consultant serving small businesses -- direct thematic fit, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dylan — saw you install AI systems into service businesses as an independent consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Alex Marantelos</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder / CEO</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Intryc (Y Combinator S24)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexmarantelos/</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a YC S24-batch startup -- confirmed very-early-stage by accelerator batch, though exact current headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage (accelerator batch is public record) even without a hard headcount number.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex — saw you're co-founder/CEO of Intryc, a Y Combinator S24 startup. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Arham Khan</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Pixated -- performance marketing agency (paid social/search)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/arhamkhan</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small performance marketing agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Hey Arham — saw you founded Pixated, a performance marketing agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Alex Brown</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Tierra -- performance marketing agency for DTC ecommerce</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-brown-tierra/</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small performance marketing agency for DTC ecommerce brands. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex — saw you're scaling DTC ecommerce brands through Tierra. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Oles Dziub</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Hey Digital -- SaaS performance marketing &amp; creative agency</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oles-dziub-b2b-saas-paid-ads-expert/</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a small agency specializing in paid ads for B2B SaaS companies -- serves exactly multiplayer's target client base.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Agency founder specializing in the B2B SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Hey Oles — saw you're running Hey Digital, a performance marketing agency focused specifically on B2B SaaS. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Beckie Blackburn-Cooper</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Boutique recruiting agency</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/beckie-blackburn-cooper-bri/</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small, self-described boutique recruiting agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly 'boutique' self-positioning -- good qualitative size signal; different vertical (recruiting) than most of this sheet, useful diversification.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Hey Beckie — saw you run a boutique recruiting agency with a niche sector focus. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Katie Matthews</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>CollabRecruit -- small recruiting agency</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kmtalentfinder/</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small recruiting agency, writes publicly about technology's role in staffing. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder already thinking publicly about tech's role in her business -- good adoption-readiness signal.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Hey Katie — saw your writing on balancing technology and human connection in recruiting at CollabRecruit. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Becky Kuntz</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>BK's Bookkeeping</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/becky-kuntz/</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small virtual bookkeeping practice serving small-business clients. Finance-ops-adjacent, similar band to Mariya Valeva elsewhere in this sheet.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Small finance-ops shop founder -- weaker fit than marketing/RevOps rows but same company-stage band and same 'wearing every hat' pain.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Hey Becky — saw you help small business owners get time back through BK's Bookkeeping. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Tom Wells</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Business Development</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Wells Virtual Bookkeeping, LLC</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom-wells-rad60/</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Small virtual bookkeeping practice; actively participates in an AI Mastermind group -- already engaged with AI adoption specifically.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Small ops-adjacent shop already active in an AI-adoption community -- good readiness signal despite being outside core marketing/RevOps.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Hey Tom — saw you're part of an AI Mastermind group applying tech-forward solutions to bookkeeping. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer Perez-Fong</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Bookkeeping Done Right</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jennifer-perez-fong-cpa/</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>CEO/founder of a small accounting practice serving SMBs, founded 2013. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Small finance-ops shop founder -- same lower-priority band as other bookkeeping rows in this sheet.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jennifer — saw you founded Bookkeeping Done Right to serve small and medium businesses in South Florida. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1979,6 +2603,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2566,9 +2566,729 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Parry Headrick</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Crackle PR -- B2B tech PR agency (Boston)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/parryheadrick/</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small B2B tech PR agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>B2B-tech-focused small agency founder -- adjacent vertical (PR) serving the same kind of small SaaS/tech clients.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Hey Parry — saw you're leading a team of senior PR leaders at Crackle PR. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Carin Warner</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Warner Communications -- PR &amp; comms strategy</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carinwarner/</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a small PR/comms firm, publishes on AI strategy in communications specifically. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Small agency co-founder already writing about AI strategy in her own field -- strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Hey Carin — saw your writing on AI strategy in communications. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Erika Torres</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>85th &amp; Park Inc. -- creative marketing &amp; communications agency</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erika-torres85/</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small creative marketing/communications agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Hey Erika — saw you're running 85th &amp; Park, a culture-driven creative marketing and comms agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Sam Poutakidis</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>New AI Automation Agency</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sampoutakidis/</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a brand-new AI automation agency. Very early-stage by definition; single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Newest-stage AI-native agency founder in this sheet -- strong thematic fit, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sam — saw you just founded a new AI automation agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>M Kazemi</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Web design agency (Issaquah, WA)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/m-kazemi-098880242/</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small web design agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Hey M — saw you're running your own web design agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Michael Lieu</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Boldly -- design agency (London)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-lieu-77746972/</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of an award-winning design agency explicitly described as a small team. Good qualitative size signal.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly 'small team' self-positioning -- solid company-size signal without a hard headcount number.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael — saw you're running Boldly with a small team of creative minds. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Kristen Ransom</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>CTO &amp; Founder</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>IncluDe Web Design and Development Agency</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristen-m-ransom/</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>CTO/Founder of a small web design/dev agency, publicly interested in AI adoption for the field. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Technical founder already thinking about AI adoption -- good early-adopter signal.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristen — saw your interest in AI adoption for web design and development. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Stefen Phelps</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Kelp Creative Agency</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stefenphelps/</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Software engineer and co-founder of a small creative agency. Headcount unconfirmed -- single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Technical co-founder at a small creative agency -- good blend of ICP fit and technical early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Hey Stefen — saw you co-founded Kelp Creative Agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Dean Swennumson</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder, Head of Operations</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Superstate</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dean-swennumson-075798125/</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder wearing the Head of Operations hat at an early-stage startup. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Textbook 'founder wearing the ops hat' ICP fit; company size inferred from co-founder/early-stage framing, not confirmed.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dean — saw you're co-founder and Head of Operations at Superstate. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Leah Bolden</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; Head of Operations</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>See Jane Drill</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leah-bolden-24419314</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/Head of Operations at a small DIY-resource startup. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Founder wearing the ops hat at an early-stage company -- solid ICP fit by role and company stage.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Hey Leah — saw you're co-founder and Head of Operations at See Jane Drill. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Michael McCormack</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; COO</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>10X ERP</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-mccormack-10xerp/</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/COO of a small startup, explicitly noted as acting as the de-facto Operations Manager -- wearing multiple hats.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder explicitly wearing both COO and hands-on ops-manager hats -- strong 'founder wearing every hat' ICP fit.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael — saw you're co-founder and de-facto Operations Manager at 10X ERP. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Pavels Mordvicevs</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Camel Digital -- PPC agency for B2B SaaS</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pavels-mordvicevs-2aaa4666/</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small PPC agency explicitly targeting B2B SaaS founders -- serves exactly multiplayer's target client base.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Agency founder specializing in the B2B SaaS vertical multiplayer targets -- strong client-overlap fit, same pattern as Oles Dziub.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Hey Pavels — saw you're targeting B2B SaaS founders specifically through Camel Digital. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Arnold</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>FeatherDot Media Group LLC -- video production/growth</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fdmg/</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small video production/growth agency, explicitly positions AI repurposing as part of the offering.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>AI-forward small agency founder -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Hey Aaron — saw your work helping brands scale with strategic video content and AI repurposing. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Evan Cassidy</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Founder</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Boomin' Brands Media</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/evanbcassidy/</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small creative media agency, already using AI content tools in production. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder already hands-on with AI production tools -- good early-adopter signal.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Hey Evan — saw you're using AI tools like Heygen and Freepik at Boomin' Brands Media. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Yash Arora</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Founder / Producer</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Lemonade Creatives</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yasharora16/</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Founder/producer of a small creative production studio incorporating AI-led production. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder already building AI into the production pipeline -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Hey Yash — saw your AI-led creative production work at Lemonade Creatives. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2616,6 +3336,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3286,9 +3286,969 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Paul Dietrich</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CPO</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Spherecast (Y Combinator S24)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pauldietrich98/</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CPO of a YC S24-batch startup -- accelerator batch is public record, confirming very-early company stage.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage; technical co-founder role suggests strong early-adopter fit.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Hey Paul — saw you're co-founder and CPO of Spherecast, a YC S24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Avi Konduru</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Shor (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avi-konduru-54b3a6bb/</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage, textbook ICP by definition.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Hey Avi — saw you're co-founder of Shor, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Dhruv Roongta</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>slashy.com (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dhruv-roongta-421a7b214/</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dhruv — saw you're co-founder of slashy.com, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Michael Kim</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>AgentMail (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michaelhyunkim/</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup building AI-agent-related infrastructure -- confirmed very-early stage and directly AI-native.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder in the AI-agent space itself -- strong thematic AND company-stage fit.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael — saw you're co-founder of AgentMail, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Ishaan Sehgal</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Omnara (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ishaan-sehgal/</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ishaan — saw you're co-founder of Omnara, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Raj Lad</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Infinite (Y Combinator W25)</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rajlad/</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Hey Raj — saw you're co-founder of Infinite, a YC W25 company, previously at Sardine. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Kushal Mohta</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Optifye.ai (Y Combinator W25)</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kushal-mohta-6926931b4/</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W25-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage AI founder -- strong thematic AND company-stage fit.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kushal — saw you're co-founder of Optifye.ai, a YC W25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Nand Vinchhi</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Axal (Y Combinator W25)</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nandvinchhi/</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nand — saw you're co-founder of Axal, a YC W25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>William Barthell</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Janet AI (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-barthell/</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage AI founder -- strong thematic AND company-stage fit.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Hey William — saw you're co-founder of Janet AI, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Iyengar</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Candor (Y Combinator W25)</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aditya-v-iyengar/</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Hey Aditya — saw you're co-founder of Candor, a YC W25 company focused on insider-risk. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Adam Wooten</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Taia -- translation workflow platform / AI consultant</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adamwooten/</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Translation-tech/AI consultant and founder of a small workflow platform. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Small AI-native tooling founder -- direct thematic fit, different vertical (localization) for diversification.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adam — saw you built Taia, a workflow system addressing friction in translation processes. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Ebru Yildirim</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Ollang -- localization</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ebru-yildirim-ollang/</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small localization company with two decades of enterprise localization experience, publicly skeptical of AI-solves-everything narratives -- a thoughtful, engaged voice.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder actively engaging with AI's real limits in her field -- a more skeptical but still relevant prospect.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ebru — saw your take that AI translating doesn't mean localization is solved. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Adriana Biarnes Garcia</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Libre Design Studio -- design studio for founders/startups</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adriana-biarnes-garcia/</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small design studio explicitly positioned to serve founders/startups. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Small studio founder serving the exact startup client base multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adriana — saw you run Libre Design Studio specifically for founders and startups. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Atiqur Rahaman</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Design Monks</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/atiq31416/</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small design agency. Headcount unconfirmed -- single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- company-stage fit inferred from agency type, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Hey Atiqur — saw you founded Design Monks. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Crystal J. Morgan</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Fractional Customer Success Consultant</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- serves SaaS founders and CS teams</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/crystaljmorgan/</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Fractional Customer Success consultant serving multiple small SaaS clients at once -- same fractional-across-many-teams pattern as other consultant rows in this sheet.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CS consultant across small SaaS clients -- ops-adjacent vertical (customer success) not yet represented in this sheet.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Hey Crystal — saw you help SaaS founders and CS teams with customer success operations as a fractional consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Christensen</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Revora Consultants -- Customer Success consulting for B2B SaaS</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-christensen-0814a39/</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small CS consultancy for B2B SaaS companies. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Small CS consultancy founder serving the exact small-SaaS client base multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Hey Thomas — saw you help B2B SaaS companies turn Customer Success into measurable revenue at Revora Consultants. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Peter Varga</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Lafluence &amp; Trendin -- AI-native OS for influencer agencies</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petervarga1/</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Ex-Google, founder of two small companies including an explicitly AI-native product for influencer agencies. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>AI-native small-company founder -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Hey Peter — saw you're building Trendin, an AI-native operating system for influencer agencies. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Jamiu Akanbi</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Hidden Gems -- creator-led growth for B2B AI &amp; SaaS companies</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jamiu-akanbi/</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small agency specializing in B2B AI/SaaS client growth -- serves exactly multiplayer's target client base.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Agency founder specializing in the B2B AI/SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jamiu — saw you're running Hidden Gems, focused on creator-led growth specifically for B2B AI &amp; SaaS companies. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Krishna Kammili</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>LegalConnect -- AI-assisted legal documents for SMEs</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/krishnakammili/</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small legal-tech company already combining AI drafting with human review. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>AI-native small-company founder in an underrepresented vertical (legal tech) -- direct thematic fit, good diversification.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Hey Krishna — saw you built LegalConnect to deliver AI-drafted, solicitor-reviewed legal documents for SMEs. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Jay Pietig</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Founding Partner</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Startup Legal Group, LLC (Kansas City)</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jay-pietig-startuplegalgroup/</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Founding partner of a small legal practice explicitly serving startup clients. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Small legal practice founder serving the exact startup client base multiplayer targets -- underrepresented vertical for diversification.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jay — saw you run Startup Legal Group, serving startup clients directly. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3351,6 +4311,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4246,9 +4246,921 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Chris Pisarski</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Crustdata (Y Combinator F24)</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-pisarski/</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC F24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chris — saw you're co-founder of Crustdata, a YC F24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Manmohit Grewal</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Crustdata (Y Combinator F24)</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manmohitgrewal/</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC F24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Hey Manmohit — saw you're co-founder of Crustdata, a YC F24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Shawn Shivdat</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Penciled (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shawn-shivdat/</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Hey Shawn — saw you're co-founder and CEO of Penciled, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Hamer</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder / COO</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>RetailReady (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarah-hamer/</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/COO of a YC W24-batch startup -- confirmed very-early stage, and she's the one directly wearing the ops hat.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage COO -- exact 'founder wearing the ops hat' ICP fit with confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sarah — saw you're co-founder and COO of RetailReady, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Chris Aeberli</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Sonia (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-aeberli/</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chris — saw you're co-founder of Sonia, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>William Wang</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Centralize (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/williamwang77/</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Hey William — saw you're co-founder of Centralize, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Andy Li</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Respan (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hanheli/</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Hey Andy — saw you're co-founder and CEO of Respan, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Givi Beridze</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>KLIPY (Techstars-backed)</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/giviberidze/</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a Techstars-backed early-stage startup -- confirmed very-early stage by accelerator affiliation.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Accelerator-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Hey Givi — saw you're co-founder and CEO of KLIPY, a Techstars-backed company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Karla Valdivieso</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Shappi (Techstars-backed)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kvaldivieso/</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a Techstars-backed early-stage startup -- confirmed very-early stage by accelerator affiliation.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Accelerator-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Hey Karla — saw you're co-founder and CEO of Shappi, a Techstars-backed company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Harry Dixon</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Co-Founder</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Building mate -- AI growth teammate for small businesses</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harryjdixon1/</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of an early-stage startup building an AI teammate product for small businesses -- directly AI-native and thematically adjacent.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Early-stage AI-native founder building a directly adjacent product category -- strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Hey Harry — saw you're building 'mate,' an AI growth teammate for small businesses. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Mihai Iancu</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>MspCoreX -- AI-first platform for Managed Service Providers</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mihai-iancu-2605681a/</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small AI-first platform for MSPs -- directly AI-native, unifying-tools angle close to multiplayer's own pitch.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>AI-native small-company founder building a product with a very similar 'unify fragmented tools' thesis.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mihai — saw you're building MspCoreX to replace fragmented MSP tool stacks with one intelligent core. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Michelle McCulloch</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Real Marketing Muscle -- helps small/mid-sized agencies grow</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michelle-mcculloch-616b953/</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small consultancy explicitly focused on helping other small agencies grow -- both an ICP member and a possible channel into other small agencies.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Small consultancy founder whose own client base is other small agencies -- potential dual lead/channel value.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michelle — saw your mission of helping small and mid-sized agencies grow through Real Marketing Muscle. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Nahme Chokeir</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Research Connections, Inc. -- market research consulting</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nchokeir/</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small market research consultancy. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder in an underrepresented vertical (market research) for diversification.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nahme — saw you're running Research Connections, a market research consulting and field management company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Jake Wujastyk</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>JakeWu Market Research</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jakewujastyk/</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Solo/very-small market research founder. Headcount unconfirmed -- single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Solo-founder small shop -- purest form of the company-stage signal, lower-confidence single source.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jake — saw you run JakeWu Market Research, a small solo-founder shop. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Moritz Schmidt</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>GEMESYS -- deeptech startup, confirmed under 10 people</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/schmidtmo/</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a deeptech startup explicitly described as under 10 people -- rare, directly confirmed headcount.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>One of the few rows with an explicitly confirmed sub-10-person headcount -- very high-confidence ICP fit.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Hey Moritz — saw you're co-founder of GEMESYS, a deeptech company with under 10 people. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Jenna Gaidusek</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>AI for Interior Designers -- educational platform</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jenna-gaidusek-33175a26/</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO of a small AI-education platform for a specific creative vertical (interior design). Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>AI-adoption-focused small-company founder in a new vertical (interior design) -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jenna — saw you founded an education platform teaching interior designers to use AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Nina Grondin</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Partner &amp; Co-Founder</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Curioso -- design/architecture studio collective</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nina-grondin/</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a small multidisciplinary design/architecture studio. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Small studio co-founder in an underrepresented vertical (architecture/design) for diversification.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nina — saw you co-founded Curioso, an assemblage of designers, architects, and business-minded creatives. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Snehadeep Das</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Chief Designer</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Studio ORCHIVIZ -- AI-driven architectural visualization</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/snehadeep-das-81203b16b/</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Founder/Chief Designer of a small AI-driven architectural visualization studio. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>AI-native small studio founder -- direct thematic fit, underrepresented vertical.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Hey Snehadeep — saw you use AI-driven design tools as founder of Studio ORCHIVIZ. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Austin Richard</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>digital3 AI -- AI accessibility for entrepreneurs and small businesses</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/digital3ai/</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a small company focused on AI accessibility for small businesses -- directly aligned mission.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>AI-native small-company co-founder whose own mission overlaps directly with multiplayer's target audience.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Hey Austin — saw you're making AI accessible and practical for entrepreneurs and small business owners at digital3 AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4331,6 +5243,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5158,9 +5158,537 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Akeem Williams</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Thread (Y Combinator W23)</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/akeem-k-williams/</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W23-batch startup. CAVEAT: this batch is ~3 years old as of now -- company may have grown well past the 5-50 band since the accelerator batch, worth re-checking current headcount before approving.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed founder, but older batch than the other YC rows in this sheet -- lower confidence on current company size specifically.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Hey Akeem — saw you're co-founder of Thread, a YC W23 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Ty Sharp</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>inBuild (Y Combinator W23)</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ty-sharp/</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a YC W23-batch startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band -- re-verify before approving.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed founder, older batch -- lower confidence on current size.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ty — saw you're co-founder and CEO of inBuild, a YC W23 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Vlad Matsiiako</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Infisical (Y Combinator W23)</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vmatsiiako/</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W23-batch developer-tools startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed founder in dev tooling, older batch -- lower confidence on current size, still worth a look given the technical audience fit.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Hey Vlad — saw you're co-founder of Infisical, a YC W23 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Neel Balar</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Clueso -- AI video creation (Y Combinator W23)</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neelbalar7/</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W23-batch AI startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>AI-native founder, older YC batch -- lower confidence on current size but strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Hey Neel — saw you're co-founder of Clueso, an AI video creation company from YC W23. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Yael Chen Zion</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Digital -- brand voice/content agency</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yaelchenzion/</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small content/brand-voice agency, already building custom AI agents into the workflow -- directly AI-native.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder already building bespoke AI agents -- strong thematic fit and technical sophistication.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Hey Yael — saw you built an AI agent trained on multiple brand voices and content formats at Ashley Digital. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Ai Jane L.</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Common AI -- AI/no-code accessibility for small businesses</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aijane-common-ai/</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small company focused on AI accessibility for small businesses -- directly aligned mission with multiplayer's audience.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>AI-native founder whose own mission is helping small businesses use AI -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ai — saw you're democratizing access to AI and no-code tools for individuals and small businesses through Common AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Vanhishikha Bhargava</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Contensify -- SEO/content for B2B SaaS</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/vanhishikhab</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small content/SEO agency specializing in B2B SaaS clients across martech, AI, HRtech, CRM and devtools.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Agency founder specializing in the exact B2B SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Hey Vanhishikha — saw you've partnered with 100+ B2B SaaS companies on SEO and content through Contensify. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Sourav Ganguly</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Branded Minds -- brand strategy for early-stage startups</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sourav-ganguly-3697904/</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small brand strategy agency serving early-stage startups. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder serving the exact early-stage startup client base multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sourav — saw you focus on brand strategy specifically for early-stage startups at Branded Minds. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Ulli Appelbaum</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CSO</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>First The Trousers -- brand strategy and positioning consultancy</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ulliappelbaum/</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CSO of a small brand strategy consultancy. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Solo/small consultancy founder -- fits the consultant pattern in this sheet.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ulli — saw you run First The Trousers as a brand strategy and positioning consultancy. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Lance Mald</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>BrandChef.ai</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lancemald/</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small, explicitly AI-named branding tool/agency. Headcount unconfirmed -- single search snippet only.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>AI-native small-company founder -- direct thematic fit, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Hey Lance — saw you're building BrandChef.ai. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Branden Lower</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Build -- branding agency</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/branden-lower-634b1b139/</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small branding agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Hey Branden — saw you founded Build, a branding agency built around practical design. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5262,6 +5790,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5686,9 +5686,969 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Morrie Schonfeld</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Pingo (Y Combinator S25) -- team of 3</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/morrie-schonfeld-1628002b1/</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup, confirmed team size of 3 -- as small and confirmed as this sheet gets.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed 3-person team -- extremely high-confidence ICP fit on company stage.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Hey Morrie — saw you're co-founder of Pingo, a YC S25 company with a team of just 3 people. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Gurveer Singh</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Certus AI (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gurveer-singh29/</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a YC S25-batch AI startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage AI founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Hey Gurveer — saw you're co-founder and CEO of Certus AI, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Alex Avnit</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Paloma -- AI-native CRM (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-avnit-222b3611a/</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch AI-native CRM startup -- confirmed very-early stage, ex-Deel/Revolut background.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage AI founder -- confirmed company stage and directly AI-native product.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex — saw you're co-founder of Paloma, an AI-native CRM from YC S25. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Khalid A.</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Munify (Y Combinator S25) -- 20 people, $20M ARR</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/khalidashmawy/</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a YC S25-batch startup with an explicitly confirmed 20-person team -- rare, directly confirmed headcount right in the ICP's sweet spot.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly confirmed 20-person team -- one of the highest-confidence company-size matches in this sheet.</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Hey Khalid — saw you've grown Munify to $20M ARR with a team of just 20 people. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Arjun Talati</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Knowlify (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arjun-talati/</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Hey Arjun — saw you're co-founder of Knowlify, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Nazli Danis</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Paloma -- AI-native CRM (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nazlidanis/</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch AI-native CRM startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage AI founder -- confirmed company stage; second co-founder at Paloma alongside Alex Avnit, both worth reaching independently.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nazli — saw you're co-founder of Paloma, an AI-native CRM from YC S25. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Neha Suresh</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Procindex (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nehasuresh1904/</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Hey Neha — saw you're co-founder of Procindex, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>John Yeo</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Autumn (Y Combinator S25)</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/johnyeocx</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Hey John — saw you're co-founder of Autumn, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Susan Sarit</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Empower and Cultivate -- People Ops &amp; Systems consulting</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/susan-sarit/</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small People Ops consultancy explicitly supporting small business owners and founders.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Consultant serving the exact small-founder audience multiplayer targets, in an underrepresented vertical (people ops).</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Hey Susan — saw you help founders build self-sufficient teams as a People Ops &amp; Systems consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Heidi R. Haskins</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Elevated Prana People Ops Consulting</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/heidiparks/</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small People Ops consultancy focused on startups and tech companies specifically.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Consultant explicitly serving the startup/tech audience multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Hey Heidi — saw you focus on People Ops/HR solutions specifically for startups and tech companies. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Michelle Dicks</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Quantum People Ops</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michelle-dicks-3872a791/</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Owner of a small People Ops consultancy providing scalable HR systems for growing teams.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Consultant in the people-ops vertical serving growing small teams.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michelle — saw you provide scalable HR systems for growing teams through Quantum People Ops. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Danielle Laurent</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Founder's HR Lab</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danielle-laurent/</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small HR consultancy explicitly focused on building systems for small businesses and agency owners.</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Consultant serving small agency owners specifically -- direct overlap with the agency-founder rows elsewhere in this sheet.</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Hey Danielle — saw you're passionate about building systems for small businesses and helping agency owners specifically. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Jill Hutchins</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Managing Consultant / Founder</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Your HR Partners -- boutique HR services</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jillhutchins/</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small, explicitly boutique HR consulting firm. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly 'boutique' self-positioning -- good qualitative size signal.</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jill — saw you run Your HR Partners as a boutique human resources services company. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Taylor Scher</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Taylor Scher Consulting, LLC -- B2B SaaS SEO/content</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/taylorjosephscher/</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a B2B SaaS content/SEO consultancy who just hired employee #1 -- explicitly confirmed as a 2-person shop right now.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly confirmed 2-person company (just crossed from solo to first hire) -- very high-confidence smallest-possible ICP fit.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Hey Taylor — saw you just onboarded your first full-time employee (an editorial manager) at Taylor Scher Consulting. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Apoorv Sharma</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Found On AI -- AI search for B2B SaaS (Bengaluru)</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/apoorvshrm/</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small AI-search consultancy for B2B SaaS companies. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>AI-native small consultancy founder serving multiplayer's exact target client base.</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Hey Apoorv — saw you're helping B2B SaaS companies with AI search visibility at Found On AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Anis Msakni</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Search &amp; AI Visibility Consultant</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- for B2B/SaaS companies</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>https://es.linkedin.com/in/anis-msakni-7b17991a9</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Solo independent Search &amp; AI Visibility consultant for B2B/SaaS companies.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Solo consultant serving multiplayer's exact target client base -- purest form of the company-stage signal.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Hey Anis — saw you help B2B/SaaS companies grow visibility and revenue through SEO and AEO. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Matt Craig</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Sheepdog Projects -- BI Consulting and Data Strategy</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mathieucraig/</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a small BI/data-strategy consultancy. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Small consultancy founder in an underrepresented vertical (BI/analytics) for diversification.</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Hey Matt — saw you co-founded Sheepdog Projects to offer BI consulting and data strategy services. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Peter O'Donoghue</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Nynch -- growth platform for consultants and fractionals</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peterodonoghue/</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small SaaS company building tools for the exact fractional-consultant audience heavily represented elsewhere in this sheet.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Small SaaS founder whose own customer base overlaps with many other rows in this sheet -- interesting potential channel as well as direct lead.</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Hey Peter — saw you're building Nynch, a growth platform specifically for consultants and fractional professionals. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Michael Twiddy</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Fame -- The B2B Podcast Agency</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/michael-twiddy-1a1391196</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small B2B podcast production agency, already discussing AI integration in the workflow.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder already engaging with AI in production -- good adoption-readiness signal.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael — saw you discuss AI integration in podcast production at Fame. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Jason Bradwell</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>B2B Better -- podcast agency</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-bradwell-40b45751/</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small B2B podcast agency, publicly discussing AI in production. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder already engaging with AI in production -- good adoption-readiness signal.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jason — saw you discuss how AI is being integrated into podcast production workflows at B2B Better. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5801,6 +6761,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6646,9 +6646,585 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Noble</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Frogotiv -- animation/video studio</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominicnoble/</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small animation/video studio, explicitly confirmed to have started with just two founders doing every function themselves -- textbook wearing-every-hat ICP signal.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed tiny founding team doing every function personally -- very high-confidence ICP fit on company stage and pain point.</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dominic — saw you and your co-founder originally handled strategy, storyboarding, illustration, animation, revisions, and client communication together at Frogotiv. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Oyinkro K</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>K.OS VISUALS -- creative GTM partner for AI/SaaS companies</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oyinkro-creativevideographer/</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small creative agency positioned specifically for AI/SaaS company clients.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder serving multiplayer's exact target client base.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Hey Oyinkro — saw you're positioning K.OS VISUALS as a creative GTM partner for fast-growing AI/SaaS companies. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Costin Modoianu</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Strategic Video Partner</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- video for SaaS &amp; Tech</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/costin-modoianu/</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Solo/small video production consultant specializing in SaaS and tech clients.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Solo consultant serving multiplayer's exact target client base.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Hey Costin — saw you turn complex SaaS products into clear, high-impact video as a strategic video partner. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Marek Bartík</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>pipetail.io -- AWS &amp; Kubernetes DevOps consulting</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marekbartik/</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Solo/small DevOps consultancy founder. Technical audience, likely an early adopter of new tooling.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Solo technical consultant -- purest form of the company-stage signal, strong early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Hey Marek — saw you help companies adopt DevOps culture through on-site workshops and consulting at pipetail.io. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Michal Maxian</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>AI &amp; Cloud Architecture consulting -- built a RAG platform for 15k+ users</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mmaxian/</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>AI &amp; Cloud Architect and founder of a small consultancy, hands-on building AI infrastructure himself.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Deeply technical AI-native founder -- strong thematic fit and early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michal — saw you built a RAG platform for 15k+ users and now consult on DevOps culture and AI adoption. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Anderson-Levy</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CMO Agency (New York)</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samuel-anderson-levy-33508528a/</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small fractional-CMO agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Fractional marketing consultant -- direct fit with the marketing-ops ICP.</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Hey Samuel — saw you run a fractional CMO agency in New York. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Joshua Kimber</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Owner</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>sōsh -- fractional CMO / digital marketing agency</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joshkimber/</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Founder/owner of a small fractional-CMO/digital-marketing agency. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Small agency founder in the core marketing-ops ICP.</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Hey Joshua — saw you're driving data-driven growth for clients as founder of sōsh. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Sara Pastor Ruprichova</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CMO</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>White Cloud Communications (Prague)</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pastorsara/</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small strategic marketing consultancy serving growing businesses across Europe and beyond.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Fractional marketing consultant serving small businesses -- direct ICP fit.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sara — saw you help founders and SMEs turn marketing spend into measurable growth through White Cloud Communications. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Kristen Palmer</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder / CEO</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Boutique digital marketing consulting firm (B2B professional services)</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristenpalmer1/</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a small, self-described boutique marketing consultancy. Ex-Accenture.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly 'boutique' self-positioning -- good qualitative company-size signal.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristen — saw you co-founded a boutique full-service digital marketing consulting firm for B2B professional services. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Jacobs</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CMO</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- partners with early-stage founders/CEOs</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dawnmjacobs/</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CMO explicitly partnering with early-stage founders. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Fractional marketing consultant serving early-stage founders -- direct ICP fit.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dawn — saw you partner with early-stage founders and CEOs to build brands that scale. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Jonny Butler</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CMO</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- strategy &amp; execution for early-stage B2B SaaS</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonnybutler/</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CMO with direct in-house B2B SaaS marketing leadership experience, now serving early-stage SaaS clients.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Fractional marketing consultant with direct B2B SaaS operator background -- strong ICP and empathy fit.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jonny — saw you've been 3x Head of Marketing at B2B SaaS startups before going fractional. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Pereira</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CGO/CMO</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Independent -- B2B SaaS &amp; deep tech</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hugosbpereira/</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Fractional CGO/CMO for B2B SaaS and deep tech, author and previously exited founder himself.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Fractional consultant with founder-side empathy (previously exited a company himself) -- strong ICP fit.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Hey Hugo — saw you wrote "Teams in Hell" and are a 1x exited founder now doing fractional growth work. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6781,6 +7357,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7222,9 +7222,489 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Annabell V.</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CTO</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>CoCrafter (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/annabell-v-86a73b227/</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CTO of a YC W24-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage technical co-founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Hey Annabell — saw you're co-founder and CTO of CoCrafter, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Nicole Atack</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Yarn (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicole-atack-98194b2b8/</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nicole — saw you're co-founder of Yarn, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>David Lalor</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Co-Founder</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Swift (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/davidlalor5/</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Hey David — saw you're CEO and co-founder of Swift, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Md Abdul Halim Rafi</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CTO</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Octolane AI (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/md-abdul-halim-rafi/</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CTO of a YC W24-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage AI founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Hey Md — saw you're co-founder and CTO of Octolane AI, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Joseph Palakapilly</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Meticulate (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jpalakapilly/</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Hey Joseph — saw you're co-founder of Meticulate, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Alex Choi</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Basalt Tech (Y Combinator W24)</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-choi/</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex — saw you co-founded Basalt Tech with Maximillian Bhatti, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Marcus McGehee</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>The AI Consulting Lab</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marcusmcgehee/</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small AI-adoption consultancy whose core finding -- that AI adoption fails on culture/training, not technology -- is nearly identical to multiplayer's own thesis about scattered, unused AI tool access.</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Near-perfect thematic match: his own research names the exact 'AI tools bought but not actually adopted/shared' problem multiplayer is built to solve.</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Hey Marcus — saw your observation that companies buy AI licenses, announce it, and six months later only 10% of the team is actually using the tools. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Miranda Jones</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Founder / Lead Consultant</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>AI Consulting Network</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miranda-jones-16a256115/</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small AI-adoption consultancy for small businesses. Headcount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>AI-adoption consultant serving multiplayer's exact target client base -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Hey Miranda — saw you're empowering small businesses with AI tools and services through AI Consulting Network. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>David MacKillop</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>MacKillop Solutions -- AI agent and automation consulting</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-mackillop/</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Founder of a small AI automation consultancy, hands-on building agent workflows for clients.</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Technical AI-agent-building consultant -- strong thematic fit and early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Hey David — saw you build intelligent workflows and AI agents using tools like n8n, Make.com, and Airtable. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Matthew Kuchera</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Mission AI Consulting</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matthewkuchera/</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn only (no public email found)</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO of a small AI consultancy specifically focused on platform adoption and implementation -- exactly the failure mode multiplayer addresses.</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>AI-adoption specialist consultant -- near-direct thematic match with multiplayer's core value proposition.</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Hey Matthew — saw you specialize in AI platform adoption and implementation at Mission AI Consulting. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7369,6 +7849,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -443,11 +443,12 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +479,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Profile Summary</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Match Reason</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Draft Message</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Date Found</t>
         </is>
@@ -505,22 +511,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Elizabeth Danowski</t>
+          <t>Katheryn Hunt</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Founder — Revenue Operations &amp; Strategy Leader</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PrecisionRevOps LLC</t>
+          <t>GROW Marketing Agency (St. Louis, MO)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elizabeth-danowski-8b264513/</t>
+          <t>https://www.linkedin.com/in/katherynhunt/</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -530,21 +536,26 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Runs her own small RevOps consulting practice (PrecisionRevOps LLC) focused on people/process/technology, CRM migration, and data quality for SaaS clients. As a solo/small-shop operator she IS the ICP: wearing every ops hat with no team to share tool context with.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small (solo/very small) RevOps consulting shop -- exact ICP fit on company stage and role. Likely juggling multiple client workstreams solo, a strong proxy for the 'no shared visibility' pain.</t>
+          <t>Founder/CEO of a small digital marketing agency (web design, digital marketing, branding). Confirmed small: 1-10 employees per Crunchbase, ~17 per ContactOut -- either way solidly inside the 5-50 band.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Hey Elizabeth — saw you're running RevOps solo through PrecisionRevOps for multiple SaaS clients. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+          <t>Confirmed small-agency founder wearing the ops hat -- one of the cleanest company-size confirmations in this batch.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Hey Katheryn, saw you're running GROW Marketing Agency as a small, founder-led shop. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -553,22 +564,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Jeremy Lamande</t>
+          <t>Donna Sluijter</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fractional Head of Revenue Operations</t>
+          <t>Startup Operator -- RevOps &amp; Strategy</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Lamande LLC (fractional RevOps for early/mid-stage SaaS); concurrent fractional roles at Rev, AgentSync, Ekho, OperateWise</t>
+          <t>Independent / embedded RevOps for startups</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jeremy-lamande/</t>
+          <t>https://www.linkedin.com/in/donnasluijter/</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -578,21 +589,26 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>20 years building RevOps functions from scratch; now runs Lamande LLC, a fractional RevOps/CRO practice serving several early-to-mid-stage SaaS startups at once. LinkedIn 'Top Sales Operations Voice.'</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Runs a small consulting practice AND sits inside multiple small SaaS teams concurrently (classic 5-50 person startup engagements) -- doubles as both a direct lead and a channel into several ICP companies at once.</t>
+          <t>Self-describes as a 'Startup Operator' bridging gaps and scaling teams in RevOps and strategy roles -- language that matches the ICP's 'founder wearing every hat' profile.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Hey Jeremy — saw you're juggling fractional RevOps/CRO roles across Rev, AgentSync, Ekho, and OperateWise at once. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+          <t>Title and self-description line up with the ICP almost exactly; specific current employer/headcount not independently confirmed.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Hey Donna, saw your work bridging gaps and scaling teams as a startup RevOps operator. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -601,22 +617,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Haris Odobasic</t>
+          <t>Kristy Buige</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Revenue Strategy Partner</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Revenue Wizards</t>
+          <t>Boutique RevOps consultancy -- B2B SaaS GTM systems</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/harisodobasic_what-does-revops-do-revenue-operations-activity-7263475951290740736-3JwA</t>
+          <t>https://www.linkedin.com/in/kristybuige/</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -626,21 +642,26 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of Revenue Wizards, a small revenue-strategy consulting firm. Posts regularly on LinkedIn about what RevOps does and removing GTM silos.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Co-founder wearing the ops hat at a small consulting shop; his own public content (silos, alignment) lines up directly with the 'scattered, untracked work' pitch angle.</t>
+          <t>Founded and leads a boutique RevOps consultancy enabling B2B SaaS companies to scale GTM systems, processes, and revenue performance.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Hey Haris — saw your recent post on what RevOps actually does and removing GTM silos. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+          <t>Founder of a small consultancy serving the same small-SaaS client base as several other rows in this sheet -- exact company name/size not independently confirmed beyond 'boutique.'</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristy, saw scaling GTM systems for B2B SaaS companies through your boutique RevOps consultancy. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -649,22 +670,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Deepa Patel</t>
+          <t>Jackie Connors</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fractional Revenue &amp; Strategy Leader</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Independent — C-Suite advisor across SaaS/AI/startup clients</t>
+          <t>Digital Marketing Direction -- virtual HubSpot partner agency</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/deepa--patel/</t>
+          <t>https://www.linkedin.com/in/jackiebconnors/</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -674,21 +695,26 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15+ years across RevOps, Marketing Ops, Enablement, Strategy and Finance; now works independently as a fractional/advisory leader to multiple high-growth startups at once.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Independent operator serving several small/startup clients in parallel -- same 'context lost across separate chats' problem multiplied across accounts rather than teammates.</t>
+          <t>Founder/CEO of a small virtual agency offering HubSpot/inbound training, consulting and content marketing. Size not independently confirmed beyond 'virtual agency' framing.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Hey Deepa — saw you're advising several high-growth startups at once as a fractional RevOps/strategy leader. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+          <t>Founder-led small HubSpot partner shop -- same ops-tooling audience multiplayer is targeting.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jackie, saw you run Digital Marketing Direction as a virtual HubSpot partner agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -697,22 +723,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Mariya Valeva</t>
+          <t>Josephine Conneely</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fractional CFO</t>
+          <t>Chief of Staff -- GTM, Operations, AI</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Independent — B2B SaaS clients (~$2M+ ARR)</t>
+          <t>Unconfirmed (UK-based startup)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mariyavaleva-yourscalingpartner/</t>
+          <t>https://uk.linkedin.com/in/josephineconneely</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -722,21 +748,26 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Fractional CFO working with early-stage B2B SaaS companies around the $2M+ ARR mark -- i.e. the 5-50 person stage. Finance/ops-adjacent rather than pure marketing/sales ops.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Ops-adjacent (finance) leader embedded in multiple small SaaS teams; weaker fit than the RevOps/MOps rows above but same team-size band and same fractional-across-many-small-teams dynamic -- worth a lower-priority pass.</t>
+          <t>Chief of Staff with GTM/Operations/AI explicitly in her title -- current employer name and headcount not independently confirmed.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Hey Mariya — saw you work as a fractional CFO across multiple early-stage B2B SaaS clients. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+          <t>Title puts AI and ops in the same remit -- strong thematic fit; company-size confirmation weaker than other rows.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Hey Josephine, saw your Chief of Staff role spanning GTM, Operations, and AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -745,7 +776,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Katheryn Hunt</t>
+          <t>Raj Goodman Anand</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -755,12 +786,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GROW Marketing Agency (St. Louis, MO)</t>
+          <t>Goodman Lantern -- B2B content marketing agency</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/katherynhunt/</t>
+          <t>https://www.linkedin.com/in/rajanand/</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -770,21 +801,26 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small digital marketing agency (web design, digital marketing, branding). Confirmed small: 1-10 employees per Crunchbase, ~17 per ContactOut -- either way solidly inside the 5-50 band.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Confirmed small-agency founder wearing the ops hat -- one of the cleanest company-size confirmations in this batch.</t>
+          <t>Founder/CEO of a B2B content marketing agency serving clients across several continents -- distributed small team model, not independently headcount-confirmed.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Hey Katheryn — saw you're running GROW Marketing Agency as a small, founder-led shop. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+          <t>Founder wearing the ops/marketing hat; 'across five continents' framing suggests a distributed small team rather than a large single office, but worth double-checking size before approving.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Hey Raj, saw you're running Goodman Lantern, a B2B content marketing agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -793,22 +829,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Adam Goyette</t>
+          <t>Paul Dietrich</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder &amp; CPO</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Growth Union (Chicago) -- boutique growth agency for early-stage B2B SaaS</t>
+          <t>Spherecast (Y Combinator S24)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adam-goyette/</t>
+          <t>https://www.linkedin.com/in/pauldietrich98/</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -818,21 +854,26 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Ex-Help Scout / G2 growth marketing exec, now runs a small agency assembling senior marketers for early-stage B2B SaaS clients (Writer, RevenueHero, Recorded Future named as clients). Exact employee count unconfirmed but the agency's model (small senior team, no bench) implies well under 50.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Founder running a lean agency serving exactly the small-SaaS client base multiplayer targets; company size inferred from agency model, not directly confirmed -- worth a second look before approving.</t>
+          <t>Co-founder/CPO of a YC S24-batch startup -- accelerator batch is public record, confirming very-early company stage.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Hey Adam — saw you've built a lean senior team at Growth Union for early-stage B2B SaaS clients like Writer and Recorded Future. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage; technical co-founder role suggests strong early-adopter fit.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Hey Paul, saw you're co-founder and CPO of Spherecast, a YC S24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -841,7 +882,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>David Malevsky</t>
+          <t>Avi Konduru</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -851,12 +892,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Lynx Growth Agency (Hallandale Beach, FL)</t>
+          <t>Shor (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/david-malevsky/</t>
+          <t>https://www.linkedin.com/in/avi-konduru-54b3a6bb/</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -866,21 +907,26 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a boutique agency (patient acquisition for regenerative/integrative clinics) built around AI-driven marketing and automation. Employee count unconfirmed -- RocketReach shows only a handful of verified staff, consistent with a small shop.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Self-describes as 'resolving business challenges using AI' -- co-founder at a small, AI-forward agency is a strong qualitative fit even though the exact headcount isn't independently confirmed.</t>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Hey David — saw you're building Lynx Growth Agency around AI-driven marketing and automation. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage, textbook ICP by definition.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Hey Avi, saw you're co-founder of Shor, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -889,22 +935,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Alex Zlotko</t>
+          <t>Dhruv Roongta</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Forecastio (B2B sales forecasting for HubSpot)</t>
+          <t>slashy.com (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alexzlotko/</t>
+          <t>https://www.linkedin.com/in/dhruv-roongta-421a7b214/</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -914,21 +960,26 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17 years in B2B sales/CS, now CEO of Forecastio, a small SaaS company building sales forecasting tools. Publishes regularly on AI agents in RevOps specifically.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Small SaaS founder/CEO already writing publicly about AI agents in RevOps -- direct thematic overlap with multiplayer's pitch, though exact headcount at Forecastio is unconfirmed.</t>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex — saw your writing on AI agents in RevOps as CEO of Forecastio. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dhruv, saw you're co-founder of slashy.com, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -937,22 +988,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Kristofer Wille</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RevOps Consultant &amp; Advisor</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Independent -- RevOpsVision (Berlin)</t>
+          <t>AgentMail (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kriswille-revopsvision-revenue-operations-consultant-advisory/</t>
+          <t>https://www.linkedin.com/in/michaelhyunkim/</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -962,21 +1013,26 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10+ years in SalesOps/RevOps in Berlin's startup scene. Self-positions explicitly as helping 'C-Level Leaders &amp; Startups Supercharge Their Small RevOps Teams' -- his own tagline names the exact ICP.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>His public positioning IS the ICP description almost word-for-word (small RevOps teams at startups). Company size self-described, not independently verified.</t>
+          <t>Co-founder of a YC S25-batch startup building AI-agent-related infrastructure -- confirmed very-early stage and directly AI-native.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristofer — saw your tagline about helping startups supercharge their small RevOps teams. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder in the AI-agent space itself -- strong thematic AND company-stage fit.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael, saw you're co-founder of AgentMail, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -985,22 +1041,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Donna Sluijter</t>
+          <t>Ishaan Sehgal</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Startup Operator -- RevOps &amp; Strategy</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Independent / embedded RevOps for startups</t>
+          <t>Omnara (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/donnasluijter/</t>
+          <t>https://www.linkedin.com/in/ishaan-sehgal/</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1010,21 +1066,26 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Self-describes as a 'Startup Operator' bridging gaps and scaling teams in RevOps and strategy roles -- language that matches the ICP's 'founder wearing every hat' profile.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Title and self-description line up with the ICP almost exactly; specific current employer/headcount not independently confirmed.</t>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Hey Donna — saw your work bridging gaps and scaling teams as a startup RevOps operator. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ishaan, saw you're co-founder of Omnara, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1033,22 +1094,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>John McArdle</t>
+          <t>Raj Lad</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Sequoia Solutions -- RevOps/HubSpot consultancy for early-stage B2B tech</t>
+          <t>Infinite (Y Combinator W25)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/john-mcardle-m-s-71b58178/</t>
+          <t>https://www.linkedin.com/in/rajlad/</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1058,21 +1119,26 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Founded a small consultancy that has worked with dozens of early-stage companies cleaning up CRM/HubSpot data and building GTM systems -- not the 'Sequoia' VC firm, a separate small boutique of the same name.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Founder-led small consultancy serving exactly the early-stage company band multiplayer targets.</t>
+          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Hey John — saw the dozens of early-stage companies you've helped clean up CRM/HubSpot data at Sequoia Solutions. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Hey Raj, saw you're co-founder of Infinite, a YC W25 company, previously at Sardine. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1081,22 +1147,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Roberto Guerra</t>
+          <t>Kushal Mohta</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Revenue Hub Latam -- RevOps + HubSpot for B2B companies in LATAM</t>
+          <t>Optifye.ai (Y Combinator W25)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robguerra/</t>
+          <t>https://www.linkedin.com/in/kushal-mohta-6926931b4/</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1106,21 +1172,26 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Runs a boutique RevOps/HubSpot consultancy for B2B companies across LATAM, publicly writing about pipeline, CRM, forecasting -- and AI.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Boutique consultancy founder already writing about AI in the RevOps workflow -- direct thematic and company-stage fit.</t>
+          <t>Co-founder of a YC W25-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Hey Roberto — saw your posts on pipeline, forecasting, and AI at Revenue Hub Latam. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+          <t>YC-backed early-stage AI founder -- strong thematic AND company-stage fit.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kushal, saw you're co-founder of Optifye.ai, a YC W25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1129,22 +1200,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Kristy Buige</t>
+          <t>Nand Vinchhi</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Boutique RevOps consultancy -- B2B SaaS GTM systems</t>
+          <t>Axal (Y Combinator W25)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kristybuige/</t>
+          <t>https://www.linkedin.com/in/nandvinchhi/</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1154,21 +1225,26 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Founded and leads a boutique RevOps consultancy enabling B2B SaaS companies to scale GTM systems, processes, and revenue performance.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small consultancy serving the same small-SaaS client base as several other rows in this sheet -- exact company name/size not independently confirmed beyond 'boutique.'</t>
+          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristy — saw scaling GTM systems for B2B SaaS companies through your boutique RevOps consultancy. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nand, saw you're co-founder of Axal, a YC W25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1177,22 +1253,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Johnathan Wang</t>
+          <t>William Barthell</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The SaaS Consultants -- fractional CMO / marketing agency for SaaS</t>
+          <t>Janet AI (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/johnathan-wang/</t>
+          <t>https://www.linkedin.com/in/william-barthell/</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1202,21 +1278,26 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Runs a small fractional-CMO agency for SaaS businesses and has personally built social-media-management software using Python/JavaScript and AI -- technical enough to be a strong early adopter.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder who is also hands-on technical/AI-building -- good combination of ICP fit and early-adopter likelihood.</t>
+          <t>Co-founder of a YC S25-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Hey Johnathan — saw you built your own AI-powered social media tooling while running The SaaS Consultants. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+          <t>YC-backed early-stage AI founder -- strong thematic AND company-stage fit.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Hey William, saw you're co-founder of Janet AI, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1225,22 +1306,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Shaun Anderson</t>
+          <t>Aditya Iyengar</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>thisisagency.ai / hobo-web.co.uk -- forensic SEO agency</t>
+          <t>Candor (Y Combinator W25)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/shaun-anderson-hobo/</t>
+          <t>https://www.linkedin.com/in/aditya-v-iyengar/</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1250,21 +1331,26 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small forensic-SEO agency, also positions himself as an AI Marketing Engineer building agentic AI systems. Found via a single search pass, not cross-verified for exact headcount.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder already hands-on with agentic AI -- strong thematic fit; company size inferred from agency type, not confirmed.</t>
+          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Hey Shaun — saw you're building agentic AI systems as an AI Marketing Engineer while running thisisagency.ai. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Hey Aditya, saw you're co-founder of Candor, a YC W25 company focused on insider-risk. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1273,22 +1359,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Jackie Connors</t>
+          <t>Chris Pisarski</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketing Direction -- virtual HubSpot partner agency</t>
+          <t>Crustdata (Y Combinator F24)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jackiebconnors/</t>
+          <t>https://www.linkedin.com/in/chris-pisarski/</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1298,21 +1384,26 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small virtual agency offering HubSpot/inbound training, consulting and content marketing. Size not independently confirmed beyond 'virtual agency' framing.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Founder-led small HubSpot partner shop -- same ops-tooling audience multiplayer is targeting.</t>
+          <t>Co-founder of a YC F24-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Hey Jackie — saw you run Digital Marketing Direction as a virtual HubSpot partner agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chris, saw you're co-founder of Crustdata, a YC F24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1321,22 +1412,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Sam Anderson</t>
+          <t>Manmohit Grewal</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Chief Growth Officer / Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Origin 63 -- small growth agency</t>
+          <t>Crustdata (Y Combinator F24)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/samanderson41/</t>
+          <t>https://www.linkedin.com/in/manmohitgrewal/</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1346,21 +1437,26 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Founder-level growth leader at a self-described small agency. Weaker verification than other rows -- single search snippet only.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Small growth-agency founder; include but treat as lower-confidence given only one source found.</t>
+          <t>Co-founder of a YC F24-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Hey Sam — saw you're running Origin 63 as a small, results-focused growth agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Hey Manmohit, saw you're co-founder of Crustdata, a YC F24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1369,22 +1465,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Josh Harcus</t>
+          <t>Shawn Shivdat</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Revenue Growth &amp; Retention Lead</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Hüify -- HubSpot partner agency</t>
+          <t>Penciled (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/joshharcus/</t>
+          <t>https://www.linkedin.com/in/shawn-shivdat/</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1394,21 +1490,26 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Works on revenue growth/retention at a HubSpot partner agency. Exact headcount at Hüify unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>HubSpot-partner-agency operator in the ops-tooling audience; company size inferred, not confirmed.</t>
+          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Hey Josh — saw your work on revenue growth and retention at Hüify, a HubSpot partner agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Hey Shawn, saw you're co-founder and CEO of Penciled, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1417,22 +1518,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Alex Williams</t>
+          <t>Sarah Hamer</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Independent HubSpot Consultant</t>
+          <t>Co-Founder / COO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Independent -- solo HubSpot consulting practice</t>
+          <t>RetailReady (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/awoxford/</t>
+          <t>https://www.linkedin.com/in/sarah-hamer/</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1442,21 +1543,26 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Solo independent HubSpot implementation/strategy consultant -- a one-person shop, which is close to the purest form of the 'wearing every hat, no one to share tool context with' ICP signal.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Solo consultant -- exact company-stage fit by definition, though this is a one-person 'team' rather than 5-50 people; worth including as a different flavor of the same pain (no one to share context with at all).</t>
+          <t>Co-founder/COO of a YC W24-batch startup -- confirmed very-early stage, and she's the one directly wearing the ops hat.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex — saw you run your own solo HubSpot consulting practice. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
+          <t>YC-backed early-stage COO -- exact 'founder wearing the ops hat' ICP fit with confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sarah, saw you're co-founder and COO of RetailReady, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1465,22 +1571,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Clwyd Probert</t>
+          <t>Chris Aeberli</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CEO &amp; Founder, AI Consultant</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Whitehat (UK) -- AI consulting</t>
+          <t>Sonia (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/clwyd-probert</t>
+          <t>https://www.linkedin.com/in/chris-aeberli/</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1490,21 +1596,26 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CEO/Founder and AI consultant; company size and exact scope of Whitehat not independently confirmed -- single search snippet only.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Directly in the AI-adoption-for-small-business space -- strong thematic fit, weaker company-size confirmation.</t>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Hey Clwyd — saw you work as an AI consultant at Whitehat, helping businesses adopt AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chris, saw you're co-founder of Sonia, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1513,22 +1624,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Clara Ma</t>
+          <t>William Wang</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Chief of Staff (Employee #3)</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Kairos -- very early-stage startup</t>
+          <t>Centralize (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/clarama/</t>
+          <t>https://www.linkedin.com/in/williamwang77/</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1538,21 +1649,26 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Chief of Staff at a very early-stage startup (self-described as employee #3) -- partners with founders through the hardest parts of scaling. About as small/early as the ICP gets.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Employee #3 at an early-stage startup wearing the ops/chief-of-staff hat -- textbook ICP fit on company stage.</t>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Hey Clara — saw you're employee #3 and Chief of Staff at Kairos. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Hey William, saw you're co-founder of Centralize, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1561,22 +1677,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Josephine Conneely</t>
+          <t>Andy Li</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Chief of Staff -- GTM, Operations, AI</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Unconfirmed (UK-based startup)</t>
+          <t>Respan (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/josephineconneely</t>
+          <t>https://www.linkedin.com/in/hanheli/</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1586,21 +1702,26 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Chief of Staff with GTM/Operations/AI explicitly in her title -- current employer name and headcount not independently confirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Title puts AI and ops in the same remit -- strong thematic fit; company-size confirmation weaker than other rows.</t>
+          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Hey Josephine — saw your Chief of Staff role spanning GTM, Operations, and AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Hey Andy, saw you're co-founder and CEO of Respan, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1609,22 +1730,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Riddhi Sharma</t>
+          <t>Givi Beridze</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CEO &amp; Founder</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Thought In A Dot -- content marketing agency</t>
+          <t>KLIPY (Techstars-backed)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sharmariddhi/</t>
+          <t>https://www.linkedin.com/in/giviberidze/</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1634,21 +1755,26 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14+ years in leadership/brand content strategy, now founder/CEO of a content marketing agency. Employee count unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder in the marketing-ops-adjacent content space.</t>
+          <t>Co-founder/CEO of a Techstars-backed early-stage startup -- confirmed very-early stage by accelerator affiliation.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Hey Riddhi — saw you're running Thought In A Dot as a content marketing agency and brand strategist. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
+          <t>Accelerator-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Hey Givi, saw you're co-founder and CEO of KLIPY, a Techstars-backed company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1657,22 +1783,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>John Liska</t>
+          <t>Karla Valdivieso</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Creative Engine (Austin, TX) -- branding &amp; digital marketing agency</t>
+          <t>Shappi (Techstars-backed)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/john-liska-594a52193/</t>
+          <t>https://www.linkedin.com/in/kvaldivieso/</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1682,21 +1808,26 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small branding/digital marketing agency in Austin. Employee count unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- fits the company-stage band, size inferred not confirmed.</t>
+          <t>Co-founder/CEO of a Techstars-backed early-stage startup -- confirmed very-early stage by accelerator affiliation.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Hey John — saw you founded Creative Engine, a branding and digital marketing agency in Austin. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+          <t>Accelerator-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Hey Karla, saw you're co-founder and CEO of Shappi, a Techstars-backed company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1705,22 +1836,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Ajay G.</t>
+          <t>Moritz Schmidt</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>MAWD Agency -- Google Ads/SEO/websites for small businesses</t>
+          <t>GEMESYS -- deeptech startup, confirmed under 10 people</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ajayg514/</t>
+          <t>https://www.linkedin.com/in/schmidtmo/</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1730,21 +1861,26 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small AI-forward performance-marketing agency serving small-business clients.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder in the exact small-business-serving segment; last-name not public in the source, listed as found.</t>
+          <t>Co-founder of a deeptech startup explicitly described as under 10 people -- rare, directly confirmed headcount.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Hey Ajay — saw you run MAWD Agency managing Google Ads, SEO, and websites for small businesses. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
+          <t>One of the few rows with an explicitly confirmed sub-10-person headcount -- very high-confidence ICP fit.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Hey Moritz, saw you're co-founder of GEMESYS, a deeptech company with under 10 people. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1753,22 +1889,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Raj Goodman Anand</t>
+          <t>Morrie Schonfeld</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Goodman Lantern -- B2B content marketing agency</t>
+          <t>Pingo (Y Combinator S25) -- team of 3</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rajanand/</t>
+          <t>https://www.linkedin.com/in/morrie-schonfeld-1628002b1/</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1778,21 +1914,26 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a B2B content marketing agency serving clients across several continents -- distributed small team model, not independently headcount-confirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Founder wearing the ops/marketing hat; 'across five continents' framing suggests a distributed small team rather than a large single office, but worth double-checking size before approving.</t>
+          <t>Co-founder of a YC S25-batch startup, confirmed team size of 3 -- as small and confirmed as this sheet gets.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Hey Raj — saw you're running Goodman Lantern, a B2B content marketing agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+          <t>Confirmed 3-person team -- extremely high-confidence ICP fit on company stage.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Hey Morrie, saw you're co-founder of Pingo, a YC S25 company with a team of just 3 people. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1801,22 +1942,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laney M. Silverman</t>
+          <t>Gurveer Singh</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>The Design Boutique, Inc.</t>
+          <t>Certus AI (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/thedesignboutique/</t>
+          <t>https://www.linkedin.com/in/gurveer-singh29/</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1826,21 +1967,26 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Founder of a self-described boutique design agency, explicitly positioned around small-team speed/agility.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Explicitly 'boutique' self-positioning -- good qualitative company-size signal even without a hard headcount number.</t>
+          <t>Co-founder/CEO of a YC S25-batch AI startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Hey Laney — saw you run The Design Boutique and pride yourselves on being able to pivot quickly as a small shop. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
+          <t>YC-backed early-stage AI founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Hey Gurveer, saw you're co-founder and CEO of Certus AI, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1849,22 +1995,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Thomas Kranzle</t>
+          <t>Alex Avnit</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Founder, Director</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Venture Visuals (Seattle) -- creative agency</t>
+          <t>Paloma -- AI-native CRM (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/thomaskranzle/</t>
+          <t>https://www.linkedin.com/in/alex-avnit-222b3611a/</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1874,21 +2020,26 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Founder/Director of a small creative agency in Seattle. Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+          <t>Co-founder of a YC S25-batch AI-native CRM startup -- confirmed very-early stage, ex-Deel/Revolut background.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Hey Thomas — saw you founded Venture Visuals, a creative agency in Seattle. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
+          <t>YC-backed early-stage AI founder -- confirmed company stage and directly AI-native product.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex, saw you're co-founder of Paloma, an AI-native CRM from YC S25. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1897,7 +2048,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Santosh Kushwaha</t>
+          <t>Khalid A.</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1907,12 +2058,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Visual Best -- AI Creative Production Agency</t>
+          <t>Munify (Y Combinator S25) -- 20 people, $20M ARR</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/in/santosh-kushwaha-explorer</t>
+          <t>https://www.linkedin.com/in/khalidashmawy/</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1922,21 +2073,26 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small, explicitly AI-native creative production agency. Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>AI-native agency founder -- strong thematic fit, company size inferred not confirmed.</t>
+          <t>Founder of a YC S25-batch startup with an explicitly confirmed 20-person team -- rare, directly confirmed headcount right in the ICP's sweet spot.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Hey Santosh — saw you're running Visual Best, an AI creative production agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
+          <t>Explicitly confirmed 20-person team -- one of the highest-confidence company-size matches in this sheet.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Hey Khalid, saw you've grown Munify to $20M ARR with a team of just 20 people. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1945,22 +2101,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>David Simões</t>
+          <t>Arjun Talati</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Sounds Good Agency -- Shopify Plus partner (CEE region)</t>
+          <t>Knowlify (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>https://cz.linkedin.com/in/davidjsimoes/en</t>
+          <t>https://www.linkedin.com/in/arjun-talati/</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1970,21 +2126,26 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Founder of a Shopify Plus agency serving DTC/B2B/Retail brands, self-describes as having an 'AI-first business mindset.' Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder explicitly framing the business around AI-first thinking -- strong thematic fit.</t>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Hey David — saw you describe your business as having an AI-first mindset while running Sounds Good Agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Hey Arjun, saw you're co-founder of Knowlify, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -1993,22 +2154,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Mark Kennaley</t>
+          <t>Nazli Danis</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SoftwareFactory.ai -- AI-native software engineering consultancy</t>
+          <t>Paloma -- AI-native CRM (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/markkennaley/</t>
+          <t>https://www.linkedin.com/in/nazlidanis/</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2018,21 +2179,26 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small AI-native software engineering consultancy. Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Small AI-forward software consultancy founder -- exactly the kind of technical early adopter this product needs.</t>
+          <t>Co-founder of a YC S25-batch AI-native CRM startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Hey Mark — saw you're a pioneer in AI-native software engineering as founder of SoftwareFactory.ai. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
+          <t>YC-backed early-stage AI founder -- confirmed company stage; second co-founder at Paloma alongside Alex Avnit, both worth reaching independently.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nazli, saw you're co-founder of Paloma, an AI-native CRM from YC S25. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2041,22 +2207,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Philip Ledgerwood</t>
+          <t>Neha Suresh</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>AI Consultant / Software Developer</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Independent -- solo AI consulting practice</t>
+          <t>Procindex (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/phil-ledgerwood/</t>
+          <t>https://www.linkedin.com/in/nehasuresh1904/</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2066,21 +2232,26 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Solo independent consultant helping companies adopt AI securely. One-person practice -- same 'no one to share context with' signal as other solo consultants in this sheet.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Solo AI consultant -- direct thematic fit and purest form of the company-stage signal.</t>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Hey Philip — saw you help companies use AI securely and purposefully as an independent consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Hey Neha, saw you're co-founder of Procindex, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2089,22 +2260,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Dylan Kinder</t>
+          <t>John Yeo</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Independent AI Consultant</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Independent -- installs AI systems into service businesses</t>
+          <t>Autumn (Y Combinator S25)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/dylankinder/</t>
+          <t>https://uk.linkedin.com/in/johnyeocx</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2114,21 +2285,26 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Solo consultant helping small service businesses adopt AI tooling. Weaker verification -- single search snippet only.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Solo AI-adoption consultant serving small businesses -- direct thematic fit, lower-confidence single-source finding.</t>
+          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Hey Dylan — saw you install AI systems into service businesses as an independent consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Hey John, saw you're co-founder of Autumn, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2137,22 +2313,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Alex Marantelos</t>
+          <t>Taylor Scher</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder / CEO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Intryc (Y Combinator S24)</t>
+          <t>Taylor Scher Consulting, LLC -- B2B SaaS SEO/content</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alexmarantelos/</t>
+          <t>https://www.linkedin.com/in/taylorjosephscher/</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2162,21 +2338,26 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a YC S24-batch startup -- confirmed very-early-stage by accelerator batch, though exact current headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage (accelerator batch is public record) even without a hard headcount number.</t>
+          <t>Founder of a B2B SaaS content/SEO consultancy who just hired employee #1 -- explicitly confirmed as a 2-person shop right now.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex — saw you're co-founder/CEO of Intryc, a Y Combinator S24 startup. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+          <t>Explicitly confirmed 2-person company (just crossed from solo to first hire) -- very high-confidence smallest-possible ICP fit.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Hey Taylor, saw you just onboarded your first full-time employee (an editorial manager) at Taylor Scher Consulting. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2185,7 +2366,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Arham Khan</t>
+          <t>Dominic Noble</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2195,12 +2376,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Pixated -- performance marketing agency (paid social/search)</t>
+          <t>Frogotiv -- animation/video studio</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/arhamkhan</t>
+          <t>https://www.linkedin.com/in/dominicnoble/</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2210,21 +2391,26 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small performance marketing agency. Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+          <t>Founder of a small animation/video studio, explicitly confirmed to have started with just two founders doing every function themselves -- textbook wearing-every-hat ICP signal.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Hey Arham — saw you founded Pixated, a performance marketing agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
+          <t>Confirmed tiny founding team doing every function personally -- very high-confidence ICP fit on company stage and pain point.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dominic, saw you and your co-founder originally handled strategy, storyboarding, illustration, animation, revisions, and client communication together at Frogotiv. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2233,22 +2419,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Alex Brown</t>
+          <t>Annabell V.</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Co-Founder &amp; CTO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Tierra -- performance marketing agency for DTC ecommerce</t>
+          <t>CoCrafter (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alex-brown-tierra/</t>
+          <t>https://www.linkedin.com/in/annabell-v-86a73b227/</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2258,21 +2444,26 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small performance marketing agency for DTC ecommerce brands. Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+          <t>Co-founder/CTO of a YC W24-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex — saw you're scaling DTC ecommerce brands through Tierra. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+          <t>YC-backed early-stage technical co-founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Hey Annabell, saw you're co-founder and CTO of CoCrafter, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2281,7 +2472,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Oles Dziub</t>
+          <t>Nicole Atack</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2291,12 +2482,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Hey Digital -- SaaS performance marketing &amp; creative agency</t>
+          <t>Yarn (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/oles-dziub-b2b-saas-paid-ads-expert/</t>
+          <t>https://www.linkedin.com/in/nicole-atack-98194b2b8/</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2306,21 +2497,26 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a small agency specializing in paid ads for B2B SaaS companies -- serves exactly multiplayer's target client base.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Agency founder specializing in the B2B SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Hey Oles — saw you're running Hey Digital, a performance marketing agency focused specifically on B2B SaaS. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nicole, saw you're co-founder of Yarn, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2329,22 +2525,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Beckie Blackburn-Cooper</t>
+          <t>David Lalor</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>CEO &amp; Co-Founder</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Boutique recruiting agency</t>
+          <t>Swift (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/beckie-blackburn-cooper-bri/</t>
+          <t>https://www.linkedin.com/in/davidlalor5/</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2354,21 +2550,26 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small, self-described boutique recruiting agency. Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Explicitly 'boutique' self-positioning -- good qualitative size signal; different vertical (recruiting) than most of this sheet, useful diversification.</t>
+          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Hey Beckie — saw you run a boutique recruiting agency with a niche sector focus. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Hey David, saw you're CEO and co-founder of Swift, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2377,22 +2578,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Katie Matthews</t>
+          <t>Md Abdul Halim Rafi</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Co-Founder &amp; CTO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>CollabRecruit -- small recruiting agency</t>
+          <t>Octolane AI (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kmtalentfinder/</t>
+          <t>https://www.linkedin.com/in/md-abdul-halim-rafi/</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2402,21 +2603,26 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small recruiting agency, writes publicly about technology's role in staffing. Headcount unconfirmed.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder already thinking publicly about tech's role in her business -- good adoption-readiness signal.</t>
+          <t>Co-founder/CTO of a YC W24-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Hey Katie — saw your writing on balancing technology and human connection in recruiting at CollabRecruit. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
+          <t>YC-backed early-stage AI founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Hey Md, saw you're co-founder and CTO of Octolane AI, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2425,22 +2631,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Becky Kuntz</t>
+          <t>Joseph Palakapilly</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>BK's Bookkeeping</t>
+          <t>Meticulate (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/becky-kuntz/</t>
+          <t>https://www.linkedin.com/in/jpalakapilly/</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2450,21 +2656,26 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small virtual bookkeeping practice serving small-business clients. Finance-ops-adjacent, similar band to Mariya Valeva elsewhere in this sheet.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Small finance-ops shop founder -- weaker fit than marketing/RevOps rows but same company-stage band and same 'wearing every hat' pain.</t>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Hey Becky — saw you help small business owners get time back through BK's Bookkeeping. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Hey Joseph, saw you're co-founder of Meticulate, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2473,22 +2684,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Tom Wells</t>
+          <t>Alex Choi</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Wells Virtual Bookkeeping, LLC</t>
+          <t>Basalt Tech (Y Combinator W24)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/tom-wells-rad60/</t>
+          <t>https://www.linkedin.com/in/alex-choi/</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2498,21 +2709,26 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Small virtual bookkeeping practice; actively participates in an AI Mastermind group -- already engaged with AI adoption specifically.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Small ops-adjacent shop already active in an AI-adoption community -- good readiness signal despite being outside core marketing/RevOps.</t>
+          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Hey Tom — saw you're part of an AI Mastermind group applying tech-forward solutions to bookkeeping. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex, saw you co-founded Basalt Tech with Maximillian Bhatti, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2521,22 +2737,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Jennifer Perez-Fong</t>
+          <t>Elizabeth Danowski</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Founder, Revenue Operations &amp; Strategy Leader</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Bookkeeping Done Right</t>
+          <t>PrecisionRevOps LLC</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jennifer-perez-fong-cpa/</t>
+          <t>https://www.linkedin.com/in/elizabeth-danowski-8b264513/</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2546,21 +2762,26 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>CEO/founder of a small accounting practice serving SMBs, founded 2013. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Small finance-ops shop founder -- same lower-priority band as other bookkeeping rows in this sheet.</t>
+          <t>Runs her own small RevOps consulting practice (PrecisionRevOps LLC) focused on people/process/technology, CRM migration, and data quality for SaaS clients. As a solo/small-shop operator she IS the ICP: wearing every ops hat with no team to share tool context with.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Hey Jennifer — saw you founded Bookkeeping Done Right to serve small and medium businesses in South Florida. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
+          <t>Founder of a small (solo/very small) RevOps consulting shop -- exact ICP fit on company stage and role. Likely juggling multiple client workstreams solo, a strong proxy for the 'no shared visibility' pain.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Hey Elizabeth, saw you're running RevOps solo through PrecisionRevOps for multiple SaaS clients. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2569,22 +2790,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Parry Headrick</t>
+          <t>Jeremy Lamande</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Fractional Head of Revenue Operations</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Crackle PR -- B2B tech PR agency (Boston)</t>
+          <t>Lamande LLC (fractional RevOps for early/mid-stage SaaS); concurrent fractional roles at Rev, AgentSync, Ekho, OperateWise</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/parryheadrick/</t>
+          <t>https://www.linkedin.com/in/jeremy-lamande/</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2594,21 +2815,26 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small B2B tech PR agency. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>B2B-tech-focused small agency founder -- adjacent vertical (PR) serving the same kind of small SaaS/tech clients.</t>
+          <t>20 years building RevOps functions from scratch; now runs Lamande LLC, a fractional RevOps/CRO practice serving several early-to-mid-stage SaaS startups at once. LinkedIn 'Top Sales Operations Voice.'</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Hey Parry — saw you're leading a team of senior PR leaders at Crackle PR. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
+          <t>Runs a small consulting practice AND sits inside multiple small SaaS teams concurrently (classic 5-50 person startup engagements) -- doubles as both a direct lead and a channel into several ICP companies at once.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jeremy, saw you're juggling fractional RevOps/CRO roles across Rev, AgentSync, Ekho, and OperateWise at once. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2617,22 +2843,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Carin Warner</t>
+          <t>Haris Odobasic</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Co-Founder &amp; Revenue Strategy Partner</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Warner Communications -- PR &amp; comms strategy</t>
+          <t>Revenue Wizards</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/carinwarner/</t>
+          <t>https://www.linkedin.com/posts/harisodobasic_what-does-revops-do-revenue-operations-activity-7263475951290740736-3JwA</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2642,21 +2868,26 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a small PR/comms firm, publishes on AI strategy in communications specifically. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Small agency co-founder already writing about AI strategy in her own field -- strong thematic fit.</t>
+          <t>Co-founder of Revenue Wizards, a small revenue-strategy consulting firm. Posts regularly on LinkedIn about what RevOps does and removing GTM silos.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Hey Carin — saw your writing on AI strategy in communications. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+          <t>Co-founder wearing the ops hat at a small consulting shop; his own public content (silos, alignment) lines up directly with the 'scattered, untracked work' pitch angle.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Hey Haris, saw your recent post on what RevOps actually does and removing GTM silos. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2665,22 +2896,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Erika Torres</t>
+          <t>Deepa Patel</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Fractional Revenue &amp; Strategy Leader</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>85th &amp; Park Inc. -- creative marketing &amp; communications agency</t>
+          <t>Independent, C-Suite advisor across SaaS/AI/startup clients</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/erika-torres85/</t>
+          <t>https://www.linkedin.com/in/deepa--patel/</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2690,21 +2921,26 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small creative marketing/communications agency. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+          <t>15+ years across RevOps, Marketing Ops, Enablement, Strategy and Finance; now works independently as a fractional/advisory leader to multiple high-growth startups at once.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Hey Erika — saw you're running 85th &amp; Park, a culture-driven creative marketing and comms agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
+          <t>Independent operator serving several small/startup clients in parallel -- same 'context lost across separate chats' problem multiplied across accounts rather than teammates.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Hey Deepa, saw you're advising several high-growth startups at once as a fractional RevOps/strategy leader. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2713,22 +2949,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Sam Poutakidis</t>
+          <t>Mariya Valeva</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Fractional CFO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>New AI Automation Agency</t>
+          <t>Independent, B2B SaaS clients (~$2M+ ARR)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sampoutakidis/</t>
+          <t>https://www.linkedin.com/in/mariyavaleva-yourscalingpartner/</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2738,21 +2974,26 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Founder of a brand-new AI automation agency. Very early-stage by definition; single search snippet only.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Newest-stage AI-native agency founder in this sheet -- strong thematic fit, lower-confidence single-source finding.</t>
+          <t>Fractional CFO working with early-stage B2B SaaS companies around the $2M+ ARR mark -- i.e. the 5-50 person stage. Finance/ops-adjacent rather than pure marketing/sales ops.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Hey Sam — saw you just founded a new AI automation agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+          <t>Ops-adjacent (finance) leader embedded in multiple small SaaS teams; weaker fit than the RevOps/MOps rows above but same team-size band and same fractional-across-many-small-teams dynamic -- worth a lower-priority pass.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mariya, saw you work as a fractional CFO across multiple early-stage B2B SaaS clients. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2761,22 +3002,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>M Kazemi</t>
+          <t>John McArdle</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Web design agency (Issaquah, WA)</t>
+          <t>Sequoia Solutions -- RevOps/HubSpot consultancy for early-stage B2B tech</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/m-kazemi-098880242/</t>
+          <t>https://www.linkedin.com/in/john-mcardle-m-s-71b58178/</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2786,21 +3027,26 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small web design agency. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+          <t>Founded a small consultancy that has worked with dozens of early-stage companies cleaning up CRM/HubSpot data and building GTM systems -- not the 'Sequoia' VC firm, a separate small boutique of the same name.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Hey M — saw you're running your own web design agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
+          <t>Founder-led small consultancy serving exactly the early-stage company band multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Hey John, saw the dozens of early-stage companies you've helped clean up CRM/HubSpot data at Sequoia Solutions. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2809,22 +3055,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Michael Lieu</t>
+          <t>Roberto Guerra</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Boldly -- design agency (London)</t>
+          <t>Revenue Hub Latam -- RevOps + HubSpot for B2B companies in LATAM</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/michael-lieu-77746972/</t>
+          <t>https://www.linkedin.com/in/robguerra/</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2834,21 +3080,26 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of an award-winning design agency explicitly described as a small team. Good qualitative size signal.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Explicitly 'small team' self-positioning -- solid company-size signal without a hard headcount number.</t>
+          <t>Runs a boutique RevOps/HubSpot consultancy for B2B companies across LATAM, publicly writing about pipeline, CRM, forecasting -- and AI.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael — saw you're running Boldly with a small team of creative minds. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
+          <t>Boutique consultancy founder already writing about AI in the RevOps workflow -- direct thematic and company-stage fit.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Hey Roberto, saw your posts on pipeline, forecasting, and AI at Revenue Hub Latam. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2857,22 +3108,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Kristen Ransom</t>
+          <t>Johnathan Wang</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CTO &amp; Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IncluDe Web Design and Development Agency</t>
+          <t>The SaaS Consultants -- fractional CMO / marketing agency for SaaS</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kristen-m-ransom/</t>
+          <t>https://www.linkedin.com/in/johnathan-wang/</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2882,21 +3133,26 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>CTO/Founder of a small web design/dev agency, publicly interested in AI adoption for the field. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Technical founder already thinking about AI adoption -- good early-adopter signal.</t>
+          <t>Runs a small fractional-CMO agency for SaaS businesses and has personally built social-media-management software using Python/JavaScript and AI -- technical enough to be a strong early adopter.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristen — saw your interest in AI adoption for web design and development. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
+          <t>Small agency founder who is also hands-on technical/AI-building -- good combination of ICP fit and early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Hey Johnathan, saw you built your own AI-powered social media tooling while running The SaaS Consultants. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2905,22 +3161,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Stefen Phelps</t>
+          <t>Alex Williams</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Independent HubSpot Consultant</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Kelp Creative Agency</t>
+          <t>Independent -- solo HubSpot consulting practice</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stefenphelps/</t>
+          <t>https://www.linkedin.com/in/awoxford/</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2930,21 +3186,26 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Software engineer and co-founder of a small creative agency. Headcount unconfirmed -- single search snippet only.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Technical co-founder at a small creative agency -- good blend of ICP fit and technical early-adopter likelihood.</t>
+          <t>Solo independent HubSpot implementation/strategy consultant -- a one-person shop, which is close to the purest form of the 'wearing every hat, no one to share tool context with' ICP signal.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Hey Stefen — saw you co-founded Kelp Creative Agency. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+          <t>Solo consultant -- exact company-stage fit by definition, though this is a one-person 'team' rather than 5-50 people; worth including as a different flavor of the same pain (no one to share context with at all).</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex, saw you run your own solo HubSpot consulting practice. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -2953,22 +3214,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Dean Swennumson</t>
+          <t>Ajay G.</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder, Head of Operations</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Superstate</t>
+          <t>MAWD Agency -- Google Ads/SEO/websites for small businesses</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/dean-swennumson-075798125/</t>
+          <t>https://www.linkedin.com/in/ajayg514/</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2978,21 +3239,26 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Co-founder wearing the Head of Operations hat at an early-stage startup. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Textbook 'founder wearing the ops hat' ICP fit; company size inferred from co-founder/early-stage framing, not confirmed.</t>
+          <t>Founder of a small AI-forward performance-marketing agency serving small-business clients.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Hey Dean — saw you're co-founder and Head of Operations at Superstate. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
+          <t>Small agency founder in the exact small-business-serving segment; last-name not public in the source, listed as found.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ajay, saw you run MAWD Agency managing Google Ads, SEO, and websites for small businesses. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3001,22 +3267,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Leah Bolden</t>
+          <t>Philip Ledgerwood</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Head of Operations</t>
+          <t>AI Consultant / Software Developer</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>See Jane Drill</t>
+          <t>Independent -- solo AI consulting practice</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/leah-bolden-24419314</t>
+          <t>https://www.linkedin.com/in/phil-ledgerwood/</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3026,21 +3292,26 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/Head of Operations at a small DIY-resource startup. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Founder wearing the ops hat at an early-stage company -- solid ICP fit by role and company stage.</t>
+          <t>Solo independent consultant helping companies adopt AI securely. One-person practice -- same 'no one to share context with' signal as other solo consultants in this sheet.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Hey Leah — saw you're co-founder and Head of Operations at See Jane Drill. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
+          <t>Solo AI consultant -- direct thematic fit and purest form of the company-stage signal.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Hey Philip, saw you help companies use AI securely and purposefully as an independent consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3049,22 +3320,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Michael McCormack</t>
+          <t>Oles Dziub</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; COO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>10X ERP</t>
+          <t>Hey Digital -- SaaS performance marketing &amp; creative agency</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/michael-mccormack-10xerp/</t>
+          <t>https://www.linkedin.com/in/oles-dziub-b2b-saas-paid-ads-expert/</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3074,21 +3345,26 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/COO of a small startup, explicitly noted as acting as the de-facto Operations Manager -- wearing multiple hats.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Co-founder explicitly wearing both COO and hands-on ops-manager hats -- strong 'founder wearing every hat' ICP fit.</t>
+          <t>Co-founder of a small agency specializing in paid ads for B2B SaaS companies -- serves exactly multiplayer's target client base.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael — saw you're co-founder and de-facto Operations Manager at 10X ERP. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
+          <t>Agency founder specializing in the B2B SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Hey Oles, saw you're running Hey Digital, a performance marketing agency focused specifically on B2B SaaS. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3097,7 +3373,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Pavels Mordvicevs</t>
+          <t>Becky Kuntz</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3107,12 +3383,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Camel Digital -- PPC agency for B2B SaaS</t>
+          <t>BK's Bookkeeping</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pavels-mordvicevs-2aaa4666/</t>
+          <t>https://www.linkedin.com/in/becky-kuntz/</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3122,21 +3398,26 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small PPC agency explicitly targeting B2B SaaS founders -- serves exactly multiplayer's target client base.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Agency founder specializing in the B2B SaaS vertical multiplayer targets -- strong client-overlap fit, same pattern as Oles Dziub.</t>
+          <t>Founder of a small virtual bookkeeping practice serving small-business clients. Finance-ops-adjacent, similar band to Mariya Valeva elsewhere in this sheet.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Hey Pavels — saw you're targeting B2B SaaS founders specifically through Camel Digital. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
+          <t>Small finance-ops shop founder -- weaker fit than marketing/RevOps rows but same company-stage band and same 'wearing every hat' pain.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Hey Becky, saw you help small business owners get time back through BK's Bookkeeping. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3145,22 +3426,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Aaron Arnold</t>
+          <t>Tom Wells</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>FeatherDot Media Group LLC -- video production/growth</t>
+          <t>Wells Virtual Bookkeeping, LLC</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fdmg/</t>
+          <t>https://www.linkedin.com/in/tom-wells-rad60/</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3170,21 +3451,26 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small video production/growth agency, explicitly positions AI repurposing as part of the offering.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>AI-forward small agency founder -- direct thematic fit.</t>
+          <t>Small virtual bookkeeping practice; actively participates in an AI Mastermind group -- already engaged with AI adoption specifically.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Hey Aaron — saw your work helping brands scale with strategic video content and AI repurposing. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
+          <t>Small ops-adjacent shop already active in an AI-adoption community -- good readiness signal despite being outside core marketing/RevOps.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Hey Tom, saw you're part of an AI Mastermind group applying tech-forward solutions to bookkeeping. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3193,22 +3479,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Evan Cassidy</t>
+          <t>Michael Lieu</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CEO &amp; Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Boomin' Brands Media</t>
+          <t>Boldly -- design agency (London)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/evanbcassidy/</t>
+          <t>https://www.linkedin.com/in/michael-lieu-77746972/</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3218,21 +3504,26 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small creative media agency, already using AI content tools in production. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder already hands-on with AI production tools -- good early-adopter signal.</t>
+          <t>Co-founder of an award-winning design agency explicitly described as a small team. Good qualitative size signal.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Hey Evan — saw you're using AI tools like Heygen and Freepik at Boomin' Brands Media. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
+          <t>Explicitly 'small team' self-positioning -- solid company-size signal without a hard headcount number.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael, saw you're running Boldly with a small team of creative minds. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3241,22 +3532,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Yash Arora</t>
+          <t>Michael McCormack</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Founder / Producer</t>
+          <t>Co-Founder &amp; COO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Lemonade Creatives</t>
+          <t>10X ERP</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/yasharora16/</t>
+          <t>https://www.linkedin.com/in/michael-mccormack-10xerp/</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3266,21 +3557,26 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Founder/producer of a small creative production studio incorporating AI-led production. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder already building AI into the production pipeline -- direct thematic fit.</t>
+          <t>Co-founder/COO of a small startup, explicitly noted as acting as the de-facto Operations Manager -- wearing multiple hats.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Hey Yash — saw your AI-led creative production work at Lemonade Creatives. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
+          <t>Co-founder explicitly wearing both COO and hands-on ops-manager hats -- strong 'founder wearing every hat' ICP fit.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael, saw you're co-founder and de-facto Operations Manager at 10X ERP. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3289,22 +3585,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Paul Dietrich</t>
+          <t>Pavels Mordvicevs</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CPO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Spherecast (Y Combinator S24)</t>
+          <t>Camel Digital -- PPC agency for B2B SaaS</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pauldietrich98/</t>
+          <t>https://www.linkedin.com/in/pavels-mordvicevs-2aaa4666/</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3314,21 +3610,26 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CPO of a YC S24-batch startup -- accelerator batch is public record, confirming very-early company stage.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage; technical co-founder role suggests strong early-adopter fit.</t>
+          <t>Founder of a small PPC agency explicitly targeting B2B SaaS founders -- serves exactly multiplayer's target client base.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Hey Paul — saw you're co-founder and CPO of Spherecast, a YC S24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
+          <t>Agency founder specializing in the B2B SaaS vertical multiplayer targets -- strong client-overlap fit, same pattern as Oles Dziub.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Hey Pavels, saw you're targeting B2B SaaS founders specifically through Camel Digital. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3337,22 +3638,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Avi Konduru</t>
+          <t>Aaron Arnold</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Shor (Y Combinator S25)</t>
+          <t>FeatherDot Media Group LLC -- video production/growth</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/avi-konduru-54b3a6bb/</t>
+          <t>https://www.linkedin.com/in/fdmg/</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3362,21 +3663,26 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage, textbook ICP by definition.</t>
+          <t>Founder of a small video production/growth agency, explicitly positions AI repurposing as part of the offering.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Hey Avi — saw you're co-founder of Shor, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
+          <t>AI-forward small agency founder -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Hey Aaron, saw your work helping brands scale with strategic video content and AI repurposing. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3385,22 +3691,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Dhruv Roongta</t>
+          <t>Ebru Yildirim</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>slashy.com (Y Combinator S25)</t>
+          <t>Ollang -- localization</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/dhruv-roongta-421a7b214/</t>
+          <t>https://www.linkedin.com/in/ebru-yildirim-ollang/</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3410,21 +3716,26 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder/CEO of a small localization company with two decades of enterprise localization experience, publicly skeptical of AI-solves-everything narratives -- a thoughtful, engaged voice.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Hey Dhruv — saw you're co-founder of slashy.com, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
+          <t>Small agency founder actively engaging with AI's real limits in her field -- a more skeptical but still relevant prospect.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ebru, saw your take that AI translating doesn't mean localization is solved. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3433,22 +3744,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Crystal J. Morgan</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Fractional Customer Success Consultant</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>AgentMail (Y Combinator S25)</t>
+          <t>Independent -- serves SaaS founders and CS teams</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/michaelhyunkim/</t>
+          <t>https://www.linkedin.com/in/crystaljmorgan/</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3458,21 +3769,26 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup building AI-agent-related infrastructure -- confirmed very-early stage and directly AI-native.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder in the AI-agent space itself -- strong thematic AND company-stage fit.</t>
+          <t>Fractional Customer Success consultant serving multiple small SaaS clients at once -- same fractional-across-many-teams pattern as other consultant rows in this sheet.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael — saw you're co-founder of AgentMail, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
+          <t>Fractional CS consultant across small SaaS clients -- ops-adjacent vertical (customer success) not yet represented in this sheet.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Hey Crystal, saw you help SaaS founders and CS teams with customer success operations as a fractional consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3481,22 +3797,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Ishaan Sehgal</t>
+          <t>Jamiu Akanbi</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Omnara (Y Combinator S25)</t>
+          <t>Hidden Gems -- creator-led growth for B2B AI &amp; SaaS companies</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ishaan-sehgal/</t>
+          <t>https://www.linkedin.com/in/jamiu-akanbi/</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3506,21 +3822,26 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small agency specializing in B2B AI/SaaS client growth -- serves exactly multiplayer's target client base.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Hey Ishaan — saw you're co-founder of Omnara, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
+          <t>Agency founder specializing in the B2B AI/SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jamiu, saw you're running Hidden Gems, focused on creator-led growth specifically for B2B AI &amp; SaaS companies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3529,22 +3850,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Raj Lad</t>
+          <t>Harry Dixon</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CEO &amp; Co-Founder</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Infinite (Y Combinator W25)</t>
+          <t>Building mate -- AI growth teammate for small businesses</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rajlad/</t>
+          <t>https://www.linkedin.com/in/harryjdixon1/</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3554,21 +3875,26 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Co-founder/CEO of an early-stage startup building an AI teammate product for small businesses -- directly AI-native and thematically adjacent.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Hey Raj — saw you're co-founder of Infinite, a YC W25 company, previously at Sardine. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
+          <t>Early-stage AI-native founder building a directly adjacent product category -- strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Hey Harry, saw you're building 'mate,' an AI growth teammate for small businesses. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3577,22 +3903,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Kushal Mohta</t>
+          <t>Mihai Iancu</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Optifye.ai (Y Combinator W25)</t>
+          <t>MspCoreX -- AI-first platform for Managed Service Providers</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kushal-mohta-6926931b4/</t>
+          <t>https://www.linkedin.com/in/mihai-iancu-2605681a/</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3602,21 +3928,26 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W25-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage AI founder -- strong thematic AND company-stage fit.</t>
+          <t>Founder/CEO of a small AI-first platform for MSPs -- directly AI-native, unifying-tools angle close to multiplayer's own pitch.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Hey Kushal — saw you're co-founder of Optifye.ai, a YC W25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
+          <t>AI-native small-company founder building a product with a very similar 'unify fragmented tools' thesis.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mihai, saw you're building MspCoreX to replace fragmented MSP tool stacks with one intelligent core. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3625,22 +3956,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Nand Vinchhi</t>
+          <t>Michelle McCulloch</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Axal (Y Combinator W25)</t>
+          <t>Real Marketing Muscle -- helps small/mid-sized agencies grow</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nandvinchhi/</t>
+          <t>https://www.linkedin.com/in/michelle-mcculloch-616b953/</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3650,21 +3981,26 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small consultancy explicitly focused on helping other small agencies grow -- both an ICP member and a possible channel into other small agencies.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Hey Nand — saw you're co-founder of Axal, a YC W25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
+          <t>Small consultancy founder whose own client base is other small agencies -- potential dual lead/channel value.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michelle, saw your mission of helping small and mid-sized agencies grow through Real Marketing Muscle. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3673,7 +4009,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>William Barthell</t>
+          <t>Austin Richard</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3683,12 +4019,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Janet AI (Y Combinator S25)</t>
+          <t>digital3 AI -- AI accessibility for entrepreneurs and small businesses</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/william-barthell/</t>
+          <t>https://www.linkedin.com/in/digital3ai/</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3698,21 +4034,26 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage AI founder -- strong thematic AND company-stage fit.</t>
+          <t>Co-founder of a small company focused on AI accessibility for small businesses -- directly aligned mission.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Hey William — saw you're co-founder of Janet AI, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
+          <t>AI-native small-company co-founder whose own mission overlaps directly with multiplayer's target audience.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Hey Austin, saw you're making AI accessible and practical for entrepreneurs and small business owners at digital3 AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3721,22 +4062,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Aditya Iyengar</t>
+          <t>Yael Chen Zion</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Candor (Y Combinator W25)</t>
+          <t>Ashley Digital -- brand voice/content agency</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aditya-v-iyengar/</t>
+          <t>https://www.linkedin.com/in/yaelchenzion/</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3746,21 +4087,26 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W25-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small content/brand-voice agency, already building custom AI agents into the workflow -- directly AI-native.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Hey Aditya — saw you're co-founder of Candor, a YC W25 company focused on insider-risk. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
+          <t>Small agency founder already building bespoke AI agents -- strong thematic fit and technical sophistication.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Hey Yael, saw you built an AI agent trained on multiple brand voices and content formats at Ashley Digital. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3769,7 +4115,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Adam Wooten</t>
+          <t>Ai Jane L.</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3779,12 +4125,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Taia -- translation workflow platform / AI consultant</t>
+          <t>Common AI -- AI/no-code accessibility for small businesses</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adamwooten/</t>
+          <t>https://www.linkedin.com/in/aijane-common-ai/</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3794,21 +4140,26 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Translation-tech/AI consultant and founder of a small workflow platform. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Small AI-native tooling founder -- direct thematic fit, different vertical (localization) for diversification.</t>
+          <t>Founder of a small company focused on AI accessibility for small businesses -- directly aligned mission with multiplayer's audience.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Hey Adam — saw you built Taia, a workflow system addressing friction in translation processes. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
+          <t>AI-native founder whose own mission is helping small businesses use AI -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ai, saw you're democratizing access to AI and no-code tools for individuals and small businesses through Common AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3817,22 +4168,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Ebru Yildirim</t>
+          <t>Vanhishikha Bhargava</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Ollang -- localization</t>
+          <t>Contensify -- SEO/content for B2B SaaS</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ebru-yildirim-ollang/</t>
+          <t>https://ae.linkedin.com/in/vanhishikhab</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3842,21 +4193,26 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small localization company with two decades of enterprise localization experience, publicly skeptical of AI-solves-everything narratives -- a thoughtful, engaged voice.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder actively engaging with AI's real limits in her field -- a more skeptical but still relevant prospect.</t>
+          <t>Founder of a small content/SEO agency specializing in B2B SaaS clients across martech, AI, HRtech, CRM and devtools.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Hey Ebru — saw your take that AI translating doesn't mean localization is solved. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr">
+          <t>Agency founder specializing in the exact B2B SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Hey Vanhishikha, saw you've partnered with 100+ B2B SaaS companies on SEO and content through Contensify. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3865,7 +4221,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Adriana Biarnes Garcia</t>
+          <t>Susan Sarit</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3875,12 +4231,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Libre Design Studio -- design studio for founders/startups</t>
+          <t>Empower and Cultivate -- People Ops &amp; Systems consulting</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adriana-biarnes-garcia/</t>
+          <t>https://www.linkedin.com/in/susan-sarit/</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3890,21 +4246,26 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small design studio explicitly positioned to serve founders/startups. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Small studio founder serving the exact startup client base multiplayer targets.</t>
+          <t>Founder of a small People Ops consultancy explicitly supporting small business owners and founders.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Hey Adriana — saw you run Libre Design Studio specifically for founders and startups. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
+          <t>Consultant serving the exact small-founder audience multiplayer targets, in an underrepresented vertical (people ops).</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Hey Susan, saw you help founders build self-sufficient teams as a People Ops &amp; Systems consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3913,7 +4274,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Atiqur Rahaman</t>
+          <t>Heidi R. Haskins</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3923,12 +4284,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Design Monks</t>
+          <t>Elevated Prana People Ops Consulting</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/atiq31416/</t>
+          <t>https://www.linkedin.com/in/heidiparks/</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3938,21 +4299,26 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small design agency. Headcount unconfirmed -- single search snippet only.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- company-stage fit inferred from agency type, lower-confidence single-source finding.</t>
+          <t>Founder of a small People Ops consultancy focused on startups and tech companies specifically.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Hey Atiqur — saw you founded Design Monks. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
+          <t>Consultant explicitly serving the startup/tech audience multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Hey Heidi, saw you focus on People Ops/HR solutions specifically for startups and tech companies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -3961,22 +4327,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Crystal J. Morgan</t>
+          <t>Michelle Dicks</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Fractional Customer Success Consultant</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Independent -- serves SaaS founders and CS teams</t>
+          <t>Quantum People Ops</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/crystaljmorgan/</t>
+          <t>https://www.linkedin.com/in/michelle-dicks-3872a791/</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3986,21 +4352,26 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Fractional Customer Success consultant serving multiple small SaaS clients at once -- same fractional-across-many-teams pattern as other consultant rows in this sheet.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Fractional CS consultant across small SaaS clients -- ops-adjacent vertical (customer success) not yet represented in this sheet.</t>
+          <t>Owner of a small People Ops consultancy providing scalable HR systems for growing teams.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Hey Crystal — saw you help SaaS founders and CS teams with customer success operations as a fractional consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
+          <t>Consultant in the people-ops vertical serving growing small teams.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michelle, saw you provide scalable HR systems for growing teams through Quantum People Ops. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4009,7 +4380,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Thomas Christensen</t>
+          <t>Danielle Laurent</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4019,12 +4390,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Revora Consultants -- Customer Success consulting for B2B SaaS</t>
+          <t>Founder's HR Lab</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/thomas-christensen-0814a39/</t>
+          <t>https://www.linkedin.com/in/danielle-laurent/</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4034,21 +4405,26 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small CS consultancy for B2B SaaS companies. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Small CS consultancy founder serving the exact small-SaaS client base multiplayer targets.</t>
+          <t>Founder of a small HR consultancy explicitly focused on building systems for small businesses and agency owners.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Hey Thomas — saw you help B2B SaaS companies turn Customer Success into measurable revenue at Revora Consultants. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr">
+          <t>Consultant serving small agency owners specifically -- direct overlap with the agency-founder rows elsewhere in this sheet.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Hey Danielle, saw you're passionate about building systems for small businesses and helping agency owners specifically. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4057,22 +4433,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Peter Varga</t>
+          <t>Anis Msakni</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Search &amp; AI Visibility Consultant</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Lafluence &amp; Trendin -- AI-native OS for influencer agencies</t>
+          <t>Independent -- for B2B/SaaS companies</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/petervarga1/</t>
+          <t>https://es.linkedin.com/in/anis-msakni-7b17991a9</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4082,21 +4458,26 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Ex-Google, founder of two small companies including an explicitly AI-native product for influencer agencies. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>AI-native small-company founder -- direct thematic fit.</t>
+          <t>Solo independent Search &amp; AI Visibility consultant for B2B/SaaS companies.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Hey Peter — saw you're building Trendin, an AI-native operating system for influencer agencies. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
+          <t>Solo consultant serving multiplayer's exact target client base -- purest form of the company-stage signal.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Hey Anis, saw you help B2B/SaaS companies grow visibility and revenue through SEO and AEO. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4105,7 +4486,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Jamiu Akanbi</t>
+          <t>Peter O'Donoghue</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4115,12 +4496,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Hidden Gems -- creator-led growth for B2B AI &amp; SaaS companies</t>
+          <t>Nynch -- growth platform for consultants and fractionals</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jamiu-akanbi/</t>
+          <t>https://www.linkedin.com/in/peterodonoghue/</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4130,21 +4511,26 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small agency specializing in B2B AI/SaaS client growth -- serves exactly multiplayer's target client base.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Agency founder specializing in the B2B AI/SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+          <t>Founder of a small SaaS company building tools for the exact fractional-consultant audience heavily represented elsewhere in this sheet.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Hey Jamiu — saw you're running Hidden Gems, focused on creator-led growth specifically for B2B AI &amp; SaaS companies. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr">
+          <t>Small SaaS founder whose own customer base overlaps with many other rows in this sheet -- interesting potential channel as well as direct lead.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Hey Peter, saw you're building Nynch, a growth platform specifically for consultants and fractional professionals. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4153,7 +4539,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Krishna Kammili</t>
+          <t>Michael Twiddy</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4163,12 +4549,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>LegalConnect -- AI-assisted legal documents for SMEs</t>
+          <t>Fame -- The B2B Podcast Agency</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/krishnakammili/</t>
+          <t>https://uk.linkedin.com/in/michael-twiddy-1a1391196</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4178,21 +4564,26 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small legal-tech company already combining AI drafting with human review. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>AI-native small-company founder in an underrepresented vertical (legal tech) -- direct thematic fit, good diversification.</t>
+          <t>Founder of a small B2B podcast production agency, already discussing AI integration in the workflow.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Hey Krishna — saw you built LegalConnect to deliver AI-drafted, solicitor-reviewed legal documents for SMEs. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
+          <t>Small agency founder already engaging with AI in production -- good adoption-readiness signal.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael, saw you discuss AI integration in podcast production at Fame. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4201,22 +4592,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Jay Pietig</t>
+          <t>Oyinkro K</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Founding Partner</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Startup Legal Group, LLC (Kansas City)</t>
+          <t>K.OS VISUALS -- creative GTM partner for AI/SaaS companies</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jay-pietig-startuplegalgroup/</t>
+          <t>https://www.linkedin.com/in/oyinkro-creativevideographer/</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4226,21 +4617,26 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Founding partner of a small legal practice explicitly serving startup clients. Headcount unconfirmed.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Small legal practice founder serving the exact startup client base multiplayer targets -- underrepresented vertical for diversification.</t>
+          <t>Founder of a small creative agency positioned specifically for AI/SaaS company clients.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Hey Jay — saw you run Startup Legal Group, serving startup clients directly. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr">
+          <t>Small agency founder serving multiplayer's exact target client base.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Hey Oyinkro, saw you're positioning K.OS VISUALS as a creative GTM partner for fast-growing AI/SaaS companies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4249,22 +4645,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Chris Pisarski</t>
+          <t>Costin Modoianu</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Strategic Video Partner</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Crustdata (Y Combinator F24)</t>
+          <t>Independent -- video for SaaS &amp; Tech</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/chris-pisarski/</t>
+          <t>https://www.linkedin.com/in/costin-modoianu/</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4274,21 +4670,26 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC F24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Solo/small video production consultant specializing in SaaS and tech clients.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Hey Chris — saw you're co-founder of Crustdata, a YC F24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
+          <t>Solo consultant serving multiplayer's exact target client base.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Hey Costin, saw you turn complex SaaS products into clear, high-impact video as a strategic video partner. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4297,22 +4698,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Manmohit Grewal</t>
+          <t>Marek Bartík</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Crustdata (Y Combinator F24)</t>
+          <t>pipetail.io -- AWS &amp; Kubernetes DevOps consulting</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/manmohitgrewal/</t>
+          <t>https://www.linkedin.com/in/marekbartik/</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4322,21 +4723,26 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC F24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Solo/small DevOps consultancy founder. Technical audience, likely an early adopter of new tooling.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Hey Manmohit — saw you're co-founder of Crustdata, a YC F24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr">
+          <t>Solo technical consultant -- purest form of the company-stage signal, strong early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Hey Marek, saw you help companies adopt DevOps culture through on-site workshops and consulting at pipetail.io. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4345,22 +4751,22 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Shawn Shivdat</t>
+          <t>Michal Maxian</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Penciled (Y Combinator W24)</t>
+          <t>AI &amp; Cloud Architecture consulting -- built a RAG platform for 15k+ users</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/shawn-shivdat/</t>
+          <t>https://www.linkedin.com/in/mmaxian/</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4370,21 +4776,26 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>AI &amp; Cloud Architect and founder of a small consultancy, hands-on building AI infrastructure himself.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Hey Shawn — saw you're co-founder and CEO of Penciled, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
+          <t>Deeply technical AI-native founder -- strong thematic fit and early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michal, saw you built a RAG platform for 15k+ users and now consult on DevOps culture and AI adoption. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4393,22 +4804,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Sarah Hamer</t>
+          <t>Sara Pastor Ruprichova</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder / COO</t>
+          <t>Fractional CMO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>RetailReady (Y Combinator W24)</t>
+          <t>White Cloud Communications (Prague)</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sarah-hamer/</t>
+          <t>https://www.linkedin.com/in/pastorsara/</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4418,21 +4829,26 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/COO of a YC W24-batch startup -- confirmed very-early stage, and she's the one directly wearing the ops hat.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage COO -- exact 'founder wearing the ops hat' ICP fit with confirmed company stage.</t>
+          <t>Founder of a small strategic marketing consultancy serving growing businesses across Europe and beyond.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Hey Sarah — saw you're co-founder and COO of RetailReady, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr">
+          <t>Fractional marketing consultant serving small businesses -- direct ICP fit.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sara, saw you help founders and SMEs turn marketing spend into measurable growth through White Cloud Communications. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4441,22 +4857,22 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Chris Aeberli</t>
+          <t>Jonny Butler</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Fractional CMO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Sonia (Y Combinator W24)</t>
+          <t>Independent -- strategy &amp; execution for early-stage B2B SaaS</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/chris-aeberli/</t>
+          <t>https://www.linkedin.com/in/jonnybutler/</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4466,21 +4882,26 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Fractional CMO with direct in-house B2B SaaS marketing leadership experience, now serving early-stage SaaS clients.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Hey Chris — saw you're co-founder of Sonia, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr">
+          <t>Fractional marketing consultant with direct B2B SaaS operator background -- strong ICP and empathy fit.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jonny, saw you've been 3x Head of Marketing at B2B SaaS startups before going fractional. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4489,22 +4910,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>William Wang</t>
+          <t>Hugo Pereira</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Fractional CGO/CMO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Centralize (Y Combinator W24)</t>
+          <t>Independent -- B2B SaaS &amp; deep tech</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/williamwang77/</t>
+          <t>https://www.linkedin.com/in/hugosbpereira/</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4514,21 +4935,26 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Fractional CGO/CMO for B2B SaaS and deep tech, author and previously exited founder himself.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Hey William — saw you're co-founder of Centralize, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr">
+          <t>Fractional consultant with founder-side empathy (previously exited a company himself) -- strong ICP fit.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Hey Hugo, saw you wrote "Teams in Hell" and are a 1x exited founder now doing fractional growth work. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4537,22 +4963,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Andy Li</t>
+          <t>Marcus McGehee</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Respan (Y Combinator W24)</t>
+          <t>The AI Consulting Lab</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hanheli/</t>
+          <t>https://www.linkedin.com/in/marcusmcgehee/</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4562,21 +4988,26 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage by accelerator batch.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small AI-adoption consultancy whose core finding -- that AI adoption fails on culture/training, not technology -- is nearly identical to multiplayer's own thesis about scattered, unused AI tool access.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Hey Andy — saw you're co-founder and CEO of Respan, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr">
+          <t>Near-perfect thematic match: his own research names the exact 'AI tools bought but not actually adopted/shared' problem multiplayer is built to solve.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Hey Marcus, saw your observation that companies buy AI licenses, announce it, and six months later only 10% of the team is actually using the tools. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4585,22 +5016,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Givi Beridze</t>
+          <t>David MacKillop</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>KLIPY (Techstars-backed)</t>
+          <t>MacKillop Solutions -- AI agent and automation consulting</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/giviberidze/</t>
+          <t>https://www.linkedin.com/in/david-mackillop/</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4610,21 +5041,26 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a Techstars-backed early-stage startup -- confirmed very-early stage by accelerator affiliation.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Accelerator-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small AI automation consultancy, hands-on building agent workflows for clients.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Hey Givi — saw you're co-founder and CEO of KLIPY, a Techstars-backed company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr">
+          <t>Technical AI-agent-building consultant -- strong thematic fit and early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Hey David, saw you build intelligent workflows and AI agents using tools like n8n, Make.com, and Airtable. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4633,7 +5069,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Karla Valdivieso</t>
+          <t>Matthew Kuchera</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4643,12 +5079,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Shappi (Techstars-backed)</t>
+          <t>Mission AI Consulting</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kvaldivieso/</t>
+          <t>https://www.linkedin.com/in/matthewkuchera/</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4658,21 +5094,26 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a Techstars-backed early-stage startup -- confirmed very-early stage by accelerator affiliation.</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Accelerator-backed early-stage founder -- confirmed company stage.</t>
+          <t>Co-founder/CEO of a small AI consultancy specifically focused on platform adoption and implementation -- exactly the failure mode multiplayer addresses.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Hey Karla — saw you're co-founder and CEO of Shappi, a Techstars-backed company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
+          <t>AI-adoption specialist consultant -- near-direct thematic match with multiplayer's core value proposition.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Hey Matthew, saw you specialize in AI platform adoption and implementation at Mission AI Consulting. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4681,22 +5122,22 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Harry Dixon</t>
+          <t>Adam Goyette</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>CEO &amp; Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Building mate -- AI growth teammate for small businesses</t>
+          <t>Growth Union (Chicago) -- boutique growth agency for early-stage B2B SaaS</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/harryjdixon1/</t>
+          <t>https://www.linkedin.com/in/adam-goyette/</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4706,21 +5147,26 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of an early-stage startup building an AI teammate product for small businesses -- directly AI-native and thematically adjacent.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Early-stage AI-native founder building a directly adjacent product category -- strong thematic fit.</t>
+          <t>Ex-Help Scout / G2 growth marketing exec, now runs a small agency assembling senior marketers for early-stage B2B SaaS clients (Writer, RevenueHero, Recorded Future named as clients). Exact employee count unconfirmed but the agency's model (small senior team, no bench) implies well under 50.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Hey Harry — saw you're building 'mate,' an AI growth teammate for small businesses. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr">
+          <t>Founder running a lean agency serving exactly the small-SaaS client base multiplayer targets; company size inferred from agency model, not directly confirmed -- worth a second look before approving.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adam, saw you've built a lean senior team at Growth Union for early-stage B2B SaaS clients like Writer and Recorded Future. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4729,22 +5175,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Mihai Iancu</t>
+          <t>David Malevsky</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>MspCoreX -- AI-first platform for Managed Service Providers</t>
+          <t>Lynx Growth Agency (Hallandale Beach, FL)</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mihai-iancu-2605681a/</t>
+          <t>https://www.linkedin.com/in/david-malevsky/</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4754,21 +5200,26 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small AI-first platform for MSPs -- directly AI-native, unifying-tools angle close to multiplayer's own pitch.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>AI-native small-company founder building a product with a very similar 'unify fragmented tools' thesis.</t>
+          <t>Co-founder of a boutique agency (patient acquisition for regenerative/integrative clinics) built around AI-driven marketing and automation. Employee count unconfirmed -- RocketReach shows only a handful of verified staff, consistent with a small shop.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Hey Mihai — saw you're building MspCoreX to replace fragmented MSP tool stacks with one intelligent core. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr">
+          <t>Self-describes as 'resolving business challenges using AI' -- co-founder at a small, AI-forward agency is a strong qualitative fit even though the exact headcount isn't independently confirmed.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Hey David, saw you're building Lynx Growth Agency around AI-driven marketing and automation. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4777,22 +5228,22 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Michelle McCulloch</t>
+          <t>Alex Zlotko</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Real Marketing Muscle -- helps small/mid-sized agencies grow</t>
+          <t>Forecastio (B2B sales forecasting for HubSpot)</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/michelle-mcculloch-616b953/</t>
+          <t>https://www.linkedin.com/in/alexzlotko/</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4802,21 +5253,26 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small consultancy explicitly focused on helping other small agencies grow -- both an ICP member and a possible channel into other small agencies.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Small consultancy founder whose own client base is other small agencies -- potential dual lead/channel value.</t>
+          <t>17 years in B2B sales/CS, now CEO of Forecastio, a small SaaS company building sales forecasting tools. Publishes regularly on AI agents in RevOps specifically.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Hey Michelle — saw your mission of helping small and mid-sized agencies grow through Real Marketing Muscle. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr">
+          <t>Small SaaS founder/CEO already writing publicly about AI agents in RevOps -- direct thematic overlap with multiplayer's pitch, though exact headcount at Forecastio is unconfirmed.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex, saw your writing on AI agents in RevOps as CEO of Forecastio. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4825,22 +5281,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Nahme Chokeir</t>
+          <t>Kristofer Wille</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>RevOps Consultant &amp; Advisor</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Research Connections, Inc. -- market research consulting</t>
+          <t>Independent -- RevOpsVision (Berlin)</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nchokeir/</t>
+          <t>https://www.linkedin.com/in/kriswille-revopsvision-revenue-operations-consultant-advisory/</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4850,21 +5306,26 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small market research consultancy. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder in an underrepresented vertical (market research) for diversification.</t>
+          <t>10+ years in SalesOps/RevOps in Berlin's startup scene. Self-positions explicitly as helping 'C-Level Leaders &amp; Startups Supercharge Their Small RevOps Teams' -- his own tagline names the exact ICP.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Hey Nahme — saw you're running Research Connections, a market research consulting and field management company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr">
+          <t>His public positioning IS the ICP description almost word-for-word (small RevOps teams at startups). Company size self-described, not independently verified.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristofer, saw your tagline about helping startups supercharge their small RevOps teams. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4873,7 +5334,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Jake Wujastyk</t>
+          <t>Shaun Anderson</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4883,12 +5344,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>JakeWu Market Research</t>
+          <t>thisisagency.ai / hobo-web.co.uk -- forensic SEO agency</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jakewujastyk/</t>
+          <t>https://www.linkedin.com/in/shaun-anderson-hobo/</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4898,21 +5359,26 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Solo/very-small market research founder. Headcount unconfirmed -- single search snippet only.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Solo-founder small shop -- purest form of the company-stage signal, lower-confidence single source.</t>
+          <t>Founder of a small forensic-SEO agency, also positions himself as an AI Marketing Engineer building agentic AI systems. Found via a single search pass, not cross-verified for exact headcount.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Hey Jake — saw you run JakeWu Market Research, a small solo-founder shop. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr">
+          <t>Small agency founder already hands-on with agentic AI -- strong thematic fit; company size inferred from agency type, not confirmed.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Hey Shaun, saw you're building agentic AI systems as an AI Marketing Engineer while running thisisagency.ai. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4921,22 +5387,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Moritz Schmidt</t>
+          <t>Sam Anderson</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Chief Growth Officer / Founder</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>GEMESYS -- deeptech startup, confirmed under 10 people</t>
+          <t>Origin 63 -- small growth agency</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/schmidtmo/</t>
+          <t>https://www.linkedin.com/in/samanderson41/</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4946,21 +5412,26 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a deeptech startup explicitly described as under 10 people -- rare, directly confirmed headcount.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>One of the few rows with an explicitly confirmed sub-10-person headcount -- very high-confidence ICP fit.</t>
+          <t>Founder-level growth leader at a self-described small agency. Weaker verification than other rows -- single search snippet only.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Hey Moritz — saw you're co-founder of GEMESYS, a deeptech company with under 10 people. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr">
+          <t>Small growth-agency founder; include but treat as lower-confidence given only one source found.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sam, saw you're running Origin 63 as a small, results-focused growth agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -4969,22 +5440,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Jenna Gaidusek</t>
+          <t>Josh Harcus</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Revenue Growth &amp; Retention Lead</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>AI for Interior Designers -- educational platform</t>
+          <t>Hüify -- HubSpot partner agency</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jenna-gaidusek-33175a26/</t>
+          <t>https://www.linkedin.com/in/joshharcus/</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4994,21 +5465,26 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Founder/CEO of a small AI-education platform for a specific creative vertical (interior design). Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>AI-adoption-focused small-company founder in a new vertical (interior design) -- direct thematic fit.</t>
+          <t>Works on revenue growth/retention at a HubSpot partner agency. Exact headcount at Hüify unconfirmed.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Hey Jenna — saw you founded an education platform teaching interior designers to use AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr">
+          <t>HubSpot-partner-agency operator in the ops-tooling audience; company size inferred, not confirmed.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Hey Josh, saw your work on revenue growth and retention at Hüify, a HubSpot partner agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5017,22 +5493,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Nina Grondin</t>
+          <t>Clwyd Probert</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Partner &amp; Co-Founder</t>
+          <t>CEO &amp; Founder, AI Consultant</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Curioso -- design/architecture studio collective</t>
+          <t>Whitehat (UK) -- AI consulting</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nina-grondin/</t>
+          <t>https://uk.linkedin.com/in/clwyd-probert</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5042,21 +5518,26 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a small multidisciplinary design/architecture studio. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Small studio co-founder in an underrepresented vertical (architecture/design) for diversification.</t>
+          <t>CEO/Founder and AI consultant; company size and exact scope of Whitehat not independently confirmed -- single search snippet only.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Hey Nina — saw you co-founded Curioso, an assemblage of designers, architects, and business-minded creatives. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr">
+          <t>Directly in the AI-adoption-for-small-business space -- strong thematic fit, weaker company-size confirmation.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Hey Clwyd, saw you work as an AI consultant at Whitehat, helping businesses adopt AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5065,22 +5546,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Snehadeep Das</t>
+          <t>Clara Ma</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Designer</t>
+          <t>Chief of Staff (Employee #3)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Studio ORCHIVIZ -- AI-driven architectural visualization</t>
+          <t>Kairos -- very early-stage startup</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/snehadeep-das-81203b16b/</t>
+          <t>https://www.linkedin.com/in/clarama/</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5090,21 +5571,26 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Founder/Chief Designer of a small AI-driven architectural visualization studio. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>AI-native small studio founder -- direct thematic fit, underrepresented vertical.</t>
+          <t>Chief of Staff at a very early-stage startup (self-described as employee #3) -- partners with founders through the hardest parts of scaling. About as small/early as the ICP gets.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Hey Snehadeep — saw you use AI-driven design tools as founder of Studio ORCHIVIZ. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr">
+          <t>Employee #3 at an early-stage startup wearing the ops/chief-of-staff hat -- textbook ICP fit on company stage.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Hey Clara, saw you're employee #3 and Chief of Staff at Kairos. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5113,22 +5599,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Austin Richard</t>
+          <t>Riddhi Sharma</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CEO &amp; Founder</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>digital3 AI -- AI accessibility for entrepreneurs and small businesses</t>
+          <t>Thought In A Dot -- content marketing agency</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/digital3ai/</t>
+          <t>https://www.linkedin.com/in/sharmariddhi/</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5138,21 +5624,26 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a small company focused on AI accessibility for small businesses -- directly aligned mission.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>AI-native small-company co-founder whose own mission overlaps directly with multiplayer's target audience.</t>
+          <t>14+ years in leadership/brand content strategy, now founder/CEO of a content marketing agency. Employee count unconfirmed.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Hey Austin — saw you're making AI accessible and practical for entrepreneurs and small business owners at digital3 AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr">
+          <t>Small agency founder in the marketing-ops-adjacent content space.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Hey Riddhi, saw you're running Thought In A Dot as a content marketing agency and brand strategist. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5161,22 +5652,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Akeem Williams</t>
+          <t>John Liska</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Thread (Y Combinator W23)</t>
+          <t>Creative Engine (Austin, TX) -- branding &amp; digital marketing agency</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/akeem-k-williams/</t>
+          <t>https://www.linkedin.com/in/john-liska-594a52193/</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5186,21 +5677,26 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W23-batch startup. CAVEAT: this batch is ~3 years old as of now -- company may have grown well past the 5-50 band since the accelerator batch, worth re-checking current headcount before approving.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>YC-backed founder, but older batch than the other YC rows in this sheet -- lower confidence on current company size specifically.</t>
+          <t>Founder of a small branding/digital marketing agency in Austin. Employee count unconfirmed.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Hey Akeem — saw you're co-founder of Thread, a YC W23 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr">
+          <t>Small agency founder -- fits the company-stage band, size inferred not confirmed.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Hey John, saw you founded Creative Engine, a branding and digital marketing agency in Austin. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5209,22 +5705,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Ty Sharp</t>
+          <t>Laney M. Silverman</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>inBuild (Y Combinator W23)</t>
+          <t>The Design Boutique, Inc.</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ty-sharp/</t>
+          <t>https://www.linkedin.com/in/thedesignboutique/</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5234,21 +5730,26 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a YC W23-batch startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band -- re-verify before approving.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>YC-backed founder, older batch -- lower confidence on current size.</t>
+          <t>Founder of a self-described boutique design agency, explicitly positioned around small-team speed/agility.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Hey Ty — saw you're co-founder and CEO of inBuild, a YC W23 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr">
+          <t>Explicitly 'boutique' self-positioning -- good qualitative company-size signal even without a hard headcount number.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Hey Laney, saw you run The Design Boutique and pride yourselves on being able to pivot quickly as a small shop. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5257,22 +5758,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Vlad Matsiiako</t>
+          <t>Thomas Kranzle</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder, Director</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Infisical (Y Combinator W23)</t>
+          <t>Venture Visuals (Seattle) -- creative agency</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/vmatsiiako/</t>
+          <t>https://www.linkedin.com/in/thomaskranzle/</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5282,21 +5783,26 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W23-batch developer-tools startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>YC-backed founder in dev tooling, older batch -- lower confidence on current size, still worth a look given the technical audience fit.</t>
+          <t>Founder/Director of a small creative agency in Seattle. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Hey Vlad — saw you're co-founder of Infisical, a YC W23 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Hey Thomas, saw you founded Venture Visuals, a creative agency in Seattle. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5305,22 +5811,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Neel Balar</t>
+          <t>Santosh Kushwaha</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Clueso -- AI video creation (Y Combinator W23)</t>
+          <t>Visual Best -- AI Creative Production Agency</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/neelbalar7/</t>
+          <t>https://in.linkedin.com/in/santosh-kushwaha-explorer</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5330,21 +5836,26 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W23-batch AI startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>AI-native founder, older YC batch -- lower confidence on current size but strong thematic fit.</t>
+          <t>Founder of a small, explicitly AI-native creative production agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Hey Neel — saw you're co-founder of Clueso, an AI video creation company from YC W23. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
+          <t>AI-native agency founder -- strong thematic fit, company size inferred not confirmed.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Hey Santosh, saw you're running Visual Best, an AI creative production agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5353,7 +5864,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Yael Chen Zion</t>
+          <t>David Simões</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5363,12 +5874,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Ashley Digital -- brand voice/content agency</t>
+          <t>Sounds Good Agency -- Shopify Plus partner (CEE region)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/yaelchenzion/</t>
+          <t>https://cz.linkedin.com/in/davidjsimoes/en</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5378,21 +5889,26 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small content/brand-voice agency, already building custom AI agents into the workflow -- directly AI-native.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder already building bespoke AI agents -- strong thematic fit and technical sophistication.</t>
+          <t>Founder of a Shopify Plus agency serving DTC/B2B/Retail brands, self-describes as having an 'AI-first business mindset.' Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Hey Yael — saw you built an AI agent trained on multiple brand voices and content formats at Ashley Digital. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr">
+          <t>Small agency founder explicitly framing the business around AI-first thinking -- strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Hey David, saw you describe your business as having an AI-first mindset while running Sounds Good Agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5401,22 +5917,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Ai Jane L.</t>
+          <t>Mark Kennaley</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Common AI -- AI/no-code accessibility for small businesses</t>
+          <t>SoftwareFactory.ai -- AI-native software engineering consultancy</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aijane-common-ai/</t>
+          <t>https://www.linkedin.com/in/markkennaley/</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5426,21 +5942,26 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small company focused on AI accessibility for small businesses -- directly aligned mission with multiplayer's audience.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>AI-native founder whose own mission is helping small businesses use AI -- direct thematic fit.</t>
+          <t>Founder/CEO of a small AI-native software engineering consultancy. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Hey Ai — saw you're democratizing access to AI and no-code tools for individuals and small businesses through Common AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
+          <t>Small AI-forward software consultancy founder -- exactly the kind of technical early adopter this product needs.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mark, saw you're a pioneer in AI-native software engineering as founder of SoftwareFactory.ai. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5449,22 +5970,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Vanhishikha Bhargava</t>
+          <t>Dylan Kinder</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Independent AI Consultant</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Contensify -- SEO/content for B2B SaaS</t>
+          <t>Independent -- installs AI systems into service businesses</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/vanhishikhab</t>
+          <t>https://www.linkedin.com/in/dylankinder/</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5474,21 +5995,26 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small content/SEO agency specializing in B2B SaaS clients across martech, AI, HRtech, CRM and devtools.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Agency founder specializing in the exact B2B SaaS vertical multiplayer targets -- strong client-overlap fit.</t>
+          <t>Solo consultant helping small service businesses adopt AI tooling. Weaker verification -- single search snippet only.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Hey Vanhishikha — saw you've partnered with 100+ B2B SaaS companies on SEO and content through Contensify. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
+          <t>Solo AI-adoption consultant serving small businesses -- direct thematic fit, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dylan, saw you install AI systems into service businesses as an independent consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5497,22 +6023,22 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Sourav Ganguly</t>
+          <t>Alex Marantelos</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder / CEO</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Branded Minds -- brand strategy for early-stage startups</t>
+          <t>Intryc (Y Combinator S24)</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sourav-ganguly-3697904/</t>
+          <t>https://www.linkedin.com/in/alexmarantelos/</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5522,21 +6048,26 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small brand strategy agency serving early-stage startups. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder serving the exact early-stage startup client base multiplayer targets.</t>
+          <t>Co-founder/CEO of a YC S24-batch startup -- confirmed very-early-stage by accelerator batch, though exact current headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Hey Sourav — saw you focus on brand strategy specifically for early-stage startups at Branded Minds. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr">
+          <t>YC-backed early-stage founder -- confirmed company stage (accelerator batch is public record) even without a hard headcount number.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex, saw you're co-founder/CEO of Intryc, a Y Combinator S24 startup. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5545,22 +6076,22 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Ulli Appelbaum</t>
+          <t>Arham Khan</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CSO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>First The Trousers -- brand strategy and positioning consultancy</t>
+          <t>Pixated -- performance marketing agency (paid social/search)</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ulliappelbaum/</t>
+          <t>https://uk.linkedin.com/in/arhamkhan</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5570,21 +6101,26 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Founder/CSO of a small brand strategy consultancy. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Solo/small consultancy founder -- fits the consultant pattern in this sheet.</t>
+          <t>Founder of a small performance marketing agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Hey Ulli — saw you run First The Trousers as a brand strategy and positioning consultancy. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr">
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Hey Arham, saw you founded Pixated, a performance marketing agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5593,22 +6129,22 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Lance Mald</t>
+          <t>Alex Brown</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>BrandChef.ai</t>
+          <t>Tierra -- performance marketing agency for DTC ecommerce</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/lancemald/</t>
+          <t>https://www.linkedin.com/in/alex-brown-tierra/</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5618,21 +6154,26 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small, explicitly AI-named branding tool/agency. Headcount unconfirmed -- single search snippet only.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>AI-native small-company founder -- direct thematic fit, lower-confidence single-source finding.</t>
+          <t>Founder/CEO of a small performance marketing agency for DTC ecommerce brands. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Hey Lance — saw you're building BrandChef.ai. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr">
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex, saw you're scaling DTC ecommerce brands through Tierra. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5641,7 +6182,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Branden Lower</t>
+          <t>Beckie Blackburn-Cooper</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5651,12 +6192,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Build -- branding agency</t>
+          <t>Boutique recruiting agency</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/branden-lower-634b1b139/</t>
+          <t>https://www.linkedin.com/in/beckie-blackburn-cooper-bri/</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5666,21 +6207,26 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small branding agency. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+          <t>Founder of a small, self-described boutique recruiting agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Hey Branden — saw you founded Build, a branding agency built around practical design. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr">
+          <t>Explicitly 'boutique' self-positioning -- good qualitative size signal; different vertical (recruiting) than most of this sheet, useful diversification.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Hey Beckie, saw you run a boutique recruiting agency with a niche sector focus. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5689,22 +6235,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Morrie Schonfeld</t>
+          <t>Katie Matthews</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Pingo (Y Combinator S25) -- team of 3</t>
+          <t>CollabRecruit -- small recruiting agency</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/morrie-schonfeld-1628002b1/</t>
+          <t>https://www.linkedin.com/in/kmtalentfinder/</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5714,21 +6260,26 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup, confirmed team size of 3 -- as small and confirmed as this sheet gets.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Confirmed 3-person team -- extremely high-confidence ICP fit on company stage.</t>
+          <t>Founder/CEO of a small recruiting agency, writes publicly about technology's role in staffing. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Hey Morrie — saw you're co-founder of Pingo, a YC S25 company with a team of just 3 people. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
+          <t>Small agency founder already thinking publicly about tech's role in her business -- good adoption-readiness signal.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Hey Katie, saw your writing on balancing technology and human connection in recruiting at CollabRecruit. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5737,22 +6288,22 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Gurveer Singh</t>
+          <t>Jennifer Perez-Fong</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Certus AI (Y Combinator S25)</t>
+          <t>Bookkeeping Done Right</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gurveer-singh29/</t>
+          <t>https://www.linkedin.com/in/jennifer-perez-fong-cpa/</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5762,21 +6313,26 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a YC S25-batch AI startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage AI founder -- confirmed company stage.</t>
+          <t>CEO/founder of a small accounting practice serving SMBs, founded 2013. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Hey Gurveer — saw you're co-founder and CEO of Certus AI, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr">
+          <t>Small finance-ops shop founder -- same lower-priority band as other bookkeeping rows in this sheet.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jennifer, saw you founded Bookkeeping Done Right to serve small and medium businesses in South Florida. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5785,22 +6341,22 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Alex Avnit</t>
+          <t>Parry Headrick</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Paloma -- AI-native CRM (Y Combinator S25)</t>
+          <t>Crackle PR -- B2B tech PR agency (Boston)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alex-avnit-222b3611a/</t>
+          <t>https://www.linkedin.com/in/parryheadrick/</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5810,21 +6366,26 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch AI-native CRM startup -- confirmed very-early stage, ex-Deel/Revolut background.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage AI founder -- confirmed company stage and directly AI-native product.</t>
+          <t>Founder of a small B2B tech PR agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex — saw you're co-founder of Paloma, an AI-native CRM from YC S25. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
+          <t>B2B-tech-focused small agency founder -- adjacent vertical (PR) serving the same kind of small SaaS/tech clients.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Hey Parry, saw you're leading a team of senior PR leaders at Crackle PR. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5833,22 +6394,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Khalid A.</t>
+          <t>Carin Warner</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Munify (Y Combinator S25) -- 20 people, $20M ARR</t>
+          <t>Warner Communications -- PR &amp; comms strategy</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/khalidashmawy/</t>
+          <t>https://www.linkedin.com/in/carinwarner/</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5858,21 +6419,26 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Founder of a YC S25-batch startup with an explicitly confirmed 20-person team -- rare, directly confirmed headcount right in the ICP's sweet spot.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Explicitly confirmed 20-person team -- one of the highest-confidence company-size matches in this sheet.</t>
+          <t>Co-founder of a small PR/comms firm, publishes on AI strategy in communications specifically. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Hey Khalid — saw you've grown Munify to $20M ARR with a team of just 20 people. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr">
+          <t>Small agency co-founder already writing about AI strategy in her own field -- strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Hey Carin, saw your writing on AI strategy in communications. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5881,22 +6447,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Arjun Talati</t>
+          <t>Erika Torres</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Knowlify (Y Combinator S25)</t>
+          <t>85th &amp; Park Inc. -- creative marketing &amp; communications agency</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/arjun-talati/</t>
+          <t>https://www.linkedin.com/in/erika-torres85/</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5906,21 +6472,26 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small creative marketing/communications agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Hey Arjun — saw you're co-founder of Knowlify, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr">
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Hey Erika, saw you're running 85th &amp; Park, a culture-driven creative marketing and comms agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5929,22 +6500,22 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Nazli Danis</t>
+          <t>Sam Poutakidis</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Paloma -- AI-native CRM (Y Combinator S25)</t>
+          <t>New AI Automation Agency</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nazlidanis/</t>
+          <t>https://www.linkedin.com/in/sampoutakidis/</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5954,21 +6525,26 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch AI-native CRM startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage AI founder -- confirmed company stage; second co-founder at Paloma alongside Alex Avnit, both worth reaching independently.</t>
+          <t>Founder of a brand-new AI automation agency. Very early-stage by definition; single search snippet only.</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Hey Nazli — saw you're co-founder of Paloma, an AI-native CRM from YC S25. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr">
+          <t>Newest-stage AI-native agency founder in this sheet -- strong thematic fit, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sam, saw you just founded a new AI automation agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -5977,22 +6553,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Neha Suresh</t>
+          <t>M Kazemi</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Procindex (Y Combinator S25)</t>
+          <t>Web design agency (Issaquah, WA)</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nehasuresh1904/</t>
+          <t>https://www.linkedin.com/in/m-kazemi-098880242/</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6002,21 +6578,26 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder/CEO of a small web design agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Hey Neha — saw you're co-founder of Procindex, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr">
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Hey M, saw you're running your own web design agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6025,22 +6606,22 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>John Yeo</t>
+          <t>Kristen Ransom</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CTO &amp; Founder</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Autumn (Y Combinator S25)</t>
+          <t>IncluDe Web Design and Development Agency</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/johnyeocx</t>
+          <t>https://www.linkedin.com/in/kristen-m-ransom/</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6050,21 +6631,26 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC S25-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>CTO/Founder of a small web design/dev agency, publicly interested in AI adoption for the field. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Hey John — saw you're co-founder of Autumn, a YC S25 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr">
+          <t>Technical founder already thinking about AI adoption -- good early-adopter signal.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristen, saw your interest in AI adoption for web design and development. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6073,22 +6659,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Susan Sarit</t>
+          <t>Stefen Phelps</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Empower and Cultivate -- People Ops &amp; Systems consulting</t>
+          <t>Kelp Creative Agency</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/susan-sarit/</t>
+          <t>https://www.linkedin.com/in/stefenphelps/</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6098,21 +6684,26 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small People Ops consultancy explicitly supporting small business owners and founders.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Consultant serving the exact small-founder audience multiplayer targets, in an underrepresented vertical (people ops).</t>
+          <t>Software engineer and co-founder of a small creative agency. Headcount unconfirmed -- single search snippet only.</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Hey Susan — saw you help founders build self-sufficient teams as a People Ops &amp; Systems consultant. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr">
+          <t>Technical co-founder at a small creative agency -- good blend of ICP fit and technical early-adopter likelihood.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Hey Stefen, saw you co-founded Kelp Creative Agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6121,22 +6712,22 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Heidi R. Haskins</t>
+          <t>Dean Swennumson</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder, Head of Operations</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Elevated Prana People Ops Consulting</t>
+          <t>Superstate</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/heidiparks/</t>
+          <t>https://www.linkedin.com/in/dean-swennumson-075798125/</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6146,21 +6737,26 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small People Ops consultancy focused on startups and tech companies specifically.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Consultant explicitly serving the startup/tech audience multiplayer targets.</t>
+          <t>Co-founder wearing the Head of Operations hat at an early-stage startup. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Hey Heidi — saw you focus on People Ops/HR solutions specifically for startups and tech companies. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr">
+          <t>Textbook 'founder wearing the ops hat' ICP fit; company size inferred from co-founder/early-stage framing, not confirmed.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dean, saw you're co-founder and Head of Operations at Superstate. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6169,22 +6765,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Michelle Dicks</t>
+          <t>Leah Bolden</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Co-Founder &amp; Head of Operations</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Quantum People Ops</t>
+          <t>See Jane Drill</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/michelle-dicks-3872a791/</t>
+          <t>https://www.linkedin.com/in/leah-bolden-24419314</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6194,21 +6790,26 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Owner of a small People Ops consultancy providing scalable HR systems for growing teams.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Consultant in the people-ops vertical serving growing small teams.</t>
+          <t>Co-founder/Head of Operations at a small DIY-resource startup. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Hey Michelle — saw you provide scalable HR systems for growing teams through Quantum People Ops. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
+          <t>Founder wearing the ops hat at an early-stage company -- solid ICP fit by role and company stage.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Hey Leah, saw you're co-founder and Head of Operations at See Jane Drill. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6217,22 +6818,22 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Danielle Laurent</t>
+          <t>Evan Cassidy</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>CEO &amp; Founder</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Founder's HR Lab</t>
+          <t>Boomin' Brands Media</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/danielle-laurent/</t>
+          <t>https://www.linkedin.com/in/evanbcassidy/</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6242,21 +6843,26 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small HR consultancy explicitly focused on building systems for small businesses and agency owners.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Consultant serving small agency owners specifically -- direct overlap with the agency-founder rows elsewhere in this sheet.</t>
+          <t>Founder/CEO of a small creative media agency, already using AI content tools in production. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Hey Danielle — saw you're passionate about building systems for small businesses and helping agency owners specifically. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr">
+          <t>Small agency founder already hands-on with AI production tools -- good early-adopter signal.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Hey Evan, saw you're using AI tools like Heygen and Freepik at Boomin' Brands Media. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6265,22 +6871,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Jill Hutchins</t>
+          <t>Yash Arora</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Managing Consultant / Founder</t>
+          <t>Founder / Producer</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Your HR Partners -- boutique HR services</t>
+          <t>Lemonade Creatives</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jillhutchins/</t>
+          <t>https://www.linkedin.com/in/yasharora16/</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6290,21 +6896,26 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small, explicitly boutique HR consulting firm. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Explicitly 'boutique' self-positioning -- good qualitative size signal.</t>
+          <t>Founder/producer of a small creative production studio incorporating AI-led production. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Hey Jill — saw you run Your HR Partners as a boutique human resources services company. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
+          <t>Small agency founder already building AI into the production pipeline -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Hey Yash, saw your AI-led creative production work at Lemonade Creatives. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6313,7 +6924,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Taylor Scher</t>
+          <t>Adam Wooten</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6323,12 +6934,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Taylor Scher Consulting, LLC -- B2B SaaS SEO/content</t>
+          <t>Taia -- translation workflow platform / AI consultant</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/taylorjosephscher/</t>
+          <t>https://www.linkedin.com/in/adamwooten/</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6338,21 +6949,26 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Founder of a B2B SaaS content/SEO consultancy who just hired employee #1 -- explicitly confirmed as a 2-person shop right now.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Explicitly confirmed 2-person company (just crossed from solo to first hire) -- very high-confidence smallest-possible ICP fit.</t>
+          <t>Translation-tech/AI consultant and founder of a small workflow platform. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Hey Taylor — saw you just onboarded your first full-time employee (an editorial manager) at Taylor Scher Consulting. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr">
+          <t>Small AI-native tooling founder -- direct thematic fit, different vertical (localization) for diversification.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adam, saw you built Taia, a workflow system addressing friction in translation processes. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6361,7 +6977,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Apoorv Sharma</t>
+          <t>Adriana Biarnes Garcia</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6371,12 +6987,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Found On AI -- AI search for B2B SaaS (Bengaluru)</t>
+          <t>Libre Design Studio -- design studio for founders/startups</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/apoorvshrm/</t>
+          <t>https://www.linkedin.com/in/adriana-biarnes-garcia/</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6386,21 +7002,26 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small AI-search consultancy for B2B SaaS companies. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>AI-native small consultancy founder serving multiplayer's exact target client base.</t>
+          <t>Founder of a small design studio explicitly positioned to serve founders/startups. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Hey Apoorv — saw you're helping B2B SaaS companies with AI search visibility at Found On AI. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
+          <t>Small studio founder serving the exact startup client base multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adriana, saw you run Libre Design Studio specifically for founders and startups. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6409,22 +7030,22 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Anis Msakni</t>
+          <t>Atiqur Rahaman</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Search &amp; AI Visibility Consultant</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Independent -- for B2B/SaaS companies</t>
+          <t>Design Monks</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>https://es.linkedin.com/in/anis-msakni-7b17991a9</t>
+          <t>https://www.linkedin.com/in/atiq31416/</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6434,21 +7055,26 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Solo independent Search &amp; AI Visibility consultant for B2B/SaaS companies.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Solo consultant serving multiplayer's exact target client base -- purest form of the company-stage signal.</t>
+          <t>Founder of a small design agency. Headcount unconfirmed -- single search snippet only.</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Hey Anis — saw you help B2B/SaaS companies grow visibility and revenue through SEO and AEO. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr">
+          <t>Small agency founder -- company-stage fit inferred from agency type, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Hey Atiqur, saw you founded Design Monks. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6457,22 +7083,22 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Matt Craig</t>
+          <t>Thomas Christensen</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Sheepdog Projects -- BI Consulting and Data Strategy</t>
+          <t>Revora Consultants -- Customer Success consulting for B2B SaaS</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mathieucraig/</t>
+          <t>https://www.linkedin.com/in/thomas-christensen-0814a39/</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6482,21 +7108,26 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a small BI/data-strategy consultancy. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Small consultancy founder in an underrepresented vertical (BI/analytics) for diversification.</t>
+          <t>Founder of a small CS consultancy for B2B SaaS companies. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Hey Matt — saw you co-founded Sheepdog Projects to offer BI consulting and data strategy services. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr">
+          <t>Small CS consultancy founder serving the exact small-SaaS client base multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Hey Thomas, saw you help B2B SaaS companies turn Customer Success into measurable revenue at Revora Consultants. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6505,7 +7136,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Peter O'Donoghue</t>
+          <t>Peter Varga</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6515,12 +7146,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Nynch -- growth platform for consultants and fractionals</t>
+          <t>Lafluence &amp; Trendin -- AI-native OS for influencer agencies</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/peterodonoghue/</t>
+          <t>https://www.linkedin.com/in/petervarga1/</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6530,21 +7161,26 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small SaaS company building tools for the exact fractional-consultant audience heavily represented elsewhere in this sheet.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Small SaaS founder whose own customer base overlaps with many other rows in this sheet -- interesting potential channel as well as direct lead.</t>
+          <t>Ex-Google, founder of two small companies including an explicitly AI-native product for influencer agencies. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Hey Peter — saw you're building Nynch, a growth platform specifically for consultants and fractional professionals. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr">
+          <t>AI-native small-company founder -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Hey Peter, saw you're building Trendin, an AI-native operating system for influencer agencies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6553,7 +7189,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Michael Twiddy</t>
+          <t>Krishna Kammili</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6563,12 +7199,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Fame -- The B2B Podcast Agency</t>
+          <t>LegalConnect -- AI-assisted legal documents for SMEs</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/michael-twiddy-1a1391196</t>
+          <t>https://www.linkedin.com/in/krishnakammili/</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6578,21 +7214,26 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small B2B podcast production agency, already discussing AI integration in the workflow.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder already engaging with AI in production -- good adoption-readiness signal.</t>
+          <t>Founder of a small legal-tech company already combining AI drafting with human review. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael — saw you discuss AI integration in podcast production at Fame. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr">
+          <t>AI-native small-company founder in an underrepresented vertical (legal tech) -- direct thematic fit, good diversification.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Hey Krishna, saw you built LegalConnect to deliver AI-drafted, solicitor-reviewed legal documents for SMEs. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6601,22 +7242,22 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Jason Bradwell</t>
+          <t>Jay Pietig</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founding Partner</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>B2B Better -- podcast agency</t>
+          <t>Startup Legal Group, LLC (Kansas City)</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jason-bradwell-40b45751/</t>
+          <t>https://www.linkedin.com/in/jay-pietig-startuplegalgroup/</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6626,21 +7267,26 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small B2B podcast agency, publicly discussing AI in production. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder already engaging with AI in production -- good adoption-readiness signal.</t>
+          <t>Founding partner of a small legal practice explicitly serving startup clients. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Hey Jason — saw you discuss how AI is being integrated into podcast production workflows at B2B Better. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr">
+          <t>Small legal practice founder serving the exact startup client base multiplayer targets -- underrepresented vertical for diversification.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jay, saw you run Startup Legal Group, serving startup clients directly. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6649,22 +7295,22 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Dominic Noble</t>
+          <t>Nahme Chokeir</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Frogotiv -- animation/video studio</t>
+          <t>Research Connections, Inc. -- market research consulting</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/dominicnoble/</t>
+          <t>https://www.linkedin.com/in/nchokeir/</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6674,21 +7320,26 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small animation/video studio, explicitly confirmed to have started with just two founders doing every function themselves -- textbook wearing-every-hat ICP signal.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Confirmed tiny founding team doing every function personally -- very high-confidence ICP fit on company stage and pain point.</t>
+          <t>Founder/CEO of a small market research consultancy. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Hey Dominic — saw you and your co-founder originally handled strategy, storyboarding, illustration, animation, revisions, and client communication together at Frogotiv. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr">
+          <t>Small agency founder in an underrepresented vertical (market research) for diversification.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nahme, saw you're running Research Connections, a market research consulting and field management company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6697,7 +7348,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Oyinkro K</t>
+          <t>Jake Wujastyk</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6707,12 +7358,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>K.OS VISUALS -- creative GTM partner for AI/SaaS companies</t>
+          <t>JakeWu Market Research</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/oyinkro-creativevideographer/</t>
+          <t>https://www.linkedin.com/in/jakewujastyk/</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6722,21 +7373,26 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small creative agency positioned specifically for AI/SaaS company clients.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder serving multiplayer's exact target client base.</t>
+          <t>Solo/very-small market research founder. Headcount unconfirmed -- single search snippet only.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Hey Oyinkro — saw you're positioning K.OS VISUALS as a creative GTM partner for fast-growing AI/SaaS companies. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr">
+          <t>Solo-founder small shop -- purest form of the company-stage signal, lower-confidence single source.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jake, saw you run JakeWu Market Research, a small solo-founder shop. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6745,22 +7401,22 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Costin Modoianu</t>
+          <t>Jenna Gaidusek</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Strategic Video Partner</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Independent -- video for SaaS &amp; Tech</t>
+          <t>AI for Interior Designers -- educational platform</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/costin-modoianu/</t>
+          <t>https://www.linkedin.com/in/jenna-gaidusek-33175a26/</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6770,21 +7426,26 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Solo/small video production consultant specializing in SaaS and tech clients.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Solo consultant serving multiplayer's exact target client base.</t>
+          <t>Founder/CEO of a small AI-education platform for a specific creative vertical (interior design). Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Hey Costin — saw you turn complex SaaS products into clear, high-impact video as a strategic video partner. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr">
+          <t>AI-adoption-focused small-company founder in a new vertical (interior design) -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jenna, saw you founded an education platform teaching interior designers to use AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6793,22 +7454,22 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Marek Bartík</t>
+          <t>Nina Grondin</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Partner &amp; Co-Founder</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>pipetail.io -- AWS &amp; Kubernetes DevOps consulting</t>
+          <t>Curioso -- design/architecture studio collective</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/marekbartik/</t>
+          <t>https://www.linkedin.com/in/nina-grondin/</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6818,21 +7479,26 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Solo/small DevOps consultancy founder. Technical audience, likely an early adopter of new tooling.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Solo technical consultant -- purest form of the company-stage signal, strong early-adopter likelihood.</t>
+          <t>Co-founder of a small multidisciplinary design/architecture studio. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Hey Marek — saw you help companies adopt DevOps culture through on-site workshops and consulting at pipetail.io. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr">
+          <t>Small studio co-founder in an underrepresented vertical (architecture/design) for diversification.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Hey Nina, saw you co-founded Curioso, an assemblage of designers, architects, and business-minded creatives. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6841,22 +7507,22 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Michal Maxian</t>
+          <t>Snehadeep Das</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founder &amp; Chief Designer</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Architecture consulting -- built a RAG platform for 15k+ users</t>
+          <t>Studio ORCHIVIZ -- AI-driven architectural visualization</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mmaxian/</t>
+          <t>https://www.linkedin.com/in/snehadeep-das-81203b16b/</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6866,21 +7532,26 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Architect and founder of a small consultancy, hands-on building AI infrastructure himself.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Deeply technical AI-native founder -- strong thematic fit and early-adopter likelihood.</t>
+          <t>Founder/Chief Designer of a small AI-driven architectural visualization studio. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Hey Michal — saw you built a RAG platform for 15k+ users and now consult on DevOps culture and AI adoption. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr">
+          <t>AI-native small studio founder -- direct thematic fit, underrepresented vertical.</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Hey Snehadeep, saw you use AI-driven design tools as founder of Studio ORCHIVIZ. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6889,22 +7560,22 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Samuel Anderson-Levy</t>
+          <t>Akeem Williams</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Fractional CMO Agency (New York)</t>
+          <t>Thread (Y Combinator W23)</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/samuel-anderson-levy-33508528a/</t>
+          <t>https://www.linkedin.com/in/akeem-k-williams/</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6914,21 +7585,26 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small fractional-CMO agency. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Fractional marketing consultant -- direct fit with the marketing-ops ICP.</t>
+          <t>Co-founder of a YC W23-batch startup. CAVEAT: this batch is ~3 years old as of now -- company may have grown well past the 5-50 band since the accelerator batch, worth re-checking current headcount before approving.</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Hey Samuel — saw you run a fractional CMO agency in New York. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr">
+          <t>YC-backed founder, but older batch than the other YC rows in this sheet -- lower confidence on current company size specifically.</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Hey Akeem, saw you're co-founder of Thread, a YC W23 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6937,22 +7613,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Joshua Kimber</t>
+          <t>Ty Sharp</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; Owner</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>sōsh -- fractional CMO / digital marketing agency</t>
+          <t>inBuild (Y Combinator W23)</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/joshkimber/</t>
+          <t>https://www.linkedin.com/in/ty-sharp/</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6962,21 +7638,26 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Founder/owner of a small fractional-CMO/digital-marketing agency. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Small agency founder in the core marketing-ops ICP.</t>
+          <t>Co-founder/CEO of a YC W23-batch startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band -- re-verify before approving.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Hey Joshua — saw you're driving data-driven growth for clients as founder of sōsh. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr">
+          <t>YC-backed founder, older batch -- lower confidence on current size.</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ty, saw you're co-founder and CEO of inBuild, a YC W23 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -6985,22 +7666,22 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Sara Pastor Ruprichova</t>
+          <t>Vlad Matsiiako</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Fractional CMO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>White Cloud Communications (Prague)</t>
+          <t>Infisical (Y Combinator W23)</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pastorsara/</t>
+          <t>https://www.linkedin.com/in/vmatsiiako/</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7010,21 +7691,26 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small strategic marketing consultancy serving growing businesses across Europe and beyond.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Fractional marketing consultant serving small businesses -- direct ICP fit.</t>
+          <t>Co-founder of a YC W23-batch developer-tools startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band.</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Hey Sara — saw you help founders and SMEs turn marketing spend into measurable growth through White Cloud Communications. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr">
+          <t>YC-backed founder in dev tooling, older batch -- lower confidence on current size, still worth a look given the technical audience fit.</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Hey Vlad, saw you're co-founder of Infisical, a YC W23 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7033,22 +7719,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Kristen Palmer</t>
+          <t>Neel Balar</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder / CEO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Boutique digital marketing consulting firm (B2B professional services)</t>
+          <t>Clueso -- AI video creation (Y Combinator W23)</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kristenpalmer1/</t>
+          <t>https://www.linkedin.com/in/neelbalar7/</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7058,21 +7744,26 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a small, self-described boutique marketing consultancy. Ex-Accenture.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Explicitly 'boutique' self-positioning -- good qualitative company-size signal.</t>
+          <t>Co-founder of a YC W23-batch AI startup. CAVEAT: batch is ~3 years old, current headcount may exceed the 5-50 band.</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristen — saw you co-founded a boutique full-service digital marketing consulting firm for B2B professional services. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr">
+          <t>AI-native founder, older YC batch -- lower confidence on current size but strong thematic fit.</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Hey Neel, saw you're co-founder of Clueso, an AI video creation company from YC W23. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7081,22 +7772,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Dawn Jacobs</t>
+          <t>Sourav Ganguly</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Fractional CMO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Independent -- partners with early-stage founders/CEOs</t>
+          <t>Branded Minds -- brand strategy for early-stage startups</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/dawnmjacobs/</t>
+          <t>https://www.linkedin.com/in/sourav-ganguly-3697904/</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7106,21 +7797,26 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Fractional CMO explicitly partnering with early-stage founders. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Fractional marketing consultant serving early-stage founders -- direct ICP fit.</t>
+          <t>Founder of a small brand strategy agency serving early-stage startups. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Hey Dawn — saw you partner with early-stage founders and CEOs to build brands that scale. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr">
+          <t>Small agency founder serving the exact early-stage startup client base multiplayer targets.</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sourav, saw you focus on brand strategy specifically for early-stage startups at Branded Minds. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7129,22 +7825,22 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Jonny Butler</t>
+          <t>Ulli Appelbaum</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Fractional CMO</t>
+          <t>Founder &amp; CSO</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Independent -- strategy &amp; execution for early-stage B2B SaaS</t>
+          <t>First The Trousers -- brand strategy and positioning consultancy</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jonnybutler/</t>
+          <t>https://www.linkedin.com/in/ulliappelbaum/</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7154,21 +7850,26 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Fractional CMO with direct in-house B2B SaaS marketing leadership experience, now serving early-stage SaaS clients.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Fractional marketing consultant with direct B2B SaaS operator background -- strong ICP and empathy fit.</t>
+          <t>Founder/CSO of a small brand strategy consultancy. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Hey Jonny — saw you've been 3x Head of Marketing at B2B SaaS startups before going fractional. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr">
+          <t>Solo/small consultancy founder -- fits the consultant pattern in this sheet.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ulli, saw you run First The Trousers as a brand strategy and positioning consultancy. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7177,22 +7878,22 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Hugo Pereira</t>
+          <t>Lance Mald</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Fractional CGO/CMO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Independent -- B2B SaaS &amp; deep tech</t>
+          <t>BrandChef.ai</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hugosbpereira/</t>
+          <t>https://www.linkedin.com/in/lancemald/</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7202,21 +7903,26 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Fractional CGO/CMO for B2B SaaS and deep tech, author and previously exited founder himself.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Fractional consultant with founder-side empathy (previously exited a company himself) -- strong ICP fit.</t>
+          <t>Founder of a small, explicitly AI-named branding tool/agency. Headcount unconfirmed -- single search snippet only.</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Hey Hugo — saw you wrote "Teams in Hell" and are a 1x exited founder now doing fractional growth work. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr">
+          <t>AI-native small-company founder -- direct thematic fit, lower-confidence single-source finding.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Hey Lance, saw you're building BrandChef.ai. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7225,22 +7931,22 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Annabell V.</t>
+          <t>Branden Lower</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CTO</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>CoCrafter (Y Combinator W24)</t>
+          <t>Build -- branding agency</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/annabell-v-86a73b227/</t>
+          <t>https://www.linkedin.com/in/branden-lower-634b1b139/</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7250,21 +7956,26 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CTO of a YC W24-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage technical co-founder -- confirmed company stage.</t>
+          <t>Founder of a small branding agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Hey Annabell — saw you're co-founder and CTO of CoCrafter, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr">
+          <t>Small agency founder -- company-stage fit inferred from agency type.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Hey Branden, saw you founded Build, a branding agency built around practical design. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7273,22 +7984,22 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Nicole Atack</t>
+          <t>Jill Hutchins</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Managing Consultant / Founder</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Yarn (Y Combinator W24)</t>
+          <t>Your HR Partners -- boutique HR services</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nicole-atack-98194b2b8/</t>
+          <t>https://www.linkedin.com/in/jillhutchins/</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7298,21 +8009,26 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small, explicitly boutique HR consulting firm. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Hey Nicole — saw you're co-founder of Yarn, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr">
+          <t>Explicitly 'boutique' self-positioning -- good qualitative size signal.</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jill, saw you run Your HR Partners as a boutique human resources services company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7321,22 +8037,22 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>David Lalor</t>
+          <t>Apoorv Sharma</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>CEO &amp; Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Swift (Y Combinator W24)</t>
+          <t>Found On AI -- AI search for B2B SaaS (Bengaluru)</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/davidlalor5/</t>
+          <t>https://www.linkedin.com/in/apoorvshrm/</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7346,21 +8062,26 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a YC W24-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small AI-search consultancy for B2B SaaS companies. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Hey David — saw you're CEO and co-founder of Swift, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr">
+          <t>AI-native small consultancy founder serving multiplayer's exact target client base.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Hey Apoorv, saw you're helping B2B SaaS companies with AI search visibility at Found On AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7369,22 +8090,22 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Md Abdul Halim Rafi</t>
+          <t>Matt Craig</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CTO</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Octolane AI (Y Combinator W24)</t>
+          <t>Sheepdog Projects -- BI Consulting and Data Strategy</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/md-abdul-halim-rafi/</t>
+          <t>https://www.linkedin.com/in/mathieucraig/</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7394,21 +8115,26 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CTO of a YC W24-batch AI startup -- confirmed very-early stage and directly AI-native.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage AI founder -- confirmed company stage.</t>
+          <t>Co-founder of a small BI/data-strategy consultancy. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Hey Md — saw you're co-founder and CTO of Octolane AI, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr">
+          <t>Small consultancy founder in an underrepresented vertical (BI/analytics) for diversification.</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Hey Matt, saw you co-founded Sheepdog Projects to offer BI consulting and data strategy services. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7417,22 +8143,22 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Joseph Palakapilly</t>
+          <t>Jason Bradwell</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Meticulate (Y Combinator W24)</t>
+          <t>B2B Better -- podcast agency</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jpalakapilly/</t>
+          <t>https://www.linkedin.com/in/jason-bradwell-40b45751/</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7442,21 +8168,26 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small B2B podcast agency, publicly discussing AI in production. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Hey Joseph — saw you're co-founder of Meticulate, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr">
+          <t>Small agency founder already engaging with AI in production -- good adoption-readiness signal.</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jason, saw you discuss how AI is being integrated into podcast production workflows at B2B Better. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7465,22 +8196,22 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Alex Choi</t>
+          <t>Samuel Anderson-Levy</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Basalt Tech (Y Combinator W24)</t>
+          <t>Fractional CMO Agency (New York)</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alex-choi/</t>
+          <t>https://www.linkedin.com/in/samuel-anderson-levy-33508528a/</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7490,21 +8221,26 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Co-founder of a YC W24-batch startup -- confirmed very-early stage.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>YC-backed early-stage founder -- confirmed company stage.</t>
+          <t>Founder of a small fractional-CMO agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex — saw you co-founded Basalt Tech with Maximillian Bhatti, a YC W24 company. Quick question: across your team, does everyone end up using ChatGPT or Claude solo, with zero shared visibility into what anyone else tried or decided? That's the exact gap I'm building multiplayer for — a shared workspace where each person's AI agent posts its work into one thread the whole team can see and jump into. Rounding up a few small teams to test it free for 30-60 days in exchange for feedback — worth a quick look?</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr">
+          <t>Fractional marketing consultant -- direct fit with the marketing-ops ICP.</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Hey Samuel, saw you run a fractional CMO agency in New York. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7513,22 +8249,22 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Marcus McGehee</t>
+          <t>Joshua Kimber</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founder &amp; Owner</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>The AI Consulting Lab</t>
+          <t>sōsh -- fractional CMO / digital marketing agency</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/marcusmcgehee/</t>
+          <t>https://www.linkedin.com/in/joshkimber/</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7538,21 +8274,26 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small AI-adoption consultancy whose core finding -- that AI adoption fails on culture/training, not technology -- is nearly identical to multiplayer's own thesis about scattered, unused AI tool access.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Near-perfect thematic match: his own research names the exact 'AI tools bought but not actually adopted/shared' problem multiplayer is built to solve.</t>
+          <t>Founder/owner of a small fractional-CMO/digital-marketing agency. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Hey Marcus — saw your observation that companies buy AI licenses, announce it, and six months later only 10% of the team is actually using the tools. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr">
+          <t>Small agency founder in the core marketing-ops ICP.</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Hey Joshua, saw you're driving data-driven growth for clients as founder of sōsh. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7561,22 +8302,22 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Miranda Jones</t>
+          <t>Kristen Palmer</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Founder / Lead Consultant</t>
+          <t>Co-Founder / CEO</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>AI Consulting Network</t>
+          <t>Boutique digital marketing consulting firm (B2B professional services)</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/miranda-jones-16a256115/</t>
+          <t>https://www.linkedin.com/in/kristenpalmer1/</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7586,21 +8327,26 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small AI-adoption consultancy for small businesses. Headcount unconfirmed.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>AI-adoption consultant serving multiplayer's exact target client base -- direct thematic fit.</t>
+          <t>Co-founder/CEO of a small, self-described boutique marketing consultancy. Ex-Accenture.</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Hey Miranda — saw you're empowering small businesses with AI tools and services through AI Consulting Network. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr">
+          <t>Explicitly 'boutique' self-positioning -- good qualitative company-size signal.</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kristen, saw you co-founded a boutique full-service digital marketing consulting firm for B2B professional services. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7609,22 +8355,22 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>David MacKillop</t>
+          <t>Dawn Jacobs</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Fractional CMO</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>MacKillop Solutions -- AI agent and automation consulting</t>
+          <t>Independent -- partners with early-stage founders/CEOs</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/david-mackillop/</t>
+          <t>https://www.linkedin.com/in/dawnmjacobs/</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7634,21 +8380,26 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Founder of a small AI automation consultancy, hands-on building agent workflows for clients.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Technical AI-agent-building consultant -- strong thematic fit and early-adopter likelihood.</t>
+          <t>Fractional CMO explicitly partnering with early-stage founders. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Hey David — saw you build intelligent workflows and AI agents using tools like n8n, Make.com, and Airtable. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr">
+          <t>Fractional marketing consultant serving early-stage founders -- direct ICP fit.</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dawn, saw you partner with early-stage founders and CEOs to build brands that scale. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7657,22 +8408,22 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Matthew Kuchera</t>
+          <t>Miranda Jones</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO</t>
+          <t>Founder / Lead Consultant</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Mission AI Consulting</t>
+          <t>AI Consulting Network</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/matthewkuchera/</t>
+          <t>https://www.linkedin.com/in/miranda-jones-16a256115/</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -7682,21 +8433,26 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Co-founder/CEO of a small AI consultancy specifically focused on platform adoption and implementation -- exactly the failure mode multiplayer addresses.</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>AI-adoption specialist consultant -- near-direct thematic match with multiplayer's core value proposition.</t>
+          <t>Founder of a small AI-adoption consultancy for small businesses. Headcount unconfirmed.</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Hey Matthew — saw you specialize in AI platform adoption and implementation at Mission AI Consulting. Curious if this resonates: across the small teams/clients you work with, is everyone using ChatGPT or Claude on their own, with no shared visibility into what got tried or decided? That's the gap I'm building multiplayer for — a shared workspace where a team's AI agents post their work into one thread instead of staying siloed in separate chats. Looking for a few small teams to test it free in exchange for feedback — think any of your clients (or you) would want an early look?</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr">
+          <t>AI-adoption consultant serving multiplayer's exact target client base -- direct thematic fit.</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Hey Miranda, saw you're empowering small businesses with AI tools and services through AI Consulting Network. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -7704,7 +8460,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7870,7 +8626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7878,11 +8634,12 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7913,25 +8670,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Profile Summary</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Match Reason</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Draft Message</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Date Found</t>
         </is>
@@ -7950,7 +8712,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Substack (independent) — background includes marketing ops leadership at Amazon</t>
+          <t>Substack (independent), background includes marketing ops leadership at Amazon</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -7965,21 +8727,26 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>Widely-read voice in the marketing-ops community; writes about team structure, career growth, and AI adoption in MOps. Not himself a 5-50 person company operator today (large-company background).</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Not a direct ICP lead -- flagged separately as a possible content/community distribution channel into the exact audience (marketing ops leads at small teams) rather than a cold-outreach target.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Hey Darrell — saw your newsletter on marketing ops team structure and career growth. I'm building multiplayer, a shared AI workspace for small ops teams — not pitching the community, just curious whether the 'everyone's using ChatGPT/Claude solo, zero shared visibility' problem is something you hear from members often. Open to a quick chat, and happy to share back whatever I learn.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Hey Darrell, saw your newsletter on marketing ops team structure and career growth. I'm researching how small ops teams actually use AI day to day, not pitching anything yet. Curious whether solo AI usage with little shared visibility across a team is a theme you hear from your community. Open to a quick chat, and happy to share back whatever I learn.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -8013,21 +8780,26 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Runs a long-running weekly newsletter for the marketing ops community; frequently features guest practitioners and AI-adoption discussion.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Same as Darrell Alfonso above -- a distribution/connector play into the ICP audience, not a direct 5-50 person company lead.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Hey Jen — saw your weekly newsletter for the marketing ops community. I'm building multiplayer, a shared AI workspace for small ops teams — not pitching the community, just curious whether the 'everyone's using ChatGPT/Claude solo, zero shared visibility' problem is something you hear from members often. Open to a quick chat, and happy to share back whatever I learn.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jen, saw your weekly newsletter for the marketing ops community. I'm researching how small ops teams actually use AI day to day, not pitching anything yet. Curious whether solo AI usage with little shared visibility across a team is a theme you hear from your community. Open to a quick chat, and happy to share back whatever I learn.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -8061,21 +8833,26 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Founded and runs MO Pros, the 4,000+ member marketing-ops community outreach-pipeline-context.md names directly as a target community. Certifies GTM Ops teams and runs the annual MOpza conference.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Not a cold-outreach target -- he IS the gatekeeper of the exact community your context doc lists as a source. Worth a warmer, separate approach (community partnership / sponsorship) rather than a first-touch DM template.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Hey Mike — saw MO Pros hitting 4,000+ marketing/RevOps members. I'm building multiplayer, a shared AI workspace for small ops teams — not pitching the community, just curious whether the 'everyone's using ChatGPT/Claude solo, zero shared visibility' problem is something you hear from members often. Open to a quick chat, and happy to share back whatever I learn.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mike, saw MO Pros hitting 4,000+ marketing/RevOps members. I'm researching how small ops teams actually use AI day to day, not pitching anything yet. Curious whether solo AI usage with little shared visibility across a team is a theme you hear from your community. Open to a quick chat, and happy to share back whatever I learn.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
@@ -8083,7 +8860,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -551,13 +551,13 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Hey Katheryn, saw you're running GROW Marketing Agency as a small, founder-led shop. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Katheryn, saw you're running GROW Marketing Agency as a small, founder-led shop. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -604,13 +604,13 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Hey Donna, saw your work bridging gaps and scaling teams as a startup RevOps operator. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Donna, saw your work bridging gaps and scaling teams as a startup RevOps operator. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -657,13 +657,13 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristy, saw scaling GTM systems for B2B SaaS companies through your boutique RevOps consultancy. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Kristy, saw scaling GTM systems for B2B SaaS companies through your boutique RevOps consultancy. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -710,13 +710,13 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Hey Jackie, saw you run Digital Marketing Direction as a virtual HubSpot partner agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Jackie, saw you run Digital Marketing Direction as a virtual HubSpot partner agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -763,13 +763,13 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Hey Josephine, saw your Chief of Staff role spanning GTM, Operations, and AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Josephine, saw your Chief of Staff role spanning GTM, Operations, and AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -816,13 +816,13 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Hey Raj, saw you're running Goodman Lantern, a B2B content marketing agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Raj, saw you're running Goodman Lantern, a B2B content marketing agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -869,13 +869,13 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Hey Paul, saw you're co-founder and CPO of Spherecast, a YC S24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Paul, saw you're co-founder and CPO of Spherecast, a YC S24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -922,13 +922,13 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Hey Avi, saw you're co-founder of Shor, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Avi, saw you're co-founder of Shor, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Hey Dhruv, saw you're co-founder of slashy.com, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Dhruv, saw you're co-founder of slashy.com, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1028,13 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael, saw you're co-founder of AgentMail, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Michael, saw you're co-founder of AgentMail, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1081,13 +1081,13 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Hey Ishaan, saw you're co-founder of Omnara, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Ishaan, saw you're co-founder of Omnara, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1134,13 +1134,13 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Hey Raj, saw you're co-founder of Infinite, a YC W25 company, previously at Sardine. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Raj, saw you're co-founder of Infinite, a YC W25 company, previously at Sardine. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1187,13 +1187,13 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Hey Kushal, saw you're co-founder of Optifye.ai, a YC W25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Kushal, saw you're co-founder of Optifye.ai, a YC W25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1240,13 +1240,13 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Hey Nand, saw you're co-founder of Axal, a YC W25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Nand, saw you're co-founder of Axal, a YC W25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1293,13 +1293,13 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Hey William, saw you're co-founder of Janet AI, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey William, saw you're co-founder of Janet AI, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1346,13 +1346,13 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Hey Aditya, saw you're co-founder of Candor, a YC W25 company focused on insider-risk. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Aditya, saw you're co-founder of Candor, a YC W25 company focused on insider-risk. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1399,13 +1399,13 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Hey Chris, saw you're co-founder of Crustdata, a YC F24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Chris, saw you're co-founder of Crustdata, a YC F24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1452,13 +1452,13 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Hey Manmohit, saw you're co-founder of Crustdata, a YC F24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Manmohit, saw you're co-founder of Crustdata, a YC F24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1505,13 +1505,13 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Hey Shawn, saw you're co-founder and CEO of Penciled, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Shawn, saw you're co-founder and CEO of Penciled, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1558,13 +1558,13 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Hey Sarah, saw you're co-founder and COO of RetailReady, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Sarah, saw you're co-founder and COO of RetailReady, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1611,13 +1611,13 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Hey Chris, saw you're co-founder of Sonia, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Chris, saw you're co-founder of Sonia, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1664,13 +1664,13 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Hey William, saw you're co-founder of Centralize, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey William, saw you're co-founder of Centralize, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1717,13 +1717,13 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Hey Andy, saw you're co-founder and CEO of Respan, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Andy, saw you're co-founder and CEO of Respan, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1770,13 +1770,13 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Hey Givi, saw you're co-founder and CEO of KLIPY, a Techstars-backed company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Givi, saw you're co-founder and CEO of KLIPY, a Techstars-backed company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1823,13 +1823,13 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Hey Karla, saw you're co-founder and CEO of Shappi, a Techstars-backed company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Karla, saw you're co-founder and CEO of Shappi, a Techstars-backed company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Hey Moritz, saw you're co-founder of GEMESYS, a deeptech company with under 10 people. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Moritz, saw you're co-founder of GEMESYS, a deeptech company with under 10 people. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1929,13 +1929,13 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Hey Morrie, saw you're co-founder of Pingo, a YC S25 company with a team of just 3 people. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Morrie, saw you're co-founder of Pingo, a YC S25 company with a team of just 3 people. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1982,13 +1982,13 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Hey Gurveer, saw you're co-founder and CEO of Certus AI, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Gurveer, saw you're co-founder and CEO of Certus AI, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex, saw you're co-founder of Paloma, an AI-native CRM from YC S25. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Alex, saw you're co-founder of Paloma, an AI-native CRM from YC S25. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2088,13 +2088,13 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Hey Khalid, saw you've grown Munify to $20M ARR with a team of just 20 people. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Khalid, saw you've grown Munify to $20M ARR with a team of just 20 people. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2141,13 +2141,13 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Hey Arjun, saw you're co-founder of Knowlify, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Arjun, saw you're co-founder of Knowlify, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2194,13 +2194,13 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Hey Nazli, saw you're co-founder of Paloma, an AI-native CRM from YC S25. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Nazli, saw you're co-founder of Paloma, an AI-native CRM from YC S25. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2247,13 +2247,13 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Hey Neha, saw you're co-founder of Procindex, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Neha, saw you're co-founder of Procindex, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2300,13 +2300,13 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Hey John, saw you're co-founder of Autumn, a YC S25 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey John, saw you're co-founder of Autumn, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2353,13 +2353,13 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Hey Taylor, saw you just onboarded your first full-time employee (an editorial manager) at Taylor Scher Consulting. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Taylor, saw you just onboarded your first full-time employee (an editorial manager) at Taylor Scher Consulting. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2406,13 +2406,13 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Hey Dominic, saw you and your co-founder originally handled strategy, storyboarding, illustration, animation, revisions, and client communication together at Frogotiv. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Dominic, saw you and your co-founder originally handled strategy, storyboarding, illustration, animation, revisions, and client communication together at Frogotiv. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2459,13 +2459,13 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Hey Annabell, saw you're co-founder and CTO of CoCrafter, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Annabell, saw you're co-founder and CTO of CoCrafter, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2512,13 +2512,13 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Hey Nicole, saw you're co-founder of Yarn, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Nicole, saw you're co-founder of Yarn, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2565,13 +2565,13 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Hey David, saw you're CEO and co-founder of Swift, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey David, saw you're CEO and co-founder of Swift, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2618,13 +2618,13 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Hey Md, saw you're co-founder and CTO of Octolane AI, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Md, saw you're co-founder and CTO of Octolane AI, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2671,13 +2671,13 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Hey Joseph, saw you're co-founder of Meticulate, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Joseph, saw you're co-founder of Meticulate, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2724,13 +2724,13 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex, saw you co-founded Basalt Tech with Maximillian Bhatti, a YC W24 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Alex, saw you co-founded Basalt Tech with Maximillian Bhatti, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2777,13 +2777,13 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Hey Elizabeth, saw you're running RevOps solo through PrecisionRevOps for multiple SaaS clients. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Elizabeth, saw you're running RevOps solo through PrecisionRevOps for multiple SaaS clients. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2830,13 +2830,13 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Hey Jeremy, saw you're juggling fractional RevOps/CRO roles across Rev, AgentSync, Ekho, and OperateWise at once. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Jeremy, saw you're juggling fractional RevOps/CRO roles across Rev, AgentSync, Ekho, and OperateWise at once. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2883,13 +2883,13 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Hey Haris, saw your recent post on what RevOps actually does and removing GTM silos. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Haris, saw your recent post on what RevOps actually does and removing GTM silos. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2936,13 +2936,13 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Hey Deepa, saw you're advising several high-growth startups at once as a fractional RevOps/strategy leader. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Deepa, saw you're advising several high-growth startups at once as a fractional RevOps/strategy leader. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2989,13 +2989,13 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Hey Mariya, saw you work as a fractional CFO across multiple early-stage B2B SaaS clients. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Mariya, saw you work as a fractional CFO across multiple early-stage B2B SaaS clients. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3042,13 +3042,13 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Hey John, saw the dozens of early-stage companies you've helped clean up CRM/HubSpot data at Sequoia Solutions. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey John, saw the dozens of early-stage companies you've helped clean up CRM/HubSpot data at Sequoia Solutions. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Hey Roberto, saw your posts on pipeline, forecasting, and AI at Revenue Hub Latam. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Roberto, saw your posts on pipeline, forecasting, and AI at Revenue Hub Latam. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3148,13 +3148,13 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Hey Johnathan, saw you built your own AI-powered social media tooling while running The SaaS Consultants. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Johnathan, saw you built your own AI-powered social media tooling while running The SaaS Consultants. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3201,13 +3201,13 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex, saw you run your own solo HubSpot consulting practice. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Alex, saw you run your own solo HubSpot consulting practice. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3254,13 +3254,13 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Hey Ajay, saw you run MAWD Agency managing Google Ads, SEO, and websites for small businesses. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Ajay, saw you run MAWD Agency managing Google Ads, SEO, and websites for small businesses. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3307,13 +3307,13 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Hey Philip, saw you help companies use AI securely and purposefully as an independent consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Philip, saw you help companies use AI securely and purposefully as an independent consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3360,13 +3360,13 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Hey Oles, saw you're running Hey Digital, a performance marketing agency focused specifically on B2B SaaS. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Oles, saw you're running Hey Digital, a performance marketing agency focused specifically on B2B SaaS. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3413,13 +3413,13 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Hey Becky, saw you help small business owners get time back through BK's Bookkeeping. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Becky, saw you help small business owners get time back through BK's Bookkeeping. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3466,13 +3466,13 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Hey Tom, saw you're part of an AI Mastermind group applying tech-forward solutions to bookkeeping. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Tom, saw you're part of an AI Mastermind group applying tech-forward solutions to bookkeeping. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3519,13 +3519,13 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael, saw you're running Boldly with a small team of creative minds. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Michael, saw you're running Boldly with a small team of creative minds. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3572,13 +3572,13 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael, saw you're co-founder and de-facto Operations Manager at 10X ERP. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Michael, saw you're co-founder and de-facto Operations Manager at 10X ERP. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3625,13 +3625,13 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Hey Pavels, saw you're targeting B2B SaaS founders specifically through Camel Digital. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Pavels, saw you're targeting B2B SaaS founders specifically through Camel Digital. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3678,13 +3678,13 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Hey Aaron, saw your work helping brands scale with strategic video content and AI repurposing. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Aaron, saw your work helping brands scale with strategic video content and AI repurposing. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3731,13 +3731,13 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Hey Ebru, saw your take that AI translating doesn't mean localization is solved. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Ebru, saw your take that AI translating doesn't mean localization is solved. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3784,13 +3784,13 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Hey Crystal, saw you help SaaS founders and CS teams with customer success operations as a fractional consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Crystal, saw you help SaaS founders and CS teams with customer success operations as a fractional consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3837,13 +3837,13 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Hey Jamiu, saw you're running Hidden Gems, focused on creator-led growth specifically for B2B AI &amp; SaaS companies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Jamiu, saw you're running Hidden Gems, focused on creator-led growth specifically for B2B AI &amp; SaaS companies. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3890,13 +3890,13 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Hey Harry, saw you're building 'mate,' an AI growth teammate for small businesses. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Harry, saw you're building 'mate,' an AI growth teammate for small businesses. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3943,13 +3943,13 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Hey Mihai, saw you're building MspCoreX to replace fragmented MSP tool stacks with one intelligent core. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Mihai, saw you're building MspCoreX to replace fragmented MSP tool stacks with one intelligent core. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3996,13 +3996,13 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Hey Michelle, saw your mission of helping small and mid-sized agencies grow through Real Marketing Muscle. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Michelle, saw your mission of helping small and mid-sized agencies grow through Real Marketing Muscle. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4049,13 +4049,13 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Hey Austin, saw you're making AI accessible and practical for entrepreneurs and small business owners at digital3 AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Austin, saw you're making AI accessible and practical for entrepreneurs and small business owners at digital3 AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4102,13 +4102,13 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Hey Yael, saw you built an AI agent trained on multiple brand voices and content formats at Ashley Digital. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Yael, saw you built an AI agent trained on multiple brand voices and content formats at Ashley Digital. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4155,13 +4155,13 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Hey Ai, saw you're democratizing access to AI and no-code tools for individuals and small businesses through Common AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Ai, saw you're democratizing access to AI and no-code tools for individuals and small businesses through Common AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4208,13 +4208,13 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Hey Vanhishikha, saw you've partnered with 100+ B2B SaaS companies on SEO and content through Contensify. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Vanhishikha, saw you've partnered with 100+ B2B SaaS companies on SEO and content through Contensify. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4261,13 +4261,13 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Hey Susan, saw you help founders build self-sufficient teams as a People Ops &amp; Systems consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Susan, saw you help founders build self-sufficient teams as a People Ops &amp; Systems consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4314,13 +4314,13 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Hey Heidi, saw you focus on People Ops/HR solutions specifically for startups and tech companies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Heidi, saw you focus on People Ops/HR solutions specifically for startups and tech companies. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4367,13 +4367,13 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Hey Michelle, saw you provide scalable HR systems for growing teams through Quantum People Ops. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Michelle, saw you provide scalable HR systems for growing teams through Quantum People Ops. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4420,13 +4420,13 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Hey Danielle, saw you're passionate about building systems for small businesses and helping agency owners specifically. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Danielle, saw you're passionate about building systems for small businesses and helping agency owners specifically. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4473,13 +4473,13 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Hey Anis, saw you help B2B/SaaS companies grow visibility and revenue through SEO and AEO. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Anis, saw you help B2B/SaaS companies grow visibility and revenue through SEO and AEO. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4526,13 +4526,13 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Hey Peter, saw you're building Nynch, a growth platform specifically for consultants and fractional professionals. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Peter, saw you're building Nynch, a growth platform specifically for consultants and fractional professionals. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4579,13 +4579,13 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Hey Michael, saw you discuss AI integration in podcast production at Fame. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Michael, saw you discuss AI integration in podcast production at Fame. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4632,13 +4632,13 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Hey Oyinkro, saw you're positioning K.OS VISUALS as a creative GTM partner for fast-growing AI/SaaS companies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Oyinkro, saw you're positioning K.OS VISUALS as a creative GTM partner for fast-growing AI/SaaS companies. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4685,13 +4685,13 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Hey Costin, saw you turn complex SaaS products into clear, high-impact video as a strategic video partner. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Costin, saw you turn complex SaaS products into clear, high-impact video as a strategic video partner. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4738,13 +4738,13 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Hey Marek, saw you help companies adopt DevOps culture through on-site workshops and consulting at pipetail.io. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Marek, saw you help companies adopt DevOps culture through on-site workshops and consulting at pipetail.io. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4791,13 +4791,13 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Hey Michal, saw you built a RAG platform for 15k+ users and now consult on DevOps culture and AI adoption. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Michal, saw you built a RAG platform for 15k+ users and now consult on DevOps culture and AI adoption. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4844,13 +4844,13 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Hey Sara, saw you help founders and SMEs turn marketing spend into measurable growth through White Cloud Communications. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Sara, saw you help founders and SMEs turn marketing spend into measurable growth through White Cloud Communications. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4897,13 +4897,13 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Hey Jonny, saw you've been 3x Head of Marketing at B2B SaaS startups before going fractional. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Jonny, saw you've been 3x Head of Marketing at B2B SaaS startups before going fractional. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4950,13 +4950,13 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Hey Hugo, saw you wrote "Teams in Hell" and are a 1x exited founder now doing fractional growth work. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Hugo, saw you wrote "Teams in Hell" and are a 1x exited founder now doing fractional growth work. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5003,13 +5003,13 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Hey Marcus, saw your observation that companies buy AI licenses, announce it, and six months later only 10% of the team is actually using the tools. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Marcus, saw your observation that companies buy AI licenses, announce it, and six months later only 10% of the team is actually using the tools. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5056,13 +5056,13 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Hey David, saw you build intelligent workflows and AI agents using tools like n8n, Make.com, and Airtable. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey David, saw you build intelligent workflows and AI agents using tools like n8n, Make.com, and Airtable. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5109,13 +5109,13 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Hey Matthew, saw you specialize in AI platform adoption and implementation at Mission AI Consulting. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Matthew, saw you specialize in AI platform adoption and implementation at Mission AI Consulting. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5162,13 +5162,13 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Hey Adam, saw you've built a lean senior team at Growth Union for early-stage B2B SaaS clients like Writer and Recorded Future. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Adam, saw you've built a lean senior team at Growth Union for early-stage B2B SaaS clients like Writer and Recorded Future. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5215,13 +5215,13 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Hey David, saw you're building Lynx Growth Agency around AI-driven marketing and automation. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey David, saw you're building Lynx Growth Agency around AI-driven marketing and automation. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5268,13 +5268,13 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex, saw your writing on AI agents in RevOps as CEO of Forecastio. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Alex, saw your writing on AI agents in RevOps as CEO of Forecastio. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5321,13 +5321,13 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristofer, saw your tagline about helping startups supercharge their small RevOps teams. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Kristofer, saw your tagline about helping startups supercharge their small RevOps teams. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5374,13 +5374,13 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Hey Shaun, saw you're building agentic AI systems as an AI Marketing Engineer while running thisisagency.ai. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Shaun, saw you're building agentic AI systems as an AI Marketing Engineer while running thisisagency.ai. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5427,13 +5427,13 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Hey Sam, saw you're running Origin 63 as a small, results-focused growth agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Sam, saw you're running Origin 63 as a small, results-focused growth agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5480,13 +5480,13 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Hey Josh, saw your work on revenue growth and retention at Hüify, a HubSpot partner agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Josh, saw your work on revenue growth and retention at Hüify, a HubSpot partner agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Hey Clwyd, saw you work as an AI consultant at Whitehat, helping businesses adopt AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Clwyd, saw you work as an AI consultant at Whitehat, helping businesses adopt AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5586,13 +5586,13 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Hey Clara, saw you're employee #3 and Chief of Staff at Kairos. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Clara, saw you're employee #3 and Chief of Staff at Kairos. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5639,13 +5639,13 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Hey Riddhi, saw you're running Thought In A Dot as a content marketing agency and brand strategist. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Riddhi, saw you're running Thought In A Dot as a content marketing agency and brand strategist. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5692,13 +5692,13 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Hey John, saw you founded Creative Engine, a branding and digital marketing agency in Austin. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey John, saw you founded Creative Engine, a branding and digital marketing agency in Austin. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5745,13 +5745,13 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Hey Laney, saw you run The Design Boutique and pride yourselves on being able to pivot quickly as a small shop. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Laney, saw you run The Design Boutique and pride yourselves on being able to pivot quickly as a small shop. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5798,13 +5798,13 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Hey Thomas, saw you founded Venture Visuals, a creative agency in Seattle. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Thomas, saw you founded Venture Visuals, a creative agency in Seattle. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5851,13 +5851,13 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Hey Santosh, saw you're running Visual Best, an AI creative production agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Santosh, saw you're running Visual Best, an AI creative production agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5904,13 +5904,13 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Hey David, saw you describe your business as having an AI-first mindset while running Sounds Good Agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey David, saw you describe your business as having an AI-first mindset while running Sounds Good Agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -5957,13 +5957,13 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Hey Mark, saw you're a pioneer in AI-native software engineering as founder of SoftwareFactory.ai. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Mark, saw you're a pioneer in AI-native software engineering as founder of SoftwareFactory.ai. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6010,13 +6010,13 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Hey Dylan, saw you install AI systems into service businesses as an independent consultant. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Dylan, saw you install AI systems into service businesses as an independent consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6063,13 +6063,13 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex, saw you're co-founder/CEO of Intryc, a Y Combinator S24 startup. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Alex, saw you're co-founder/CEO of Intryc, a Y Combinator S24 startup. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6116,13 +6116,13 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Hey Arham, saw you founded Pixated, a performance marketing agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Arham, saw you founded Pixated, a performance marketing agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6169,13 +6169,13 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Hey Alex, saw you're scaling DTC ecommerce brands through Tierra. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Alex, saw you're scaling DTC ecommerce brands through Tierra. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6222,13 +6222,13 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Hey Beckie, saw you run a boutique recruiting agency with a niche sector focus. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Beckie, saw you run a boutique recruiting agency with a niche sector focus. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6275,13 +6275,13 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Hey Katie, saw your writing on balancing technology and human connection in recruiting at CollabRecruit. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Katie, saw your writing on balancing technology and human connection in recruiting at CollabRecruit. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6328,13 +6328,13 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Hey Jennifer, saw you founded Bookkeeping Done Right to serve small and medium businesses in South Florida. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Jennifer, saw you founded Bookkeeping Done Right to serve small and medium businesses in South Florida. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6381,13 +6381,13 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Hey Parry, saw you're leading a team of senior PR leaders at Crackle PR. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Parry, saw you're leading a team of senior PR leaders at Crackle PR. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6434,13 +6434,13 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Hey Carin, saw your writing on AI strategy in communications. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Carin, saw your writing on AI strategy in communications. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6487,13 +6487,13 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Hey Erika, saw you're running 85th &amp; Park, a culture-driven creative marketing and comms agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Erika, saw you're running 85th &amp; Park, a culture-driven creative marketing and comms agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6540,13 +6540,13 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Hey Sam, saw you just founded a new AI automation agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Sam, saw you just founded a new AI automation agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6593,13 +6593,13 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Hey M, saw you're running your own web design agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey M, saw you're running your own web design agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6646,13 +6646,13 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristen, saw your interest in AI adoption for web design and development. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Kristen, saw your interest in AI adoption for web design and development. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Hey Stefen, saw you co-founded Kelp Creative Agency. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Stefen, saw you co-founded Kelp Creative Agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6752,13 +6752,13 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Hey Dean, saw you're co-founder and Head of Operations at Superstate. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Dean, saw you're co-founder and Head of Operations at Superstate. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6805,13 +6805,13 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Hey Leah, saw you're co-founder and Head of Operations at See Jane Drill. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Leah, saw you're co-founder and Head of Operations at See Jane Drill. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6858,13 +6858,13 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Hey Evan, saw you're using AI tools like Heygen and Freepik at Boomin' Brands Media. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Evan, saw you're using AI tools like Heygen and Freepik at Boomin' Brands Media. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6911,13 +6911,13 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Hey Yash, saw your AI-led creative production work at Lemonade Creatives. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Yash, saw your AI-led creative production work at Lemonade Creatives. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6964,13 +6964,13 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Hey Adam, saw you built Taia, a workflow system addressing friction in translation processes. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Adam, saw you built Taia, a workflow system addressing friction in translation processes. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7017,13 +7017,13 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Hey Adriana, saw you run Libre Design Studio specifically for founders and startups. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Adriana, saw you run Libre Design Studio specifically for founders and startups. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7070,13 +7070,13 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Hey Atiqur, saw you founded Design Monks. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Atiqur, saw you founded Design Monks. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7123,13 +7123,13 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Hey Thomas, saw you help B2B SaaS companies turn Customer Success into measurable revenue at Revora Consultants. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Thomas, saw you help B2B SaaS companies turn Customer Success into measurable revenue at Revora Consultants. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7176,13 +7176,13 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Hey Peter, saw you're building Trendin, an AI-native operating system for influencer agencies. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Peter, saw you're building Trendin, an AI-native operating system for influencer agencies. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7229,13 +7229,13 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Hey Krishna, saw you built LegalConnect to deliver AI-drafted, solicitor-reviewed legal documents for SMEs. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Krishna, saw you built LegalConnect to deliver AI-drafted, solicitor-reviewed legal documents for SMEs. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7282,13 +7282,13 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Hey Jay, saw you run Startup Legal Group, serving startup clients directly. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Jay, saw you run Startup Legal Group, serving startup clients directly. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7335,13 +7335,13 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Hey Nahme, saw you're running Research Connections, a market research consulting and field management company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Nahme, saw you're running Research Connections, a market research consulting and field management company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7388,13 +7388,13 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Hey Jake, saw you run JakeWu Market Research, a small solo-founder shop. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Jake, saw you run JakeWu Market Research, a small solo-founder shop. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7441,13 +7441,13 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Hey Jenna, saw you founded an education platform teaching interior designers to use AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Jenna, saw you founded an education platform teaching interior designers to use AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7494,13 +7494,13 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Hey Nina, saw you co-founded Curioso, an assemblage of designers, architects, and business-minded creatives. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Nina, saw you co-founded Curioso, an assemblage of designers, architects, and business-minded creatives. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7547,13 +7547,13 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Hey Snehadeep, saw you use AI-driven design tools as founder of Studio ORCHIVIZ. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Snehadeep, saw you use AI-driven design tools as founder of Studio ORCHIVIZ. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7600,13 +7600,13 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Hey Akeem, saw you're co-founder of Thread, a YC W23 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Akeem, saw you're co-founder of Thread, a YC W23 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7653,13 +7653,13 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Hey Ty, saw you're co-founder and CEO of inBuild, a YC W23 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Ty, saw you're co-founder and CEO of inBuild, a YC W23 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7706,13 +7706,13 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Hey Vlad, saw you're co-founder of Infisical, a YC W23 company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Vlad, saw you're co-founder of Infisical, a YC W23 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7759,13 +7759,13 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Hey Neel, saw you're co-founder of Clueso, an AI video creation company from YC W23. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Neel, saw you're co-founder of Clueso, an AI video creation company from YC W23. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7812,13 +7812,13 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Hey Sourav, saw you focus on brand strategy specifically for early-stage startups at Branded Minds. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Sourav, saw you focus on brand strategy specifically for early-stage startups at Branded Minds. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7865,13 +7865,13 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Hey Ulli, saw you run First The Trousers as a brand strategy and positioning consultancy. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Ulli, saw you run First The Trousers as a brand strategy and positioning consultancy. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7918,13 +7918,13 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Hey Lance, saw you're building BrandChef.ai. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Lance, saw you're building BrandChef.ai. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7971,13 +7971,13 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Hey Branden, saw you founded Build, a branding agency built around practical design. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Branden, saw you founded Build, a branding agency built around practical design. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8024,13 +8024,13 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Hey Jill, saw you run Your HR Partners as a boutique human resources services company. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Jill, saw you run Your HR Partners as a boutique human resources services company. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8077,13 +8077,13 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Hey Apoorv, saw you're helping B2B SaaS companies with AI search visibility at Found On AI. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Apoorv, saw you're helping B2B SaaS companies with AI search visibility at Found On AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8130,13 +8130,13 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Hey Matt, saw you co-founded Sheepdog Projects to offer BI consulting and data strategy services. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Matt, saw you co-founded Sheepdog Projects to offer BI consulting and data strategy services. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8183,13 +8183,13 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Hey Jason, saw you discuss how AI is being integrated into podcast production workflows at B2B Better. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Jason, saw you discuss how AI is being integrated into podcast production workflows at B2B Better. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8236,13 +8236,13 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Hey Samuel, saw you run a fractional CMO agency in New York. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Samuel, saw you run a fractional CMO agency in New York. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8289,13 +8289,13 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Hey Joshua, saw you're driving data-driven growth for clients as founder of sōsh. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Joshua, saw you're driving data-driven growth for clients as founder of sōsh. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8342,13 +8342,13 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Hey Kristen, saw you co-founded a boutique full-service digital marketing consulting firm for B2B professional services. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across your team, does everyone end up using ChatGPT or Claude on their own, or is there any shared visibility into what people are trying or deciding? Would you be open to a quick chat about how your team handles it?</t>
+          <t>Hey Kristen, saw you co-founded a boutique full-service digital marketing consulting firm for B2B professional services. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8395,13 +8395,13 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Hey Dawn, saw you partner with early-stage founders and CEOs to build brands that scale. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Dawn, saw you partner with early-stage founders and CEOs to build brands that scale. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8448,13 +8448,13 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Hey Miranda, saw you're empowering small businesses with AI tools and services through AI Consulting Network. I'm looking into how small teams actually use AI day to day before building anything. Quick question: across the teams or clients you work with, is AI tool usage mostly solo, or is there any shared visibility into what's being tried? Would love your read, open to a quick chat?</t>
+          <t>Hey Miranda, saw you're empowering small businesses with AI tools and services through AI Consulting Network. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8742,13 +8742,13 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Hey Darrell, saw your newsletter on marketing ops team structure and career growth. I'm researching how small ops teams actually use AI day to day, not pitching anything yet. Curious whether solo AI usage with little shared visibility across a team is a theme you hear from your community. Open to a quick chat, and happy to share back whatever I learn.</t>
+          <t>Hey Darrell, saw your newsletter on marketing ops team structure and career growth. Question for you: is solo AI tool usage with little shared visibility across a team something you hear about often from your community? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8795,13 +8795,13 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Hey Jen, saw your weekly newsletter for the marketing ops community. I'm researching how small ops teams actually use AI day to day, not pitching anything yet. Curious whether solo AI usage with little shared visibility across a team is a theme you hear from your community. Open to a quick chat, and happy to share back whatever I learn.</t>
+          <t>Hey Jen, saw your weekly newsletter for the marketing ops community. Question for you: is solo AI tool usage with little shared visibility across a team something you hear about often from your community? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8848,13 +8848,13 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Hey Mike, saw MO Pros hitting 4,000+ marketing/RevOps members. I'm researching how small ops teams actually use AI day to day, not pitching anything yet. Curious whether solo AI usage with little shared visibility across a team is a theme you hear from your community. Open to a quick chat, and happy to share back whatever I learn.</t>
+          <t>Hey Mike, saw MO Pros hitting 4,000+ marketing/RevOps members. Question for you: is solo AI tool usage with little shared visibility across a team something you hear about often from your community? Curious what you're seeing.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>

--- a/outreach/leads.xlsx
+++ b/outreach/leads.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -446,9 +446,10 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,15 +495,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Draft Message</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Date Found</t>
         </is>
@@ -551,11 +557,16 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>Hey Katheryn, saw you're running GROW Marketing Agency as a small, founder-led shop. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -604,11 +615,16 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>Hey Donna, saw your work bridging gaps and scaling teams as a startup RevOps operator. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -657,11 +673,16 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>Hey Kristy, saw scaling GTM systems for B2B SaaS companies through your boutique RevOps consultancy. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -710,11 +731,16 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>Hey Jackie, saw you run Digital Marketing Direction as a virtual HubSpot partner agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -763,11 +789,16 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>Hey Josephine, saw your Chief of Staff role spanning GTM, Operations, and AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -816,11 +847,16 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>Hey Raj, saw you're running Goodman Lantern, a B2B content marketing agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -869,11 +905,16 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>Hey Paul, saw you're co-founder and CPO of Spherecast, a YC S24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -922,11 +963,16 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>Hey Avi, saw you're co-founder of Shor, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -975,11 +1021,16 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>Hey Dhruv, saw you're co-founder of slashy.com, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1028,11 +1079,16 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>Hey Michael, saw you're co-founder of AgentMail, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1081,11 +1137,16 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>Hey Ishaan, saw you're co-founder of Omnara, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1134,11 +1195,16 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>Hey Raj, saw you're co-founder of Infinite, a YC W25 company, previously at Sardine. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1187,11 +1253,16 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>Hey Kushal, saw you're co-founder of Optifye.ai, a YC W25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1240,11 +1311,16 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>Hey Nand, saw you're co-founder of Axal, a YC W25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1293,11 +1369,16 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>Hey William, saw you're co-founder of Janet AI, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1346,11 +1427,16 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>Hey Aditya, saw you're co-founder of Candor, a YC W25 company focused on insider-risk. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1399,11 +1485,16 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>Hey Chris, saw you're co-founder of Crustdata, a YC F24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1452,11 +1543,16 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>Hey Manmohit, saw you're co-founder of Crustdata, a YC F24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1505,11 +1601,16 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>Hey Shawn, saw you're co-founder and CEO of Penciled, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1558,11 +1659,16 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>Hey Sarah, saw you're co-founder and COO of RetailReady, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1611,11 +1717,16 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>Hey Chris, saw you're co-founder of Sonia, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1664,11 +1775,16 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>Hey William, saw you're co-founder of Centralize, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1717,11 +1833,16 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>Hey Andy, saw you're co-founder and CEO of Respan, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1770,11 +1891,16 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>Hey Givi, saw you're co-founder and CEO of KLIPY, a Techstars-backed company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1823,11 +1949,16 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>Hey Karla, saw you're co-founder and CEO of Shappi, a Techstars-backed company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1876,11 +2007,16 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>Hey Moritz, saw you're co-founder of GEMESYS, a deeptech company with under 10 people. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1929,11 +2065,16 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>Hey Morrie, saw you're co-founder of Pingo, a YC S25 company with a team of just 3 people. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -1982,11 +2123,16 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>Hey Gurveer, saw you're co-founder and CEO of Certus AI, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2035,11 +2181,16 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>Hey Alex, saw you're co-founder of Paloma, an AI-native CRM from YC S25. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2088,11 +2239,16 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>Hey Khalid, saw you've grown Munify to $20M ARR with a team of just 20 people. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2141,11 +2297,16 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>Hey Arjun, saw you're co-founder of Knowlify, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2194,11 +2355,16 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>Hey Nazli, saw you're co-founder of Paloma, an AI-native CRM from YC S25. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2247,11 +2413,16 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>Hey Neha, saw you're co-founder of Procindex, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2300,11 +2471,16 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>Hey John, saw you're co-founder of Autumn, a YC S25 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2353,11 +2529,16 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>Hey Taylor, saw you just onboarded your first full-time employee (an editorial manager) at Taylor Scher Consulting. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2406,11 +2587,16 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>Hey Dominic, saw you and your co-founder originally handled strategy, storyboarding, illustration, animation, revisions, and client communication together at Frogotiv. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2459,11 +2645,16 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>Hey Annabell, saw you're co-founder and CTO of CoCrafter, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2512,11 +2703,16 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>Hey Nicole, saw you're co-founder of Yarn, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2565,11 +2761,16 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>Hey David, saw you're CEO and co-founder of Swift, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2618,11 +2819,16 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>Hey Md, saw you're co-founder and CTO of Octolane AI, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2671,11 +2877,16 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>Hey Joseph, saw you're co-founder of Meticulate, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2724,11 +2935,16 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>Hey Alex, saw you co-founded Basalt Tech with Maximillian Bhatti, a YC W24 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2777,11 +2993,16 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>Hey Elizabeth, saw you're running RevOps solo through PrecisionRevOps for multiple SaaS clients. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2830,11 +3051,16 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>Hey Jeremy, saw you're juggling fractional RevOps/CRO roles across Rev, AgentSync, Ekho, and OperateWise at once. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2883,11 +3109,16 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>Hey Haris, saw your recent post on what RevOps actually does and removing GTM silos. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2936,11 +3167,16 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>Hey Deepa, saw you're advising several high-growth startups at once as a fractional RevOps/strategy leader. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -2989,11 +3225,16 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>Hey Mariya, saw you work as a fractional CFO across multiple early-stage B2B SaaS clients. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3042,11 +3283,16 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>Hey John, saw the dozens of early-stage companies you've helped clean up CRM/HubSpot data at Sequoia Solutions. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3095,11 +3341,16 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>Hey Roberto, saw your posts on pipeline, forecasting, and AI at Revenue Hub Latam. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3148,11 +3399,16 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>Hey Johnathan, saw you built your own AI-powered social media tooling while running The SaaS Consultants. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3201,11 +3457,16 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>Hey Alex, saw you run your own solo HubSpot consulting practice. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3254,11 +3515,16 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>Hey Ajay, saw you run MAWD Agency managing Google Ads, SEO, and websites for small businesses. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3307,11 +3573,16 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>Hey Philip, saw you help companies use AI securely and purposefully as an independent consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3360,11 +3631,16 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>Hey Oles, saw you're running Hey Digital, a performance marketing agency focused specifically on B2B SaaS. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3413,11 +3689,16 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>Hey Becky, saw you help small business owners get time back through BK's Bookkeeping. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3466,11 +3747,16 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>Hey Tom, saw you're part of an AI Mastermind group applying tech-forward solutions to bookkeeping. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3519,11 +3805,16 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>Hey Michael, saw you're running Boldly with a small team of creative minds. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3572,11 +3863,16 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>Hey Michael, saw you're co-founder and de-facto Operations Manager at 10X ERP. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3625,11 +3921,16 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>Hey Pavels, saw you're targeting B2B SaaS founders specifically through Camel Digital. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3678,11 +3979,16 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>Hey Aaron, saw your work helping brands scale with strategic video content and AI repurposing. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3731,11 +4037,16 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>Hey Ebru, saw your take that AI translating doesn't mean localization is solved. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3784,11 +4095,16 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>Hey Crystal, saw you help SaaS founders and CS teams with customer success operations as a fractional consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3837,11 +4153,16 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>Hey Jamiu, saw you're running Hidden Gems, focused on creator-led growth specifically for B2B AI &amp; SaaS companies. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3890,11 +4211,16 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
           <t>Hey Harry, saw you're building 'mate,' an AI growth teammate for small businesses. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3943,11 +4269,16 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>Hey Mihai, saw you're building MspCoreX to replace fragmented MSP tool stacks with one intelligent core. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -3996,11 +4327,16 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
           <t>Hey Michelle, saw your mission of helping small and mid-sized agencies grow through Real Marketing Muscle. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4049,11 +4385,16 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
           <t>Hey Austin, saw you're making AI accessible and practical for entrepreneurs and small business owners at digital3 AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4102,11 +4443,16 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
           <t>Hey Yael, saw you built an AI agent trained on multiple brand voices and content formats at Ashley Digital. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4155,11 +4501,16 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
           <t>Hey Ai, saw you're democratizing access to AI and no-code tools for individuals and small businesses through Common AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4208,11 +4559,16 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
           <t>Hey Vanhishikha, saw you've partnered with 100+ B2B SaaS companies on SEO and content through Contensify. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4261,11 +4617,16 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
           <t>Hey Susan, saw you help founders build self-sufficient teams as a People Ops &amp; Systems consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4314,11 +4675,16 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
           <t>Hey Heidi, saw you focus on People Ops/HR solutions specifically for startups and tech companies. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4367,11 +4733,16 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
           <t>Hey Michelle, saw you provide scalable HR systems for growing teams through Quantum People Ops. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4420,11 +4791,16 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
           <t>Hey Danielle, saw you're passionate about building systems for small businesses and helping agency owners specifically. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4473,11 +4849,16 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
           <t>Hey Anis, saw you help B2B/SaaS companies grow visibility and revenue through SEO and AEO. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4526,11 +4907,16 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
           <t>Hey Peter, saw you're building Nynch, a growth platform specifically for consultants and fractional professionals. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4579,11 +4965,16 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
           <t>Hey Michael, saw you discuss AI integration in podcast production at Fame. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4632,11 +5023,16 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
           <t>Hey Oyinkro, saw you're positioning K.OS VISUALS as a creative GTM partner for fast-growing AI/SaaS companies. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4685,11 +5081,16 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
           <t>Hey Costin, saw you turn complex SaaS products into clear, high-impact video as a strategic video partner. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4738,11 +5139,16 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
           <t>Hey Marek, saw you help companies adopt DevOps culture through on-site workshops and consulting at pipetail.io. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4791,11 +5197,16 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
           <t>Hey Michal, saw you built a RAG platform for 15k+ users and now consult on DevOps culture and AI adoption. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4844,11 +5255,16 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
           <t>Hey Sara, saw you help founders and SMEs turn marketing spend into measurable growth through White Cloud Communications. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4897,11 +5313,16 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
           <t>Hey Jonny, saw you've been 3x Head of Marketing at B2B SaaS startups before going fractional. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -4950,11 +5371,16 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
           <t>Hey Hugo, saw you wrote "Teams in Hell" and are a 1x exited founder now doing fractional growth work. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5003,11 +5429,16 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
           <t>Hey Marcus, saw your observation that companies buy AI licenses, announce it, and six months later only 10% of the team is actually using the tools. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5056,11 +5487,16 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
           <t>Hey David, saw you build intelligent workflows and AI agents using tools like n8n, Make.com, and Airtable. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5109,11 +5545,16 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
           <t>Hey Matthew, saw you specialize in AI platform adoption and implementation at Mission AI Consulting. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5162,11 +5603,16 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
           <t>Hey Adam, saw you've built a lean senior team at Growth Union for early-stage B2B SaaS clients like Writer and Recorded Future. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5215,11 +5661,16 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
           <t>Hey David, saw you're building Lynx Growth Agency around AI-driven marketing and automation. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5268,11 +5719,16 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
           <t>Hey Alex, saw your writing on AI agents in RevOps as CEO of Forecastio. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5321,11 +5777,16 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
           <t>Hey Kristofer, saw your tagline about helping startups supercharge their small RevOps teams. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5374,11 +5835,16 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
           <t>Hey Shaun, saw you're building agentic AI systems as an AI Marketing Engineer while running thisisagency.ai. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5427,11 +5893,16 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
           <t>Hey Sam, saw you're running Origin 63 as a small, results-focused growth agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5480,11 +5951,16 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
           <t>Hey Josh, saw your work on revenue growth and retention at Hüify, a HubSpot partner agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5533,11 +6009,16 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
           <t>Hey Clwyd, saw you work as an AI consultant at Whitehat, helping businesses adopt AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5586,11 +6067,16 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
           <t>Hey Clara, saw you're employee #3 and Chief of Staff at Kairos. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5639,11 +6125,16 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
           <t>Hey Riddhi, saw you're running Thought In A Dot as a content marketing agency and brand strategist. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5692,11 +6183,16 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
           <t>Hey John, saw you founded Creative Engine, a branding and digital marketing agency in Austin. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5745,11 +6241,16 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
           <t>Hey Laney, saw you run The Design Boutique and pride yourselves on being able to pivot quickly as a small shop. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5798,11 +6299,16 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
           <t>Hey Thomas, saw you founded Venture Visuals, a creative agency in Seattle. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5851,11 +6357,16 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
           <t>Hey Santosh, saw you're running Visual Best, an AI creative production agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5904,11 +6415,16 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
           <t>Hey David, saw you describe your business as having an AI-first mindset while running Sounds Good Agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -5957,11 +6473,16 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
           <t>Hey Mark, saw you're a pioneer in AI-native software engineering as founder of SoftwareFactory.ai. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6010,11 +6531,16 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
           <t>Hey Dylan, saw you install AI systems into service businesses as an independent consultant. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6063,11 +6589,16 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
           <t>Hey Alex, saw you're co-founder/CEO of Intryc, a Y Combinator S24 startup. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6116,11 +6647,16 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
           <t>Hey Arham, saw you founded Pixated, a performance marketing agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6169,11 +6705,16 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
           <t>Hey Alex, saw you're scaling DTC ecommerce brands through Tierra. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6222,11 +6763,16 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
           <t>Hey Beckie, saw you run a boutique recruiting agency with a niche sector focus. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6275,11 +6821,16 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
           <t>Hey Katie, saw your writing on balancing technology and human connection in recruiting at CollabRecruit. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6328,11 +6879,16 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
           <t>Hey Jennifer, saw you founded Bookkeeping Done Right to serve small and medium businesses in South Florida. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6381,11 +6937,16 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
           <t>Hey Parry, saw you're leading a team of senior PR leaders at Crackle PR. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6434,11 +6995,16 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
           <t>Hey Carin, saw your writing on AI strategy in communications. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6487,11 +7053,16 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
           <t>Hey Erika, saw you're running 85th &amp; Park, a culture-driven creative marketing and comms agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6540,11 +7111,16 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
           <t>Hey Sam, saw you just founded a new AI automation agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6593,11 +7169,16 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
           <t>Hey M, saw you're running your own web design agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6646,11 +7227,16 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
           <t>Hey Kristen, saw your interest in AI adoption for web design and development. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6699,11 +7285,16 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
           <t>Hey Stefen, saw you co-founded Kelp Creative Agency. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6752,11 +7343,16 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
           <t>Hey Dean, saw you're co-founder and Head of Operations at Superstate. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6805,11 +7401,16 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
           <t>Hey Leah, saw you're co-founder and Head of Operations at See Jane Drill. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6858,11 +7459,16 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
           <t>Hey Evan, saw you're using AI tools like Heygen and Freepik at Boomin' Brands Media. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr">
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6911,11 +7517,16 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
           <t>Hey Yash, saw your AI-led creative production work at Lemonade Creatives. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -6964,11 +7575,16 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
           <t>Hey Adam, saw you built Taia, a workflow system addressing friction in translation processes. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7017,11 +7633,16 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
           <t>Hey Adriana, saw you run Libre Design Studio specifically for founders and startups. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7070,11 +7691,16 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
           <t>Hey Atiqur, saw you founded Design Monks. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="2" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7123,11 +7749,16 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
           <t>Hey Thomas, saw you help B2B SaaS companies turn Customer Success into measurable revenue at Revora Consultants. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7176,11 +7807,16 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
           <t>Hey Peter, saw you're building Trendin, an AI-native operating system for influencer agencies. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7229,11 +7865,16 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
           <t>Hey Krishna, saw you built LegalConnect to deliver AI-drafted, solicitor-reviewed legal documents for SMEs. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr">
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7282,11 +7923,16 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
           <t>Hey Jay, saw you run Startup Legal Group, serving startup clients directly. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="2" t="inlineStr">
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7335,11 +7981,16 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
           <t>Hey Nahme, saw you're running Research Connections, a market research consulting and field management company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr"/>
-      <c r="K130" s="2" t="inlineStr">
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7388,11 +8039,16 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
           <t>Hey Jake, saw you run JakeWu Market Research, a small solo-founder shop. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr">
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7441,11 +8097,16 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
           <t>Hey Jenna, saw you founded an education platform teaching interior designers to use AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="2" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7494,11 +8155,16 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
           <t>Hey Nina, saw you co-founded Curioso, an assemblage of designers, architects, and business-minded creatives. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr"/>
-      <c r="K133" s="2" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7547,11 +8213,16 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
           <t>Hey Snehadeep, saw you use AI-driven design tools as founder of Studio ORCHIVIZ. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7600,11 +8271,16 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
           <t>Hey Akeem, saw you're co-founder of Thread, a YC W23 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7653,11 +8329,16 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
           <t>Hey Ty, saw you're co-founder and CEO of inBuild, a YC W23 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7706,11 +8387,16 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
           <t>Hey Vlad, saw you're co-founder of Infisical, a YC W23 company. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr"/>
-      <c r="K137" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7759,11 +8445,16 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
           <t>Hey Neel, saw you're co-founder of Clueso, an AI video creation company from YC W23. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7812,11 +8503,16 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
           <t>Hey Sourav, saw you focus on brand strategy specifically for early-stage startups at Branded Minds. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7865,11 +8561,16 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
           <t>Hey Ulli, saw you run First The Trousers as a brand strategy and positioning consultancy. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7918,11 +8619,16 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
           <t>Hey Lance, saw you're building BrandChef.ai. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="2" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -7971,11 +8677,16 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
           <t>Hey Branden, saw you founded Build, a branding agency built around practical design. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8024,11 +8735,16 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
           <t>Hey Jill, saw you run Your HR Partners as a boutique human resources services company. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr"/>
-      <c r="K143" s="2" t="inlineStr">
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8077,11 +8793,16 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
           <t>Hey Apoorv, saw you're helping B2B SaaS companies with AI search visibility at Found On AI. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr"/>
-      <c r="K144" s="2" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8130,11 +8851,16 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
           <t>Hey Matt, saw you co-founded Sheepdog Projects to offer BI consulting and data strategy services. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr"/>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8183,11 +8909,16 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
           <t>Hey Jason, saw you discuss how AI is being integrated into podcast production workflows at B2B Better. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr"/>
-      <c r="K146" s="2" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8236,11 +8967,16 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
           <t>Hey Samuel, saw you run a fractional CMO agency in New York. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr"/>
-      <c r="K147" s="2" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8289,11 +9025,16 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
           <t>Hey Joshua, saw you're driving data-driven growth for clients as founder of sōsh. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr"/>
-      <c r="K148" s="2" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8342,11 +9083,16 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
+          <t>Question about your team and AI tools</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
           <t>Hey Kristen, saw you co-founded a boutique full-service digital marketing consulting firm for B2B professional services. Question for you: does your team use ChatGPT or Claude much, and if so, is it mostly everyone working solo, or is there any shared visibility into what people are trying or deciding? Curious how you all handle it.</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr"/>
-      <c r="K149" s="2" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8395,11 +9141,16 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
           <t>Hey Dawn, saw you partner with early-stage founders and CEOs to build brands that scale. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr"/>
-      <c r="K150" s="2" t="inlineStr">
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8448,11 +9199,16 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
+          <t>Question about your clients and AI tools</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
           <t>Hey Miranda, saw you're empowering small businesses with AI tools and services through AI Consulting Network. Question for you: across the teams or clients you work with, is AI tool usage mostly a solo thing per person, or is there any shared visibility into what's being tried? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr">
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8460,7 +9216,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8626,7 +9382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8637,9 +9393,10 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8685,15 +9442,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Draft Message</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Date Found</t>
         </is>
@@ -8742,11 +9504,16 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Question about AI usage in your community</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>Hey Darrell, saw your newsletter on marketing ops team structure and career growth. Question for you: is solo AI tool usage with little shared visibility across a team something you hear about often from your community? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8795,11 +9562,16 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>Question about AI usage in your community</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>Hey Jen, saw your weekly newsletter for the marketing ops community. Question for you: is solo AI tool usage with little shared visibility across a team something you hear about often from your community? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8848,11 +9620,16 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>Question about AI usage in your community</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>Hey Mike, saw MO Pros hitting 4,000+ marketing/RevOps members. Question for you: is solo AI tool usage with little shared visibility across a team something you hear about often from your community? Curious what you're seeing.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
@@ -8860,7 +9637,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
